--- a/spoilers/trades.xlsx
+++ b/spoilers/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F096020-45CC-49AF-8D55-EFBBD8DA9743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A935C6AF-8619-4626-AA4C-7181CBBD84DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -861,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1010,27 +1010,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1464,9 +1482,9 @@
   <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12" style="27" customWidth="1"/>
+    <col min="2" max="2" width="18" style="27" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="27" customWidth="1"/>
     <col min="4" max="4" width="8" style="27" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="10" style="27" customWidth="1"/>
@@ -1479,13 +1497,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="18" t="s">
         <v>23</v>
       </c>
       <c r="D1" s="18" t="s">
@@ -1517,13 +1535,13 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="19">
@@ -1551,13 +1569,13 @@
       <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="19">
@@ -1587,13 +1605,13 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="19">
@@ -1623,13 +1641,13 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="19">
@@ -1659,13 +1677,13 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="19">
@@ -1695,13 +1713,13 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="19">
@@ -1729,13 +1747,13 @@
       <c r="L7" s="36"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="19">
@@ -1763,13 +1781,13 @@
       <c r="L8" s="36"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="19">
@@ -1799,13 +1817,13 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="19">
@@ -1835,13 +1853,13 @@
       </c>
     </row>
     <row r="11" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="20">
@@ -1871,13 +1889,13 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="19">
@@ -1905,13 +1923,13 @@
       <c r="L12" s="36"/>
     </row>
     <row r="13" spans="1:12" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="19">
@@ -1943,13 +1961,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="19">
@@ -1977,13 +1995,13 @@
       <c r="L14" s="36"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D15" s="19">
@@ -2011,13 +2029,13 @@
       <c r="L15" s="36"/>
     </row>
     <row r="16" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="19">
@@ -2047,13 +2065,13 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="20">
@@ -2083,13 +2101,13 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="19">
@@ -2121,13 +2139,13 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="19">
@@ -2155,13 +2173,13 @@
       <c r="L19" s="36"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="19">
@@ -2189,13 +2207,13 @@
       <c r="L20" s="36"/>
     </row>
     <row r="21" spans="1:12" s="13" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="21">
@@ -2225,13 +2243,13 @@
       </c>
     </row>
     <row r="22" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="22" t="s">
         <v>63</v>
       </c>
       <c r="D22" s="22">
@@ -2259,13 +2277,13 @@
       <c r="L22" s="38"/>
     </row>
     <row r="23" spans="1:12" s="13" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="21">
@@ -2297,13 +2315,13 @@
       </c>
     </row>
     <row r="24" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="23" t="s">
         <v>69</v>
       </c>
       <c r="D24" s="23">
@@ -2331,13 +2349,13 @@
       <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="23" t="s">
         <v>69</v>
       </c>
       <c r="D25" s="23">
@@ -2365,13 +2383,13 @@
       <c r="L25" s="47"/>
     </row>
     <row r="26" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="23" t="s">
         <v>69</v>
       </c>
       <c r="D26" s="23">
@@ -2399,13 +2417,13 @@
       <c r="L26" s="47"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="23" t="s">
         <v>69</v>
       </c>
       <c r="D27" s="23">
@@ -2433,13 +2451,13 @@
       <c r="L27" s="48"/>
     </row>
     <row r="28" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D28" s="24">
@@ -2469,13 +2487,13 @@
       </c>
     </row>
     <row r="29" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="24">
@@ -2503,13 +2521,13 @@
       <c r="L29" s="49"/>
     </row>
     <row r="30" spans="1:12" s="8" customFormat="1" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="24">
@@ -2541,13 +2559,13 @@
       </c>
     </row>
     <row r="31" spans="1:12" s="8" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="24">
@@ -2579,13 +2597,13 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="25" t="s">
         <v>90</v>
       </c>
       <c r="D32" s="25">
@@ -2615,13 +2633,13 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="25" t="s">
         <v>90</v>
       </c>
       <c r="D33" s="25">
@@ -2651,13 +2669,13 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="60" t="s">
         <v>100</v>
       </c>
       <c r="D34" s="23">
@@ -2687,13 +2705,13 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="60" t="s">
         <v>100</v>
       </c>
       <c r="D35" s="23">
@@ -2723,13 +2741,13 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="60" t="s">
         <v>100</v>
       </c>
       <c r="D36" s="23">
@@ -2759,13 +2777,13 @@
       </c>
     </row>
     <row r="37" spans="1:12" s="30" customFormat="1" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D37" s="33">
@@ -2795,13 +2813,13 @@
       <c r="L37" s="51"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D38" s="23">
@@ -2829,13 +2847,13 @@
       <c r="L38" s="47"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="23">
@@ -2863,13 +2881,13 @@
       <c r="L39" s="47"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D40" s="23">
@@ -2897,13 +2915,13 @@
       <c r="L40" s="47"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D41" s="23">
@@ -2931,13 +2949,13 @@
       <c r="L41" s="47"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D42" s="23">
@@ -2965,13 +2983,13 @@
       <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D43" s="23">
@@ -3001,13 +3019,13 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D44" s="31">
@@ -3037,13 +3055,13 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D45" s="31">
@@ -3073,13 +3091,13 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D46" s="31">
@@ -3109,13 +3127,13 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D47" s="31">
@@ -3143,13 +3161,13 @@
       <c r="L47" s="47"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D48" s="31">
@@ -3177,13 +3195,13 @@
       <c r="L48" s="47"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D49" s="31">
@@ -3211,13 +3229,13 @@
       <c r="L49" s="47"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="60" t="s">
         <v>101</v>
       </c>
       <c r="D50" s="31">
@@ -3245,13 +3263,13 @@
       <c r="L50" s="47"/>
     </row>
     <row r="51" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D51" s="23">
@@ -3281,13 +3299,13 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D52" s="23">
@@ -3315,13 +3333,13 @@
       <c r="L52" s="47"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D53" s="23">
@@ -3349,13 +3367,13 @@
       <c r="L53" s="47"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D54" s="23">
@@ -3383,13 +3401,13 @@
       <c r="L54" s="47"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D55" s="23">
@@ -3417,13 +3435,13 @@
       <c r="L55" s="47"/>
     </row>
     <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="23">
@@ -3453,13 +3471,13 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="23">
@@ -3489,13 +3507,13 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="31">
@@ -3525,13 +3543,13 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D59" s="23">
@@ -3559,13 +3577,13 @@
       <c r="L59" s="49"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D60" s="23">
@@ -3593,13 +3611,13 @@
       <c r="L60" s="49"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D61" s="23">
@@ -3627,13 +3645,13 @@
       <c r="L61" s="49"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="23">
@@ -4021,13 +4039,13 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D73" s="31">
@@ -4057,13 +4075,13 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D74" s="23">
@@ -4093,13 +4111,13 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D75" s="23">
@@ -4129,13 +4147,13 @@
       </c>
     </row>
     <row r="76" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D76" s="23">
@@ -4165,13 +4183,13 @@
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="23">
@@ -4201,13 +4219,13 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="60" t="s">
         <v>103</v>
       </c>
       <c r="D78" s="23">
@@ -4237,13 +4255,13 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A79" s="56" t="s">
+      <c r="A79" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="26" t="s">
         <v>168</v>
       </c>
       <c r="D79" s="26">
@@ -4273,13 +4291,13 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="56" t="s">
+      <c r="A80" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="26" t="s">
         <v>173</v>
       </c>
       <c r="D80" s="26">
@@ -4307,13 +4325,13 @@
       <c r="L80" s="48"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="56" t="s">
+      <c r="A81" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="26" t="s">
         <v>173</v>
       </c>
       <c r="D81" s="26">
@@ -4341,13 +4359,13 @@
       <c r="L81" s="48"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="26" t="s">
         <v>173</v>
       </c>
       <c r="D82" s="26">
@@ -4375,13 +4393,13 @@
       <c r="L82" s="48"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="56" t="s">
+      <c r="A83" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="26" t="s">
         <v>173</v>
       </c>
       <c r="D83" s="26">
@@ -4409,13 +4427,13 @@
       <c r="L83" s="48"/>
     </row>
     <row r="84" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="26" t="s">
         <v>181</v>
       </c>
       <c r="D84" s="26">
@@ -4440,18 +4458,18 @@
       <c r="K84" s="28">
         <v>5</v>
       </c>
-      <c r="L84" s="59" t="s">
+      <c r="L84" s="57" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="26" t="s">
         <v>181</v>
       </c>
       <c r="D85" s="26">
@@ -4476,16 +4494,16 @@
       <c r="K85" s="29">
         <v>30</v>
       </c>
-      <c r="L85" s="59"/>
+      <c r="L85" s="57"/>
     </row>
     <row r="86" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="26" t="s">
         <v>181</v>
       </c>
       <c r="D86" s="26">
@@ -4510,7 +4528,7 @@
       <c r="K86" s="29">
         <v>30</v>
       </c>
-      <c r="L86" s="59" t="s">
+      <c r="L86" s="57" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4539,7 +4557,7 @@
       <c r="H87" s="33">
         <v>1</v>
       </c>
-      <c r="I87" s="57" t="s">
+      <c r="I87" s="56" t="s">
         <v>185</v>
       </c>
       <c r="J87" s="28">
@@ -4548,18 +4566,18 @@
       <c r="K87" s="28">
         <v>5</v>
       </c>
-      <c r="L87" s="59" t="s">
+      <c r="L87" s="57" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="56" t="s">
+      <c r="A88" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="58" t="s">
+      <c r="B88" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="26" t="s">
         <v>168</v>
       </c>
       <c r="D88" s="26">
@@ -4589,13 +4607,13 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="56" t="s">
+      <c r="A89" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B89" s="58" t="s">
+      <c r="B89" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="26" t="s">
         <v>168</v>
       </c>
       <c r="D89" s="26">
@@ -4625,13 +4643,13 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="56" t="s">
+      <c r="A90" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="26" t="s">
         <v>191</v>
       </c>
       <c r="D90" s="26">
@@ -4656,16 +4674,16 @@
       <c r="K90" s="28">
         <v>0</v>
       </c>
-      <c r="L90" s="59"/>
+      <c r="L90" s="57"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="56" t="s">
+      <c r="A91" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="26" t="s">
         <v>191</v>
       </c>
       <c r="D91" s="26">
@@ -4693,13 +4711,13 @@
       <c r="L91" s="48"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="56" t="s">
+      <c r="A92" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="26" t="s">
         <v>191</v>
       </c>
       <c r="D92" s="26">
@@ -4727,13 +4745,13 @@
       <c r="L92" s="48"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="56" t="s">
+      <c r="A93" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="26" t="s">
         <v>191</v>
       </c>
       <c r="D93" s="26">
@@ -4761,101 +4779,101 @@
       <c r="L93" s="48"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="60" t="s">
+      <c r="A94" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="B94" s="61"/>
-      <c r="C94" s="62" t="s">
+      <c r="B94" s="65"/>
+      <c r="C94" s="66" t="s">
         <v>200</v>
       </c>
-      <c r="D94" s="65"/>
-      <c r="E94" s="64"/>
-      <c r="F94" s="65"/>
-      <c r="G94" s="64"/>
-      <c r="H94" s="65"/>
+      <c r="D94" s="59"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="59"/>
       <c r="I94" s="41"/>
       <c r="J94" s="28"/>
       <c r="K94" s="28"/>
       <c r="L94" s="48"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="63" t="s">
+      <c r="A95" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="B95" s="64"/>
-      <c r="C95" s="63" t="s">
+      <c r="B95" s="59"/>
+      <c r="C95" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="D95" s="65"/>
-      <c r="E95" s="64"/>
-      <c r="F95" s="65"/>
-      <c r="G95" s="64"/>
-      <c r="H95" s="65"/>
+      <c r="D95" s="59"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="58"/>
+      <c r="H95" s="59"/>
       <c r="I95" s="41"/>
       <c r="J95" s="28"/>
       <c r="K95" s="28"/>
       <c r="L95" s="48"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="63" t="s">
+      <c r="A96" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="B96" s="64"/>
-      <c r="C96" s="63" t="s">
+      <c r="B96" s="59"/>
+      <c r="C96" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="D96" s="65"/>
-      <c r="E96" s="64"/>
-      <c r="F96" s="65"/>
-      <c r="G96" s="64"/>
-      <c r="H96" s="65"/>
+      <c r="D96" s="59"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="59"/>
+      <c r="G96" s="58"/>
+      <c r="H96" s="59"/>
       <c r="I96" s="41"/>
       <c r="J96" s="28"/>
       <c r="K96" s="28"/>
       <c r="L96" s="48"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="63" t="s">
+      <c r="A97" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="B97" s="64"/>
-      <c r="C97" s="63" t="s">
+      <c r="B97" s="59"/>
+      <c r="C97" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="D97" s="65"/>
-      <c r="E97" s="64"/>
-      <c r="F97" s="65"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="65"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="58"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="58"/>
+      <c r="H97" s="59"/>
       <c r="I97" s="41"/>
       <c r="J97" s="28"/>
       <c r="K97" s="28"/>
       <c r="L97" s="48"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="63" t="s">
+      <c r="A98" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="B98" s="64"/>
-      <c r="C98" s="63" t="s">
+      <c r="B98" s="59"/>
+      <c r="C98" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="D98" s="65"/>
-      <c r="E98" s="64"/>
-      <c r="F98" s="65"/>
-      <c r="G98" s="64"/>
-      <c r="H98" s="65"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="58"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="58"/>
+      <c r="H98" s="59"/>
       <c r="I98" s="41"/>
       <c r="J98" s="28"/>
       <c r="K98" s="28"/>
       <c r="L98" s="48"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="66" t="s">
+      <c r="A99" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="B99" s="64"/>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="59"/>
+      <c r="C99" s="69" t="s">
         <v>205</v>
       </c>
       <c r="D99" s="26"/>
@@ -4869,9 +4887,9 @@
       <c r="L99" s="48"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
+      <c r="A100" s="26"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
       <c r="D100" s="26"/>
       <c r="E100" s="5"/>
       <c r="F100" s="26"/>
@@ -4883,9 +4901,9 @@
       <c r="L100" s="48"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
+      <c r="A101" s="26"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
       <c r="D101" s="26"/>
       <c r="E101" s="5"/>
       <c r="F101" s="26"/>
@@ -4897,9 +4915,9 @@
       <c r="L101" s="48"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
+      <c r="A102" s="26"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
       <c r="D102" s="26"/>
       <c r="E102" s="5"/>
       <c r="F102" s="26"/>
@@ -4911,9 +4929,9 @@
       <c r="L102" s="48"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
+      <c r="A103" s="26"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
       <c r="D103" s="26"/>
       <c r="E103" s="5"/>
       <c r="F103" s="26"/>
@@ -4925,9 +4943,9 @@
       <c r="L103" s="48"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
+      <c r="A104" s="26"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
       <c r="D104" s="26"/>
       <c r="E104" s="5"/>
       <c r="F104" s="26"/>
@@ -4939,9 +4957,9 @@
       <c r="L104" s="48"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
+      <c r="A105" s="26"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
       <c r="D105" s="26"/>
       <c r="E105" s="5"/>
       <c r="F105" s="26"/>
@@ -4953,9 +4971,9 @@
       <c r="L105" s="48"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
+      <c r="A106" s="26"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="5"/>
       <c r="F106" s="26"/>
@@ -4967,9 +4985,9 @@
       <c r="L106" s="48"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
+      <c r="A107" s="26"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="5"/>
       <c r="F107" s="26"/>
@@ -4981,9 +4999,9 @@
       <c r="L107" s="48"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
+      <c r="A108" s="26"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="5"/>
       <c r="F108" s="26"/>
@@ -4995,9 +5013,9 @@
       <c r="L108" s="48"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="5"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
+      <c r="A109" s="26"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
       <c r="D109" s="26"/>
       <c r="E109" s="5"/>
       <c r="F109" s="26"/>
@@ -5009,9 +5027,9 @@
       <c r="L109" s="48"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
+      <c r="A110" s="26"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
       <c r="D110" s="26"/>
       <c r="E110" s="5"/>
       <c r="F110" s="26"/>
@@ -5023,9 +5041,9 @@
       <c r="L110" s="48"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
+      <c r="A111" s="26"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
       <c r="D111" s="26"/>
       <c r="E111" s="5"/>
       <c r="F111" s="26"/>
@@ -5037,9 +5055,9 @@
       <c r="L111" s="48"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
+      <c r="A112" s="26"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
       <c r="D112" s="26"/>
       <c r="E112" s="5"/>
       <c r="F112" s="26"/>
@@ -5051,9 +5069,9 @@
       <c r="L112" s="48"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
+      <c r="A113" s="26"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
       <c r="D113" s="26"/>
       <c r="E113" s="5"/>
       <c r="F113" s="26"/>
@@ -5065,9 +5083,9 @@
       <c r="L113" s="48"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
+      <c r="A114" s="26"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
       <c r="D114" s="26"/>
       <c r="E114" s="5"/>
       <c r="F114" s="26"/>
@@ -5079,9 +5097,9 @@
       <c r="L114" s="48"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
+      <c r="A115" s="26"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
       <c r="D115" s="26"/>
       <c r="E115" s="5"/>
       <c r="F115" s="26"/>
@@ -5093,9 +5111,9 @@
       <c r="L115" s="48"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
+      <c r="A116" s="26"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
       <c r="D116" s="26"/>
       <c r="E116" s="5"/>
       <c r="F116" s="26"/>
@@ -5107,9 +5125,9 @@
       <c r="L116" s="48"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
+      <c r="A117" s="26"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
       <c r="D117" s="26"/>
       <c r="E117" s="5"/>
       <c r="F117" s="26"/>
@@ -5121,9 +5139,9 @@
       <c r="L117" s="48"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="5"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
+      <c r="A118" s="26"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
       <c r="D118" s="26"/>
       <c r="E118" s="5"/>
       <c r="F118" s="26"/>
@@ -5135,9 +5153,9 @@
       <c r="L118" s="48"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
+      <c r="A119" s="26"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
       <c r="D119" s="26"/>
       <c r="E119" s="5"/>
       <c r="F119" s="26"/>
@@ -5149,9 +5167,9 @@
       <c r="L119" s="48"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
+      <c r="A120" s="26"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
       <c r="D120" s="26"/>
       <c r="E120" s="5"/>
       <c r="F120" s="26"/>
@@ -5163,9 +5181,9 @@
       <c r="L120" s="48"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
+      <c r="A121" s="26"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
       <c r="D121" s="26"/>
       <c r="E121" s="5"/>
       <c r="F121" s="26"/>
@@ -5177,9 +5195,9 @@
       <c r="L121" s="48"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
+      <c r="A122" s="26"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
       <c r="D122" s="26"/>
       <c r="E122" s="5"/>
       <c r="F122" s="26"/>
@@ -5191,9 +5209,9 @@
       <c r="L122" s="48"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
+      <c r="A123" s="26"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
       <c r="D123" s="26"/>
       <c r="E123" s="5"/>
       <c r="F123" s="26"/>
@@ -5205,9 +5223,9 @@
       <c r="L123" s="48"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
+      <c r="A124" s="26"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
       <c r="D124" s="26"/>
       <c r="E124" s="5"/>
       <c r="F124" s="26"/>
@@ -5219,9 +5237,9 @@
       <c r="L124" s="48"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
+      <c r="A125" s="26"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
       <c r="D125" s="26"/>
       <c r="E125" s="5"/>
       <c r="F125" s="26"/>
@@ -5233,9 +5251,9 @@
       <c r="L125" s="48"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
+      <c r="A126" s="26"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
       <c r="D126" s="26"/>
       <c r="E126" s="5"/>
       <c r="F126" s="26"/>
@@ -5247,9 +5265,9 @@
       <c r="L126" s="48"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
+      <c r="A127" s="26"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
       <c r="D127" s="26"/>
       <c r="E127" s="5"/>
       <c r="F127" s="26"/>
@@ -5261,9 +5279,9 @@
       <c r="L127" s="48"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
+      <c r="A128" s="26"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
       <c r="D128" s="26"/>
       <c r="E128" s="5"/>
       <c r="F128" s="26"/>
@@ -5275,9 +5293,9 @@
       <c r="L128" s="48"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
+      <c r="A129" s="26"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
       <c r="D129" s="26"/>
       <c r="E129" s="5"/>
       <c r="F129" s="26"/>
@@ -5289,9 +5307,9 @@
       <c r="L129" s="48"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
+      <c r="A130" s="26"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
       <c r="D130" s="26"/>
       <c r="E130" s="5"/>
       <c r="F130" s="26"/>
@@ -5303,9 +5321,9 @@
       <c r="L130" s="48"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
+      <c r="A131" s="26"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
       <c r="D131" s="26"/>
       <c r="E131" s="5"/>
       <c r="F131" s="26"/>
@@ -5317,9 +5335,9 @@
       <c r="L131" s="48"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
+      <c r="A132" s="26"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
       <c r="D132" s="26"/>
       <c r="E132" s="5"/>
       <c r="F132" s="26"/>
@@ -5331,9 +5349,9 @@
       <c r="L132" s="48"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="5"/>
+      <c r="A133" s="26"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
       <c r="D133" s="26"/>
       <c r="E133" s="5"/>
       <c r="F133" s="26"/>
@@ -5345,9 +5363,9 @@
       <c r="L133" s="48"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
+      <c r="A134" s="26"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
       <c r="D134" s="26"/>
       <c r="E134" s="5"/>
       <c r="F134" s="26"/>
@@ -5359,9 +5377,9 @@
       <c r="L134" s="48"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="5"/>
+      <c r="A135" s="26"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
       <c r="D135" s="26"/>
       <c r="E135" s="5"/>
       <c r="F135" s="26"/>
@@ -5373,9 +5391,9 @@
       <c r="L135" s="48"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="5"/>
+      <c r="A136" s="26"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
       <c r="D136" s="26"/>
       <c r="E136" s="5"/>
       <c r="F136" s="26"/>
@@ -5387,9 +5405,9 @@
       <c r="L136" s="48"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="5"/>
+      <c r="A137" s="26"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
       <c r="D137" s="26"/>
       <c r="E137" s="5"/>
       <c r="F137" s="26"/>
@@ -5401,9 +5419,9 @@
       <c r="L137" s="48"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="5"/>
+      <c r="A138" s="26"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
       <c r="D138" s="26"/>
       <c r="E138" s="5"/>
       <c r="F138" s="26"/>
@@ -5415,9 +5433,9 @@
       <c r="L138" s="48"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
       <c r="D139" s="26"/>
       <c r="E139" s="5"/>
       <c r="F139" s="26"/>
@@ -5429,9 +5447,9 @@
       <c r="L139" s="48"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
       <c r="D140" s="26"/>
       <c r="E140" s="5"/>
       <c r="F140" s="26"/>
@@ -5443,9 +5461,9 @@
       <c r="L140" s="48"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A141" s="5"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="5"/>
+      <c r="A141" s="26"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
       <c r="D141" s="26"/>
       <c r="E141" s="5"/>
       <c r="F141" s="26"/>
@@ -5457,9 +5475,9 @@
       <c r="L141" s="48"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" s="5"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="5"/>
+      <c r="A142" s="26"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="26"/>
       <c r="D142" s="26"/>
       <c r="E142" s="5"/>
       <c r="F142" s="26"/>
@@ -5471,9 +5489,9 @@
       <c r="L142" s="48"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
+      <c r="A143" s="26"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="26"/>
       <c r="D143" s="26"/>
       <c r="E143" s="5"/>
       <c r="F143" s="26"/>
@@ -5485,9 +5503,9 @@
       <c r="L143" s="48"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5"/>
+      <c r="A144" s="26"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="26"/>
       <c r="D144" s="26"/>
       <c r="E144" s="5"/>
       <c r="F144" s="26"/>
@@ -5499,9 +5517,9 @@
       <c r="L144" s="48"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" s="5"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="5"/>
+      <c r="A145" s="26"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="26"/>
       <c r="D145" s="26"/>
       <c r="E145" s="5"/>
       <c r="F145" s="26"/>
@@ -5513,9 +5531,9 @@
       <c r="L145" s="48"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" s="5"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="5"/>
+      <c r="A146" s="26"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="26"/>
       <c r="D146" s="26"/>
       <c r="E146" s="5"/>
       <c r="F146" s="26"/>
@@ -5527,9 +5545,9 @@
       <c r="L146" s="48"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" s="5"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
+      <c r="A147" s="26"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
       <c r="D147" s="26"/>
       <c r="E147" s="5"/>
       <c r="F147" s="26"/>
@@ -5541,9 +5559,9 @@
       <c r="L147" s="48"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
+      <c r="A148" s="26"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
       <c r="D148" s="26"/>
       <c r="E148" s="5"/>
       <c r="F148" s="26"/>
@@ -5555,9 +5573,9 @@
       <c r="L148" s="48"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" s="5"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="5"/>
+      <c r="A149" s="26"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
       <c r="D149" s="26"/>
       <c r="E149" s="5"/>
       <c r="F149" s="26"/>
@@ -5569,9 +5587,9 @@
       <c r="L149" s="48"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" s="5"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
+      <c r="A150" s="26"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
       <c r="D150" s="26"/>
       <c r="E150" s="5"/>
       <c r="F150" s="26"/>
@@ -5583,9 +5601,9 @@
       <c r="L150" s="48"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" s="5"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
+      <c r="A151" s="26"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
       <c r="D151" s="26"/>
       <c r="E151" s="5"/>
       <c r="F151" s="26"/>
@@ -5597,9 +5615,9 @@
       <c r="L151" s="48"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
+      <c r="A152" s="26"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
       <c r="D152" s="26"/>
       <c r="E152" s="5"/>
       <c r="F152" s="26"/>
@@ -5611,9 +5629,9 @@
       <c r="L152" s="48"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A153" s="5"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="5"/>
+      <c r="A153" s="26"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="26"/>
       <c r="D153" s="26"/>
       <c r="E153" s="5"/>
       <c r="F153" s="26"/>
@@ -5625,9 +5643,9 @@
       <c r="L153" s="48"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A154" s="5"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="5"/>
+      <c r="A154" s="26"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="26"/>
       <c r="D154" s="26"/>
       <c r="E154" s="5"/>
       <c r="F154" s="26"/>
@@ -5639,9 +5657,9 @@
       <c r="L154" s="48"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" s="5"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
+      <c r="A155" s="26"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="26"/>
       <c r="D155" s="26"/>
       <c r="E155" s="5"/>
       <c r="F155" s="26"/>
@@ -5653,9 +5671,9 @@
       <c r="L155" s="48"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" s="5"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
+      <c r="A156" s="26"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="26"/>
       <c r="D156" s="26"/>
       <c r="E156" s="5"/>
       <c r="F156" s="26"/>
@@ -5667,9 +5685,9 @@
       <c r="L156" s="48"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" s="5"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="5"/>
+      <c r="A157" s="26"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="26"/>
       <c r="D157" s="26"/>
       <c r="E157" s="5"/>
       <c r="F157" s="26"/>
@@ -5681,9 +5699,9 @@
       <c r="L157" s="48"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" s="5"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="5"/>
+      <c r="A158" s="26"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="26"/>
       <c r="D158" s="26"/>
       <c r="E158" s="5"/>
       <c r="F158" s="26"/>
@@ -5695,9 +5713,9 @@
       <c r="L158" s="48"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" s="5"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="5"/>
+      <c r="A159" s="26"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="26"/>
       <c r="D159" s="26"/>
       <c r="E159" s="5"/>
       <c r="F159" s="26"/>
@@ -5709,9 +5727,9 @@
       <c r="L159" s="48"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" s="5"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="5"/>
+      <c r="A160" s="26"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="26"/>
       <c r="D160" s="26"/>
       <c r="E160" s="5"/>
       <c r="F160" s="26"/>
@@ -5723,9 +5741,9 @@
       <c r="L160" s="48"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" s="5"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="5"/>
+      <c r="A161" s="26"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="26"/>
       <c r="D161" s="26"/>
       <c r="E161" s="5"/>
       <c r="F161" s="26"/>
@@ -5737,9 +5755,9 @@
       <c r="L161" s="48"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A162" s="5"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="5"/>
+      <c r="A162" s="26"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="26"/>
       <c r="D162" s="26"/>
       <c r="E162" s="5"/>
       <c r="F162" s="26"/>
@@ -5751,9 +5769,9 @@
       <c r="L162" s="48"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
+      <c r="A163" s="26"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="26"/>
       <c r="D163" s="26"/>
       <c r="E163" s="5"/>
       <c r="F163" s="26"/>
@@ -5765,9 +5783,9 @@
       <c r="L163" s="48"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
+      <c r="A164" s="26"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="26"/>
       <c r="D164" s="26"/>
       <c r="E164" s="5"/>
       <c r="F164" s="26"/>
@@ -5779,9 +5797,9 @@
       <c r="L164" s="48"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A165" s="5"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
+      <c r="A165" s="26"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="26"/>
       <c r="D165" s="26"/>
       <c r="E165" s="5"/>
       <c r="F165" s="26"/>
@@ -5793,9 +5811,9 @@
       <c r="L165" s="48"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A166" s="5"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="5"/>
+      <c r="A166" s="26"/>
+      <c r="B166" s="26"/>
+      <c r="C166" s="26"/>
       <c r="D166" s="26"/>
       <c r="E166" s="5"/>
       <c r="F166" s="26"/>
@@ -5807,9 +5825,9 @@
       <c r="L166" s="48"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="5"/>
+      <c r="A167" s="26"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
       <c r="D167" s="26"/>
       <c r="E167" s="5"/>
       <c r="F167" s="26"/>
@@ -5821,9 +5839,9 @@
       <c r="L167" s="48"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A168" s="5"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="5"/>
+      <c r="A168" s="26"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="26"/>
       <c r="D168" s="26"/>
       <c r="E168" s="5"/>
       <c r="F168" s="26"/>
@@ -5835,9 +5853,9 @@
       <c r="L168" s="48"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A169" s="5"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="5"/>
+      <c r="A169" s="26"/>
+      <c r="B169" s="26"/>
+      <c r="C169" s="26"/>
       <c r="D169" s="26"/>
       <c r="E169" s="5"/>
       <c r="F169" s="26"/>
@@ -5849,9 +5867,9 @@
       <c r="L169" s="48"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A170" s="5"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="5"/>
+      <c r="A170" s="26"/>
+      <c r="B170" s="26"/>
+      <c r="C170" s="26"/>
       <c r="D170" s="26"/>
       <c r="E170" s="5"/>
       <c r="F170" s="26"/>
@@ -5863,9 +5881,9 @@
       <c r="L170" s="48"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A171" s="5"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="5"/>
+      <c r="A171" s="26"/>
+      <c r="B171" s="26"/>
+      <c r="C171" s="26"/>
       <c r="D171" s="26"/>
       <c r="E171" s="5"/>
       <c r="F171" s="26"/>
@@ -5877,9 +5895,9 @@
       <c r="L171" s="48"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A172" s="5"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
+      <c r="A172" s="26"/>
+      <c r="B172" s="26"/>
+      <c r="C172" s="26"/>
       <c r="D172" s="26"/>
       <c r="E172" s="5"/>
       <c r="F172" s="26"/>
@@ -5891,9 +5909,9 @@
       <c r="L172" s="48"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A173" s="5"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
+      <c r="A173" s="26"/>
+      <c r="B173" s="26"/>
+      <c r="C173" s="26"/>
       <c r="D173" s="26"/>
       <c r="E173" s="5"/>
       <c r="F173" s="26"/>
@@ -5905,9 +5923,9 @@
       <c r="L173" s="48"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A174" s="5"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="5"/>
+      <c r="A174" s="26"/>
+      <c r="B174" s="26"/>
+      <c r="C174" s="26"/>
       <c r="D174" s="26"/>
       <c r="E174" s="5"/>
       <c r="F174" s="26"/>
@@ -5919,9 +5937,9 @@
       <c r="L174" s="48"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A175" s="5"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
+      <c r="A175" s="26"/>
+      <c r="B175" s="26"/>
+      <c r="C175" s="26"/>
       <c r="D175" s="26"/>
       <c r="E175" s="5"/>
       <c r="F175" s="26"/>
@@ -5933,9 +5951,9 @@
       <c r="L175" s="48"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A176" s="5"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
+      <c r="A176" s="26"/>
+      <c r="B176" s="26"/>
+      <c r="C176" s="26"/>
       <c r="D176" s="26"/>
       <c r="E176" s="5"/>
       <c r="F176" s="26"/>
@@ -5947,9 +5965,9 @@
       <c r="L176" s="48"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A177" s="5"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="5"/>
+      <c r="A177" s="26"/>
+      <c r="B177" s="26"/>
+      <c r="C177" s="26"/>
       <c r="D177" s="26"/>
       <c r="E177" s="5"/>
       <c r="F177" s="26"/>
@@ -5961,9 +5979,9 @@
       <c r="L177" s="48"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A178" s="5"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="5"/>
+      <c r="A178" s="26"/>
+      <c r="B178" s="26"/>
+      <c r="C178" s="26"/>
       <c r="D178" s="26"/>
       <c r="E178" s="5"/>
       <c r="F178" s="26"/>
@@ -5975,9 +5993,9 @@
       <c r="L178" s="48"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="5"/>
+      <c r="A179" s="26"/>
+      <c r="B179" s="26"/>
+      <c r="C179" s="26"/>
       <c r="D179" s="26"/>
       <c r="E179" s="5"/>
       <c r="F179" s="26"/>
@@ -5989,9 +6007,9 @@
       <c r="L179" s="48"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A180" s="5"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
+      <c r="A180" s="26"/>
+      <c r="B180" s="26"/>
+      <c r="C180" s="26"/>
       <c r="D180" s="26"/>
       <c r="E180" s="5"/>
       <c r="F180" s="26"/>
@@ -6003,9 +6021,9 @@
       <c r="L180" s="48"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A181" s="5"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
+      <c r="A181" s="26"/>
+      <c r="B181" s="26"/>
+      <c r="C181" s="26"/>
       <c r="D181" s="26"/>
       <c r="E181" s="5"/>
       <c r="F181" s="26"/>
@@ -6017,9 +6035,9 @@
       <c r="L181" s="48"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A182" s="5"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="5"/>
+      <c r="A182" s="26"/>
+      <c r="B182" s="26"/>
+      <c r="C182" s="26"/>
       <c r="D182" s="26"/>
       <c r="E182" s="5"/>
       <c r="F182" s="26"/>
@@ -6031,9 +6049,9 @@
       <c r="L182" s="48"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
+      <c r="A183" s="26"/>
+      <c r="B183" s="26"/>
+      <c r="C183" s="26"/>
       <c r="D183" s="26"/>
       <c r="E183" s="5"/>
       <c r="F183" s="26"/>
@@ -6045,9 +6063,9 @@
       <c r="L183" s="48"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="5"/>
+      <c r="A184" s="26"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
       <c r="D184" s="26"/>
       <c r="E184" s="5"/>
       <c r="F184" s="26"/>
@@ -6059,9 +6077,9 @@
       <c r="L184" s="48"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A185" s="5"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="5"/>
+      <c r="A185" s="26"/>
+      <c r="B185" s="26"/>
+      <c r="C185" s="26"/>
       <c r="D185" s="26"/>
       <c r="E185" s="5"/>
       <c r="F185" s="26"/>
@@ -6073,9 +6091,9 @@
       <c r="L185" s="48"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A186" s="5"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
+      <c r="A186" s="26"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="26"/>
       <c r="D186" s="26"/>
       <c r="E186" s="5"/>
       <c r="F186" s="26"/>
@@ -6087,9 +6105,9 @@
       <c r="L186" s="48"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A187" s="5"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="5"/>
+      <c r="A187" s="26"/>
+      <c r="B187" s="26"/>
+      <c r="C187" s="26"/>
       <c r="D187" s="26"/>
       <c r="E187" s="5"/>
       <c r="F187" s="26"/>
@@ -6101,9 +6119,9 @@
       <c r="L187" s="48"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
+      <c r="A188" s="26"/>
+      <c r="B188" s="26"/>
+      <c r="C188" s="26"/>
       <c r="D188" s="26"/>
       <c r="E188" s="5"/>
       <c r="F188" s="26"/>
@@ -6115,9 +6133,9 @@
       <c r="L188" s="48"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A189" s="5"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
+      <c r="A189" s="26"/>
+      <c r="B189" s="26"/>
+      <c r="C189" s="26"/>
       <c r="D189" s="26"/>
       <c r="E189" s="5"/>
       <c r="F189" s="26"/>
@@ -6129,9 +6147,9 @@
       <c r="L189" s="48"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="5"/>
+      <c r="A190" s="26"/>
+      <c r="B190" s="26"/>
+      <c r="C190" s="26"/>
       <c r="D190" s="26"/>
       <c r="E190" s="5"/>
       <c r="F190" s="26"/>
@@ -6143,9 +6161,9 @@
       <c r="L190" s="48"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A191" s="5"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
+      <c r="A191" s="26"/>
+      <c r="B191" s="26"/>
+      <c r="C191" s="26"/>
       <c r="D191" s="26"/>
       <c r="E191" s="5"/>
       <c r="F191" s="26"/>
@@ -6157,9 +6175,9 @@
       <c r="L191" s="48"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A192" s="5"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
+      <c r="A192" s="26"/>
+      <c r="B192" s="26"/>
+      <c r="C192" s="26"/>
       <c r="D192" s="26"/>
       <c r="E192" s="5"/>
       <c r="F192" s="26"/>
@@ -6171,9 +6189,9 @@
       <c r="L192" s="48"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A193" s="5"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
+      <c r="A193" s="26"/>
+      <c r="B193" s="26"/>
+      <c r="C193" s="26"/>
       <c r="D193" s="26"/>
       <c r="E193" s="5"/>
       <c r="F193" s="26"/>
@@ -6185,9 +6203,9 @@
       <c r="L193" s="48"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A194" s="5"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="5"/>
+      <c r="A194" s="26"/>
+      <c r="B194" s="26"/>
+      <c r="C194" s="26"/>
       <c r="D194" s="26"/>
       <c r="E194" s="5"/>
       <c r="F194" s="26"/>
@@ -6199,9 +6217,9 @@
       <c r="L194" s="48"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A195" s="5"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
+      <c r="A195" s="26"/>
+      <c r="B195" s="26"/>
+      <c r="C195" s="26"/>
       <c r="D195" s="26"/>
       <c r="E195" s="5"/>
       <c r="F195" s="26"/>
@@ -6213,9 +6231,9 @@
       <c r="L195" s="48"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="5"/>
+      <c r="A196" s="26"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="26"/>
       <c r="D196" s="26"/>
       <c r="E196" s="5"/>
       <c r="F196" s="26"/>
@@ -6227,9 +6245,9 @@
       <c r="L196" s="48"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A197" s="5"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
+      <c r="A197" s="26"/>
+      <c r="B197" s="26"/>
+      <c r="C197" s="26"/>
       <c r="D197" s="26"/>
       <c r="E197" s="5"/>
       <c r="F197" s="26"/>
@@ -6241,9 +6259,9 @@
       <c r="L197" s="48"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A198" s="5"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="5"/>
+      <c r="A198" s="26"/>
+      <c r="B198" s="26"/>
+      <c r="C198" s="26"/>
       <c r="D198" s="26"/>
       <c r="E198" s="5"/>
       <c r="F198" s="26"/>
@@ -6255,9 +6273,9 @@
       <c r="L198" s="48"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A199" s="5"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
+      <c r="A199" s="26"/>
+      <c r="B199" s="26"/>
+      <c r="C199" s="26"/>
       <c r="D199" s="26"/>
       <c r="E199" s="5"/>
       <c r="F199" s="26"/>
@@ -6269,9 +6287,9 @@
       <c r="L199" s="48"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
+      <c r="A200" s="26"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
       <c r="D200" s="26"/>
       <c r="E200" s="5"/>
       <c r="F200" s="26"/>
@@ -6283,9 +6301,9 @@
       <c r="L200" s="48"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A201" s="5"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
+      <c r="A201" s="26"/>
+      <c r="B201" s="26"/>
+      <c r="C201" s="26"/>
       <c r="D201" s="26"/>
       <c r="E201" s="5"/>
       <c r="F201" s="26"/>
@@ -6297,9 +6315,9 @@
       <c r="L201" s="48"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A202" s="5"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="5"/>
+      <c r="A202" s="26"/>
+      <c r="B202" s="26"/>
+      <c r="C202" s="26"/>
       <c r="D202" s="26"/>
       <c r="E202" s="5"/>
       <c r="F202" s="26"/>
@@ -6311,9 +6329,9 @@
       <c r="L202" s="48"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A203" s="5"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
+      <c r="A203" s="26"/>
+      <c r="B203" s="26"/>
+      <c r="C203" s="26"/>
       <c r="D203" s="26"/>
       <c r="E203" s="5"/>
       <c r="F203" s="26"/>
@@ -6325,9 +6343,9 @@
       <c r="L203" s="48"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A204" s="5"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="5"/>
+      <c r="A204" s="26"/>
+      <c r="B204" s="26"/>
+      <c r="C204" s="26"/>
       <c r="D204" s="26"/>
       <c r="E204" s="5"/>
       <c r="F204" s="26"/>
@@ -6339,9 +6357,9 @@
       <c r="L204" s="48"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A205" s="5"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
+      <c r="A205" s="26"/>
+      <c r="B205" s="26"/>
+      <c r="C205" s="26"/>
       <c r="D205" s="26"/>
       <c r="E205" s="5"/>
       <c r="F205" s="26"/>
@@ -6353,9 +6371,9 @@
       <c r="L205" s="48"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A206" s="5"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="5"/>
+      <c r="A206" s="26"/>
+      <c r="B206" s="26"/>
+      <c r="C206" s="26"/>
       <c r="D206" s="26"/>
       <c r="E206" s="5"/>
       <c r="F206" s="26"/>
@@ -6367,9 +6385,9 @@
       <c r="L206" s="48"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A207" s="5"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="5"/>
+      <c r="A207" s="26"/>
+      <c r="B207" s="26"/>
+      <c r="C207" s="26"/>
       <c r="D207" s="26"/>
       <c r="E207" s="5"/>
       <c r="F207" s="26"/>
@@ -6381,9 +6399,9 @@
       <c r="L207" s="48"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A208" s="5"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
+      <c r="A208" s="26"/>
+      <c r="B208" s="26"/>
+      <c r="C208" s="26"/>
       <c r="D208" s="26"/>
       <c r="E208" s="5"/>
       <c r="F208" s="26"/>
@@ -6395,9 +6413,9 @@
       <c r="L208" s="48"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A209" s="5"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="5"/>
+      <c r="A209" s="26"/>
+      <c r="B209" s="26"/>
+      <c r="C209" s="26"/>
       <c r="D209" s="26"/>
       <c r="E209" s="5"/>
       <c r="F209" s="26"/>
@@ -6409,9 +6427,9 @@
       <c r="L209" s="48"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A210" s="5"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="5"/>
+      <c r="A210" s="26"/>
+      <c r="B210" s="26"/>
+      <c r="C210" s="26"/>
       <c r="D210" s="26"/>
       <c r="E210" s="5"/>
       <c r="F210" s="26"/>
@@ -6423,9 +6441,9 @@
       <c r="L210" s="48"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A211" s="5"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
+      <c r="A211" s="26"/>
+      <c r="B211" s="26"/>
+      <c r="C211" s="26"/>
       <c r="D211" s="26"/>
       <c r="E211" s="5"/>
       <c r="F211" s="26"/>
@@ -6437,9 +6455,9 @@
       <c r="L211" s="48"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A212" s="5"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
+      <c r="A212" s="26"/>
+      <c r="B212" s="26"/>
+      <c r="C212" s="26"/>
       <c r="D212" s="26"/>
       <c r="E212" s="5"/>
       <c r="F212" s="26"/>
@@ -6451,9 +6469,9 @@
       <c r="L212" s="48"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A213" s="5"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
+      <c r="A213" s="26"/>
+      <c r="B213" s="26"/>
+      <c r="C213" s="26"/>
       <c r="D213" s="26"/>
       <c r="E213" s="5"/>
       <c r="F213" s="26"/>
@@ -6465,9 +6483,9 @@
       <c r="L213" s="48"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A214" s="5"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
+      <c r="A214" s="26"/>
+      <c r="B214" s="26"/>
+      <c r="C214" s="26"/>
       <c r="D214" s="26"/>
       <c r="E214" s="5"/>
       <c r="F214" s="26"/>
@@ -6479,9 +6497,9 @@
       <c r="L214" s="48"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A215" s="5"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="5"/>
+      <c r="A215" s="26"/>
+      <c r="B215" s="26"/>
+      <c r="C215" s="26"/>
       <c r="D215" s="26"/>
       <c r="E215" s="5"/>
       <c r="F215" s="26"/>
@@ -6493,9 +6511,9 @@
       <c r="L215" s="48"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A216" s="5"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
+      <c r="A216" s="26"/>
+      <c r="B216" s="26"/>
+      <c r="C216" s="26"/>
       <c r="D216" s="26"/>
       <c r="E216" s="5"/>
       <c r="F216" s="26"/>
@@ -6507,9 +6525,9 @@
       <c r="L216" s="48"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A217" s="5"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="5"/>
+      <c r="A217" s="26"/>
+      <c r="B217" s="26"/>
+      <c r="C217" s="26"/>
       <c r="D217" s="26"/>
       <c r="E217" s="5"/>
       <c r="F217" s="26"/>
@@ -6521,9 +6539,9 @@
       <c r="L217" s="48"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A218" s="5"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
+      <c r="A218" s="26"/>
+      <c r="B218" s="26"/>
+      <c r="C218" s="26"/>
       <c r="D218" s="26"/>
       <c r="E218" s="5"/>
       <c r="F218" s="26"/>
@@ -6535,9 +6553,9 @@
       <c r="L218" s="48"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A219" s="5"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
+      <c r="A219" s="26"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
       <c r="D219" s="26"/>
       <c r="E219" s="5"/>
       <c r="F219" s="26"/>
@@ -6549,9 +6567,9 @@
       <c r="L219" s="48"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A220" s="5"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
+      <c r="A220" s="26"/>
+      <c r="B220" s="26"/>
+      <c r="C220" s="26"/>
       <c r="D220" s="26"/>
       <c r="E220" s="5"/>
       <c r="F220" s="26"/>
@@ -6563,9 +6581,9 @@
       <c r="L220" s="48"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A221" s="5"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
+      <c r="A221" s="26"/>
+      <c r="B221" s="26"/>
+      <c r="C221" s="26"/>
       <c r="D221" s="26"/>
       <c r="E221" s="5"/>
       <c r="F221" s="26"/>
@@ -6577,9 +6595,9 @@
       <c r="L221" s="48"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A222" s="5"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
+      <c r="A222" s="26"/>
+      <c r="B222" s="26"/>
+      <c r="C222" s="26"/>
       <c r="D222" s="26"/>
       <c r="E222" s="5"/>
       <c r="F222" s="26"/>
@@ -6591,9 +6609,9 @@
       <c r="L222" s="48"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A223" s="5"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
+      <c r="A223" s="26"/>
+      <c r="B223" s="26"/>
+      <c r="C223" s="26"/>
       <c r="D223" s="26"/>
       <c r="E223" s="5"/>
       <c r="F223" s="26"/>
@@ -6605,9 +6623,9 @@
       <c r="L223" s="48"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A224" s="5"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
+      <c r="A224" s="26"/>
+      <c r="B224" s="26"/>
+      <c r="C224" s="26"/>
       <c r="D224" s="26"/>
       <c r="E224" s="5"/>
       <c r="F224" s="26"/>
@@ -6619,9 +6637,9 @@
       <c r="L224" s="48"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A225" s="5"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="5"/>
+      <c r="A225" s="26"/>
+      <c r="B225" s="26"/>
+      <c r="C225" s="26"/>
       <c r="D225" s="26"/>
       <c r="E225" s="5"/>
       <c r="F225" s="26"/>
@@ -6633,9 +6651,9 @@
       <c r="L225" s="48"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
+      <c r="A226" s="26"/>
+      <c r="B226" s="26"/>
+      <c r="C226" s="26"/>
       <c r="D226" s="26"/>
       <c r="E226" s="5"/>
       <c r="F226" s="26"/>
@@ -6647,9 +6665,9 @@
       <c r="L226" s="48"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="5"/>
+      <c r="A227" s="26"/>
+      <c r="B227" s="26"/>
+      <c r="C227" s="26"/>
       <c r="D227" s="26"/>
       <c r="E227" s="5"/>
       <c r="F227" s="26"/>
@@ -6661,9 +6679,9 @@
       <c r="L227" s="48"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A228" s="5"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
+      <c r="A228" s="26"/>
+      <c r="B228" s="26"/>
+      <c r="C228" s="26"/>
       <c r="D228" s="26"/>
       <c r="E228" s="5"/>
       <c r="F228" s="26"/>
@@ -6675,9 +6693,9 @@
       <c r="L228" s="48"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A229" s="5"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
+      <c r="A229" s="26"/>
+      <c r="B229" s="26"/>
+      <c r="C229" s="26"/>
       <c r="D229" s="26"/>
       <c r="E229" s="5"/>
       <c r="F229" s="26"/>
@@ -6689,9 +6707,9 @@
       <c r="L229" s="48"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A230" s="5"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
+      <c r="A230" s="26"/>
+      <c r="B230" s="26"/>
+      <c r="C230" s="26"/>
       <c r="D230" s="26"/>
       <c r="E230" s="5"/>
       <c r="F230" s="26"/>
@@ -6703,9 +6721,9 @@
       <c r="L230" s="48"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A231" s="5"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="5"/>
+      <c r="A231" s="26"/>
+      <c r="B231" s="26"/>
+      <c r="C231" s="26"/>
       <c r="D231" s="26"/>
       <c r="E231" s="5"/>
       <c r="F231" s="26"/>
@@ -6717,9 +6735,9 @@
       <c r="L231" s="48"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A232" s="5"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
+      <c r="A232" s="26"/>
+      <c r="B232" s="26"/>
+      <c r="C232" s="26"/>
       <c r="D232" s="26"/>
       <c r="E232" s="5"/>
       <c r="F232" s="26"/>
@@ -6731,9 +6749,9 @@
       <c r="L232" s="48"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A233" s="5"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
+      <c r="A233" s="26"/>
+      <c r="B233" s="26"/>
+      <c r="C233" s="26"/>
       <c r="D233" s="26"/>
       <c r="E233" s="5"/>
       <c r="F233" s="26"/>
@@ -6745,9 +6763,9 @@
       <c r="L233" s="48"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A234" s="5"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5"/>
+      <c r="A234" s="26"/>
+      <c r="B234" s="26"/>
+      <c r="C234" s="26"/>
       <c r="D234" s="26"/>
       <c r="E234" s="5"/>
       <c r="F234" s="26"/>
@@ -6759,9 +6777,9 @@
       <c r="L234" s="48"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A235" s="5"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="5"/>
+      <c r="A235" s="26"/>
+      <c r="B235" s="26"/>
+      <c r="C235" s="26"/>
       <c r="D235" s="26"/>
       <c r="E235" s="5"/>
       <c r="F235" s="26"/>
@@ -6773,9 +6791,9 @@
       <c r="L235" s="48"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A236" s="5"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
+      <c r="A236" s="26"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
       <c r="D236" s="26"/>
       <c r="E236" s="5"/>
       <c r="F236" s="26"/>
@@ -6787,9 +6805,9 @@
       <c r="L236" s="48"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A237" s="5"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
+      <c r="A237" s="26"/>
+      <c r="B237" s="26"/>
+      <c r="C237" s="26"/>
       <c r="D237" s="26"/>
       <c r="E237" s="5"/>
       <c r="F237" s="26"/>
@@ -6801,9 +6819,9 @@
       <c r="L237" s="48"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A238" s="5"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
+      <c r="A238" s="26"/>
+      <c r="B238" s="26"/>
+      <c r="C238" s="26"/>
       <c r="D238" s="26"/>
       <c r="E238" s="5"/>
       <c r="F238" s="26"/>
@@ -6815,9 +6833,9 @@
       <c r="L238" s="48"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A239" s="5"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5"/>
+      <c r="A239" s="26"/>
+      <c r="B239" s="26"/>
+      <c r="C239" s="26"/>
       <c r="D239" s="26"/>
       <c r="E239" s="5"/>
       <c r="F239" s="26"/>
@@ -6829,9 +6847,9 @@
       <c r="L239" s="48"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A240" s="5"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
+      <c r="A240" s="26"/>
+      <c r="B240" s="26"/>
+      <c r="C240" s="26"/>
       <c r="D240" s="26"/>
       <c r="E240" s="5"/>
       <c r="F240" s="26"/>
@@ -6843,9 +6861,9 @@
       <c r="L240" s="48"/>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A241" s="5"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="5"/>
+      <c r="A241" s="26"/>
+      <c r="B241" s="26"/>
+      <c r="C241" s="26"/>
       <c r="D241" s="26"/>
       <c r="E241" s="5"/>
       <c r="F241" s="26"/>
@@ -6857,9 +6875,9 @@
       <c r="L241" s="48"/>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A242" s="5"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="5"/>
+      <c r="A242" s="26"/>
+      <c r="B242" s="26"/>
+      <c r="C242" s="26"/>
       <c r="D242" s="26"/>
       <c r="E242" s="5"/>
       <c r="F242" s="26"/>
@@ -6871,9 +6889,9 @@
       <c r="L242" s="48"/>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A243" s="5"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="5"/>
+      <c r="A243" s="26"/>
+      <c r="B243" s="26"/>
+      <c r="C243" s="26"/>
       <c r="D243" s="26"/>
       <c r="E243" s="5"/>
       <c r="F243" s="26"/>
@@ -6885,9 +6903,9 @@
       <c r="L243" s="48"/>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A244" s="5"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5"/>
+      <c r="A244" s="26"/>
+      <c r="B244" s="26"/>
+      <c r="C244" s="26"/>
       <c r="D244" s="26"/>
       <c r="E244" s="5"/>
       <c r="F244" s="26"/>
@@ -6899,9 +6917,9 @@
       <c r="L244" s="48"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A245" s="5"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="5"/>
+      <c r="A245" s="26"/>
+      <c r="B245" s="26"/>
+      <c r="C245" s="26"/>
       <c r="D245" s="26"/>
       <c r="E245" s="5"/>
       <c r="F245" s="26"/>
@@ -6913,9 +6931,9 @@
       <c r="L245" s="48"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A246" s="5"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
+      <c r="A246" s="26"/>
+      <c r="B246" s="26"/>
+      <c r="C246" s="26"/>
       <c r="D246" s="26"/>
       <c r="E246" s="5"/>
       <c r="F246" s="26"/>
@@ -6927,9 +6945,9 @@
       <c r="L246" s="48"/>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A247" s="5"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="5"/>
+      <c r="A247" s="26"/>
+      <c r="B247" s="26"/>
+      <c r="C247" s="26"/>
       <c r="D247" s="26"/>
       <c r="E247" s="5"/>
       <c r="F247" s="26"/>
@@ -6941,9 +6959,9 @@
       <c r="L247" s="48"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A248" s="5"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="5"/>
+      <c r="A248" s="26"/>
+      <c r="B248" s="26"/>
+      <c r="C248" s="26"/>
       <c r="D248" s="26"/>
       <c r="E248" s="5"/>
       <c r="F248" s="26"/>
@@ -6955,9 +6973,9 @@
       <c r="L248" s="48"/>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A249" s="5"/>
-      <c r="B249" s="5"/>
-      <c r="C249" s="5"/>
+      <c r="A249" s="26"/>
+      <c r="B249" s="26"/>
+      <c r="C249" s="26"/>
       <c r="D249" s="26"/>
       <c r="E249" s="5"/>
       <c r="F249" s="26"/>
@@ -6969,9 +6987,9 @@
       <c r="L249" s="48"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A250" s="5"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5"/>
+      <c r="A250" s="26"/>
+      <c r="B250" s="26"/>
+      <c r="C250" s="26"/>
       <c r="D250" s="26"/>
       <c r="E250" s="5"/>
       <c r="F250" s="26"/>
@@ -6983,9 +7001,9 @@
       <c r="L250" s="48"/>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A251" s="5"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="5"/>
+      <c r="A251" s="26"/>
+      <c r="B251" s="26"/>
+      <c r="C251" s="26"/>
       <c r="D251" s="26"/>
       <c r="E251" s="5"/>
       <c r="F251" s="26"/>
@@ -6997,9 +7015,9 @@
       <c r="L251" s="48"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A252" s="5"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
+      <c r="A252" s="26"/>
+      <c r="B252" s="26"/>
+      <c r="C252" s="26"/>
       <c r="D252" s="26"/>
       <c r="E252" s="5"/>
       <c r="F252" s="26"/>
@@ -7011,9 +7029,9 @@
       <c r="L252" s="48"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A253" s="5"/>
-      <c r="B253" s="5"/>
-      <c r="C253" s="5"/>
+      <c r="A253" s="26"/>
+      <c r="B253" s="26"/>
+      <c r="C253" s="26"/>
       <c r="D253" s="26"/>
       <c r="E253" s="5"/>
       <c r="F253" s="26"/>
@@ -7025,9 +7043,9 @@
       <c r="L253" s="48"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A254" s="5"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
+      <c r="A254" s="26"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
       <c r="D254" s="26"/>
       <c r="E254" s="5"/>
       <c r="F254" s="26"/>
@@ -7039,9 +7057,9 @@
       <c r="L254" s="48"/>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A255" s="5"/>
-      <c r="B255" s="5"/>
-      <c r="C255" s="5"/>
+      <c r="A255" s="26"/>
+      <c r="B255" s="26"/>
+      <c r="C255" s="26"/>
       <c r="D255" s="26"/>
       <c r="E255" s="5"/>
       <c r="F255" s="26"/>
@@ -7053,9 +7071,9 @@
       <c r="L255" s="48"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A256" s="5"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="5"/>
+      <c r="A256" s="26"/>
+      <c r="B256" s="26"/>
+      <c r="C256" s="26"/>
       <c r="D256" s="26"/>
       <c r="E256" s="5"/>
       <c r="F256" s="26"/>
@@ -7067,9 +7085,9 @@
       <c r="L256" s="48"/>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A257" s="5"/>
-      <c r="B257" s="5"/>
-      <c r="C257" s="5"/>
+      <c r="A257" s="26"/>
+      <c r="B257" s="26"/>
+      <c r="C257" s="26"/>
       <c r="D257" s="26"/>
       <c r="E257" s="5"/>
       <c r="F257" s="26"/>
@@ -7081,9 +7099,9 @@
       <c r="L257" s="48"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A258" s="5"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="5"/>
+      <c r="A258" s="26"/>
+      <c r="B258" s="26"/>
+      <c r="C258" s="26"/>
       <c r="D258" s="26"/>
       <c r="E258" s="5"/>
       <c r="F258" s="26"/>
@@ -7095,9 +7113,9 @@
       <c r="L258" s="48"/>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A259" s="5"/>
-      <c r="B259" s="5"/>
-      <c r="C259" s="5"/>
+      <c r="A259" s="26"/>
+      <c r="B259" s="26"/>
+      <c r="C259" s="26"/>
       <c r="D259" s="26"/>
       <c r="E259" s="5"/>
       <c r="F259" s="26"/>
@@ -7109,9 +7127,9 @@
       <c r="L259" s="48"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A260" s="5"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="5"/>
+      <c r="A260" s="26"/>
+      <c r="B260" s="26"/>
+      <c r="C260" s="26"/>
       <c r="D260" s="26"/>
       <c r="E260" s="5"/>
       <c r="F260" s="26"/>
@@ -7123,9 +7141,9 @@
       <c r="L260" s="48"/>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A261" s="5"/>
-      <c r="B261" s="5"/>
-      <c r="C261" s="5"/>
+      <c r="A261" s="26"/>
+      <c r="B261" s="26"/>
+      <c r="C261" s="26"/>
       <c r="D261" s="26"/>
       <c r="E261" s="5"/>
       <c r="F261" s="26"/>
@@ -7137,9 +7155,9 @@
       <c r="L261" s="48"/>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A262" s="5"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
+      <c r="A262" s="26"/>
+      <c r="B262" s="26"/>
+      <c r="C262" s="26"/>
       <c r="D262" s="26"/>
       <c r="E262" s="5"/>
       <c r="F262" s="26"/>
@@ -7151,9 +7169,9 @@
       <c r="L262" s="48"/>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A263" s="5"/>
-      <c r="B263" s="5"/>
-      <c r="C263" s="5"/>
+      <c r="A263" s="26"/>
+      <c r="B263" s="26"/>
+      <c r="C263" s="26"/>
       <c r="D263" s="26"/>
       <c r="E263" s="5"/>
       <c r="F263" s="26"/>
@@ -7165,9 +7183,9 @@
       <c r="L263" s="48"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A264" s="5"/>
-      <c r="B264" s="5"/>
-      <c r="C264" s="5"/>
+      <c r="A264" s="26"/>
+      <c r="B264" s="26"/>
+      <c r="C264" s="26"/>
       <c r="D264" s="26"/>
       <c r="E264" s="5"/>
       <c r="F264" s="26"/>
@@ -7179,9 +7197,9 @@
       <c r="L264" s="48"/>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A265" s="5"/>
-      <c r="B265" s="5"/>
-      <c r="C265" s="5"/>
+      <c r="A265" s="26"/>
+      <c r="B265" s="26"/>
+      <c r="C265" s="26"/>
       <c r="D265" s="26"/>
       <c r="E265" s="5"/>
       <c r="F265" s="26"/>
@@ -7193,9 +7211,9 @@
       <c r="L265" s="48"/>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A266" s="5"/>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5"/>
+      <c r="A266" s="26"/>
+      <c r="B266" s="26"/>
+      <c r="C266" s="26"/>
       <c r="D266" s="26"/>
       <c r="E266" s="5"/>
       <c r="F266" s="26"/>
@@ -7207,9 +7225,9 @@
       <c r="L266" s="48"/>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A267" s="5"/>
-      <c r="B267" s="5"/>
-      <c r="C267" s="5"/>
+      <c r="A267" s="26"/>
+      <c r="B267" s="26"/>
+      <c r="C267" s="26"/>
       <c r="D267" s="26"/>
       <c r="E267" s="5"/>
       <c r="F267" s="26"/>
@@ -7221,9 +7239,9 @@
       <c r="L267" s="48"/>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A268" s="5"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5"/>
+      <c r="A268" s="26"/>
+      <c r="B268" s="26"/>
+      <c r="C268" s="26"/>
       <c r="D268" s="26"/>
       <c r="E268" s="5"/>
       <c r="F268" s="26"/>
@@ -7235,9 +7253,9 @@
       <c r="L268" s="48"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A269" s="5"/>
-      <c r="B269" s="5"/>
-      <c r="C269" s="5"/>
+      <c r="A269" s="26"/>
+      <c r="B269" s="26"/>
+      <c r="C269" s="26"/>
       <c r="D269" s="26"/>
       <c r="E269" s="5"/>
       <c r="F269" s="26"/>
@@ -7249,9 +7267,9 @@
       <c r="L269" s="48"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A270" s="5"/>
-      <c r="B270" s="5"/>
-      <c r="C270" s="5"/>
+      <c r="A270" s="26"/>
+      <c r="B270" s="26"/>
+      <c r="C270" s="26"/>
       <c r="D270" s="26"/>
       <c r="E270" s="5"/>
       <c r="F270" s="26"/>
@@ -7263,9 +7281,9 @@
       <c r="L270" s="48"/>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A271" s="5"/>
-      <c r="B271" s="5"/>
-      <c r="C271" s="5"/>
+      <c r="A271" s="26"/>
+      <c r="B271" s="26"/>
+      <c r="C271" s="26"/>
       <c r="D271" s="26"/>
       <c r="E271" s="5"/>
       <c r="F271" s="26"/>
@@ -7277,9 +7295,9 @@
       <c r="L271" s="48"/>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A272" s="5"/>
-      <c r="B272" s="5"/>
-      <c r="C272" s="5"/>
+      <c r="A272" s="26"/>
+      <c r="B272" s="26"/>
+      <c r="C272" s="26"/>
       <c r="D272" s="26"/>
       <c r="E272" s="5"/>
       <c r="F272" s="26"/>
@@ -7291,9 +7309,9 @@
       <c r="L272" s="48"/>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A273" s="5"/>
-      <c r="B273" s="5"/>
-      <c r="C273" s="5"/>
+      <c r="A273" s="26"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
       <c r="D273" s="26"/>
       <c r="E273" s="5"/>
       <c r="F273" s="26"/>
@@ -7305,9 +7323,9 @@
       <c r="L273" s="48"/>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A274" s="5"/>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5"/>
+      <c r="A274" s="26"/>
+      <c r="B274" s="26"/>
+      <c r="C274" s="26"/>
       <c r="D274" s="26"/>
       <c r="E274" s="5"/>
       <c r="F274" s="26"/>
@@ -7319,9 +7337,9 @@
       <c r="L274" s="48"/>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A275" s="5"/>
-      <c r="B275" s="5"/>
-      <c r="C275" s="5"/>
+      <c r="A275" s="26"/>
+      <c r="B275" s="26"/>
+      <c r="C275" s="26"/>
       <c r="D275" s="26"/>
       <c r="E275" s="5"/>
       <c r="F275" s="26"/>
@@ -7333,9 +7351,9 @@
       <c r="L275" s="48"/>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A276" s="5"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="5"/>
+      <c r="A276" s="26"/>
+      <c r="B276" s="26"/>
+      <c r="C276" s="26"/>
       <c r="D276" s="26"/>
       <c r="E276" s="5"/>
       <c r="F276" s="26"/>
@@ -7347,9 +7365,9 @@
       <c r="L276" s="48"/>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A277" s="5"/>
-      <c r="B277" s="5"/>
-      <c r="C277" s="5"/>
+      <c r="A277" s="26"/>
+      <c r="B277" s="26"/>
+      <c r="C277" s="26"/>
       <c r="D277" s="26"/>
       <c r="E277" s="5"/>
       <c r="F277" s="26"/>
@@ -7361,9 +7379,9 @@
       <c r="L277" s="48"/>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A278" s="5"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="5"/>
+      <c r="A278" s="26"/>
+      <c r="B278" s="26"/>
+      <c r="C278" s="26"/>
       <c r="D278" s="26"/>
       <c r="E278" s="5"/>
       <c r="F278" s="26"/>
@@ -7375,9 +7393,9 @@
       <c r="L278" s="48"/>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A279" s="5"/>
-      <c r="B279" s="5"/>
-      <c r="C279" s="5"/>
+      <c r="A279" s="26"/>
+      <c r="B279" s="26"/>
+      <c r="C279" s="26"/>
       <c r="D279" s="26"/>
       <c r="E279" s="5"/>
       <c r="F279" s="26"/>
@@ -7389,9 +7407,9 @@
       <c r="L279" s="48"/>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A280" s="5"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="5"/>
+      <c r="A280" s="26"/>
+      <c r="B280" s="26"/>
+      <c r="C280" s="26"/>
       <c r="D280" s="26"/>
       <c r="E280" s="5"/>
       <c r="F280" s="26"/>
@@ -7403,9 +7421,9 @@
       <c r="L280" s="48"/>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A281" s="5"/>
-      <c r="B281" s="5"/>
-      <c r="C281" s="5"/>
+      <c r="A281" s="26"/>
+      <c r="B281" s="26"/>
+      <c r="C281" s="26"/>
       <c r="D281" s="26"/>
       <c r="E281" s="5"/>
       <c r="F281" s="26"/>
@@ -7417,9 +7435,9 @@
       <c r="L281" s="48"/>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A282" s="5"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="5"/>
+      <c r="A282" s="26"/>
+      <c r="B282" s="26"/>
+      <c r="C282" s="26"/>
       <c r="D282" s="26"/>
       <c r="E282" s="5"/>
       <c r="F282" s="26"/>
@@ -7431,9 +7449,9 @@
       <c r="L282" s="48"/>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A283" s="5"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="5"/>
+      <c r="A283" s="26"/>
+      <c r="B283" s="26"/>
+      <c r="C283" s="26"/>
       <c r="D283" s="26"/>
       <c r="E283" s="5"/>
       <c r="F283" s="26"/>
@@ -7445,9 +7463,9 @@
       <c r="L283" s="48"/>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A284" s="5"/>
-      <c r="B284" s="5"/>
-      <c r="C284" s="5"/>
+      <c r="A284" s="26"/>
+      <c r="B284" s="26"/>
+      <c r="C284" s="26"/>
       <c r="D284" s="26"/>
       <c r="E284" s="5"/>
       <c r="F284" s="26"/>
@@ -7459,9 +7477,9 @@
       <c r="L284" s="48"/>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A285" s="5"/>
-      <c r="B285" s="5"/>
-      <c r="C285" s="5"/>
+      <c r="A285" s="26"/>
+      <c r="B285" s="26"/>
+      <c r="C285" s="26"/>
       <c r="D285" s="26"/>
       <c r="E285" s="5"/>
       <c r="F285" s="26"/>
@@ -7473,9 +7491,9 @@
       <c r="L285" s="48"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A286" s="5"/>
-      <c r="B286" s="5"/>
-      <c r="C286" s="5"/>
+      <c r="A286" s="26"/>
+      <c r="B286" s="26"/>
+      <c r="C286" s="26"/>
       <c r="D286" s="26"/>
       <c r="E286" s="5"/>
       <c r="F286" s="26"/>
@@ -7487,9 +7505,9 @@
       <c r="L286" s="48"/>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A287" s="5"/>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
+      <c r="A287" s="26"/>
+      <c r="B287" s="26"/>
+      <c r="C287" s="26"/>
       <c r="D287" s="26"/>
       <c r="E287" s="5"/>
       <c r="F287" s="26"/>
@@ -7501,9 +7519,9 @@
       <c r="L287" s="48"/>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A288" s="5"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="5"/>
+      <c r="A288" s="26"/>
+      <c r="B288" s="26"/>
+      <c r="C288" s="26"/>
       <c r="D288" s="26"/>
       <c r="E288" s="5"/>
       <c r="F288" s="26"/>
@@ -7515,9 +7533,9 @@
       <c r="L288" s="48"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A289" s="5"/>
-      <c r="B289" s="5"/>
-      <c r="C289" s="5"/>
+      <c r="A289" s="26"/>
+      <c r="B289" s="26"/>
+      <c r="C289" s="26"/>
       <c r="D289" s="26"/>
       <c r="E289" s="5"/>
       <c r="F289" s="26"/>
@@ -7529,9 +7547,9 @@
       <c r="L289" s="48"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A290" s="5"/>
-      <c r="B290" s="5"/>
-      <c r="C290" s="5"/>
+      <c r="A290" s="26"/>
+      <c r="B290" s="26"/>
+      <c r="C290" s="26"/>
       <c r="D290" s="26"/>
       <c r="E290" s="5"/>
       <c r="F290" s="26"/>
@@ -7543,9 +7561,9 @@
       <c r="L290" s="48"/>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A291" s="5"/>
-      <c r="B291" s="5"/>
-      <c r="C291" s="5"/>
+      <c r="A291" s="26"/>
+      <c r="B291" s="26"/>
+      <c r="C291" s="26"/>
       <c r="D291" s="26"/>
       <c r="E291" s="5"/>
       <c r="F291" s="26"/>
@@ -7557,9 +7575,9 @@
       <c r="L291" s="48"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A292" s="5"/>
-      <c r="B292" s="5"/>
-      <c r="C292" s="5"/>
+      <c r="A292" s="26"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
       <c r="D292" s="26"/>
       <c r="E292" s="5"/>
       <c r="F292" s="26"/>
@@ -7571,9 +7589,9 @@
       <c r="L292" s="48"/>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A293" s="5"/>
-      <c r="B293" s="5"/>
-      <c r="C293" s="5"/>
+      <c r="A293" s="26"/>
+      <c r="B293" s="26"/>
+      <c r="C293" s="26"/>
       <c r="D293" s="26"/>
       <c r="E293" s="5"/>
       <c r="F293" s="26"/>
@@ -7585,9 +7603,9 @@
       <c r="L293" s="48"/>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A294" s="5"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="5"/>
+      <c r="A294" s="26"/>
+      <c r="B294" s="26"/>
+      <c r="C294" s="26"/>
       <c r="D294" s="26"/>
       <c r="E294" s="5"/>
       <c r="F294" s="26"/>
@@ -7599,9 +7617,9 @@
       <c r="L294" s="48"/>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A295" s="5"/>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
+      <c r="A295" s="26"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="26"/>
       <c r="D295" s="26"/>
       <c r="E295" s="5"/>
       <c r="F295" s="26"/>
@@ -7613,9 +7631,9 @@
       <c r="L295" s="48"/>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A296" s="5"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="5"/>
+      <c r="A296" s="26"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="26"/>
       <c r="D296" s="26"/>
       <c r="E296" s="5"/>
       <c r="F296" s="26"/>
@@ -7627,9 +7645,9 @@
       <c r="L296" s="48"/>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A297" s="5"/>
-      <c r="B297" s="5"/>
-      <c r="C297" s="5"/>
+      <c r="A297" s="26"/>
+      <c r="B297" s="26"/>
+      <c r="C297" s="26"/>
       <c r="D297" s="26"/>
       <c r="E297" s="5"/>
       <c r="F297" s="26"/>
@@ -7641,9 +7659,9 @@
       <c r="L297" s="48"/>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A298" s="5"/>
-      <c r="B298" s="5"/>
-      <c r="C298" s="5"/>
+      <c r="A298" s="26"/>
+      <c r="B298" s="26"/>
+      <c r="C298" s="26"/>
       <c r="D298" s="26"/>
       <c r="E298" s="5"/>
       <c r="F298" s="26"/>
@@ -7655,9 +7673,9 @@
       <c r="L298" s="48"/>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A299" s="5"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="5"/>
+      <c r="A299" s="26"/>
+      <c r="B299" s="26"/>
+      <c r="C299" s="26"/>
       <c r="D299" s="26"/>
       <c r="E299" s="5"/>
       <c r="F299" s="26"/>
@@ -7669,9 +7687,9 @@
       <c r="L299" s="48"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A300" s="5"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="5"/>
+      <c r="A300" s="26"/>
+      <c r="B300" s="26"/>
+      <c r="C300" s="26"/>
       <c r="D300" s="26"/>
       <c r="E300" s="5"/>
       <c r="F300" s="26"/>
@@ -7683,9 +7701,9 @@
       <c r="L300" s="48"/>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A301" s="5"/>
-      <c r="B301" s="5"/>
-      <c r="C301" s="5"/>
+      <c r="A301" s="26"/>
+      <c r="B301" s="26"/>
+      <c r="C301" s="26"/>
       <c r="D301" s="26"/>
       <c r="E301" s="5"/>
       <c r="F301" s="26"/>
@@ -7697,9 +7715,9 @@
       <c r="L301" s="48"/>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A302" s="5"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="5"/>
+      <c r="A302" s="26"/>
+      <c r="B302" s="26"/>
+      <c r="C302" s="26"/>
       <c r="D302" s="26"/>
       <c r="E302" s="5"/>
       <c r="F302" s="26"/>
@@ -7711,9 +7729,9 @@
       <c r="L302" s="48"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A303" s="5"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="5"/>
+      <c r="A303" s="26"/>
+      <c r="B303" s="26"/>
+      <c r="C303" s="26"/>
       <c r="D303" s="26"/>
       <c r="E303" s="5"/>
       <c r="F303" s="26"/>
@@ -7725,9 +7743,9 @@
       <c r="L303" s="48"/>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A304" s="5"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="5"/>
+      <c r="A304" s="26"/>
+      <c r="B304" s="26"/>
+      <c r="C304" s="26"/>
       <c r="D304" s="26"/>
       <c r="E304" s="5"/>
       <c r="F304" s="26"/>
@@ -7739,9 +7757,9 @@
       <c r="L304" s="48"/>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A305" s="5"/>
-      <c r="B305" s="5"/>
-      <c r="C305" s="5"/>
+      <c r="A305" s="26"/>
+      <c r="B305" s="26"/>
+      <c r="C305" s="26"/>
       <c r="D305" s="26"/>
       <c r="E305" s="5"/>
       <c r="F305" s="26"/>
@@ -7753,9 +7771,9 @@
       <c r="L305" s="48"/>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A306" s="5"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="5"/>
+      <c r="A306" s="26"/>
+      <c r="B306" s="26"/>
+      <c r="C306" s="26"/>
       <c r="D306" s="26"/>
       <c r="E306" s="5"/>
       <c r="F306" s="26"/>
@@ -7767,9 +7785,9 @@
       <c r="L306" s="48"/>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A307" s="5"/>
-      <c r="B307" s="5"/>
-      <c r="C307" s="5"/>
+      <c r="A307" s="26"/>
+      <c r="B307" s="26"/>
+      <c r="C307" s="26"/>
       <c r="D307" s="26"/>
       <c r="E307" s="5"/>
       <c r="F307" s="26"/>
@@ -7781,9 +7799,9 @@
       <c r="L307" s="48"/>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A308" s="5"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="5"/>
+      <c r="A308" s="26"/>
+      <c r="B308" s="26"/>
+      <c r="C308" s="26"/>
       <c r="D308" s="26"/>
       <c r="E308" s="5"/>
       <c r="F308" s="26"/>
@@ -7795,9 +7813,9 @@
       <c r="L308" s="48"/>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A309" s="5"/>
-      <c r="B309" s="5"/>
-      <c r="C309" s="5"/>
+      <c r="A309" s="26"/>
+      <c r="B309" s="26"/>
+      <c r="C309" s="26"/>
       <c r="D309" s="26"/>
       <c r="E309" s="5"/>
       <c r="F309" s="26"/>
@@ -7809,9 +7827,9 @@
       <c r="L309" s="48"/>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A310" s="5"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="5"/>
+      <c r="A310" s="26"/>
+      <c r="B310" s="26"/>
+      <c r="C310" s="26"/>
       <c r="D310" s="26"/>
       <c r="E310" s="5"/>
       <c r="F310" s="26"/>
@@ -7823,9 +7841,9 @@
       <c r="L310" s="48"/>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A311" s="5"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
+      <c r="A311" s="26"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
       <c r="D311" s="26"/>
       <c r="E311" s="5"/>
       <c r="F311" s="26"/>
@@ -7837,9 +7855,9 @@
       <c r="L311" s="48"/>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A312" s="5"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="5"/>
+      <c r="A312" s="26"/>
+      <c r="B312" s="26"/>
+      <c r="C312" s="26"/>
       <c r="D312" s="26"/>
       <c r="E312" s="5"/>
       <c r="F312" s="26"/>
@@ -7851,9 +7869,9 @@
       <c r="L312" s="48"/>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A313" s="5"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="5"/>
+      <c r="A313" s="26"/>
+      <c r="B313" s="26"/>
+      <c r="C313" s="26"/>
       <c r="D313" s="26"/>
       <c r="E313" s="5"/>
       <c r="F313" s="26"/>
@@ -7865,9 +7883,9 @@
       <c r="L313" s="48"/>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A314" s="5"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="5"/>
+      <c r="A314" s="26"/>
+      <c r="B314" s="26"/>
+      <c r="C314" s="26"/>
       <c r="D314" s="26"/>
       <c r="E314" s="5"/>
       <c r="F314" s="26"/>
@@ -7879,9 +7897,9 @@
       <c r="L314" s="48"/>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A315" s="5"/>
-      <c r="B315" s="5"/>
-      <c r="C315" s="5"/>
+      <c r="A315" s="26"/>
+      <c r="B315" s="26"/>
+      <c r="C315" s="26"/>
       <c r="D315" s="26"/>
       <c r="E315" s="5"/>
       <c r="F315" s="26"/>
@@ -7893,9 +7911,9 @@
       <c r="L315" s="48"/>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A316" s="5"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="5"/>
+      <c r="A316" s="26"/>
+      <c r="B316" s="26"/>
+      <c r="C316" s="26"/>
       <c r="D316" s="26"/>
       <c r="E316" s="5"/>
       <c r="F316" s="26"/>
@@ -7907,9 +7925,9 @@
       <c r="L316" s="48"/>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A317" s="5"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="5"/>
+      <c r="A317" s="26"/>
+      <c r="B317" s="26"/>
+      <c r="C317" s="26"/>
       <c r="D317" s="26"/>
       <c r="E317" s="5"/>
       <c r="F317" s="26"/>
@@ -7921,9 +7939,9 @@
       <c r="L317" s="48"/>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A318" s="5"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="5"/>
+      <c r="A318" s="26"/>
+      <c r="B318" s="26"/>
+      <c r="C318" s="26"/>
       <c r="D318" s="26"/>
       <c r="E318" s="5"/>
       <c r="F318" s="26"/>
@@ -7935,9 +7953,9 @@
       <c r="L318" s="48"/>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A319" s="5"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
+      <c r="A319" s="26"/>
+      <c r="B319" s="26"/>
+      <c r="C319" s="26"/>
       <c r="D319" s="26"/>
       <c r="E319" s="5"/>
       <c r="F319" s="26"/>
@@ -7949,7 +7967,7 @@
       <c r="L319" s="48"/>
     </row>
     <row r="1048576" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1048576" s="5" t="s">
+      <c r="A1048576" s="26" t="s">
         <v>190</v>
       </c>
     </row>

--- a/spoilers/trades.xlsx
+++ b/spoilers/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A935C6AF-8619-4626-AA4C-7181CBBD84DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0296F742-0C33-46F1-A098-A3C0F3D704B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Trades" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Trades!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Trades!$A$1:$L$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="265">
   <si>
     <t>NBT Villager Trade Template</t>
   </si>
@@ -285,6 +285,555 @@
   </si>
   <si>
     <t>Lore book on CRAFTING POTIONS</t>
+  </si>
+  <si>
+    <t>Pepper</t>
+  </si>
+  <si>
+    <t>Shepherd</t>
+  </si>
+  <si>
+    <t>black_wool</t>
+  </si>
+  <si>
+    <t>black carpet</t>
+  </si>
+  <si>
+    <t>brown_wool</t>
+  </si>
+  <si>
+    <t>brown_carpet</t>
+  </si>
+  <si>
+    <t>Unlocks conversation about rune location</t>
+  </si>
+  <si>
+    <t>Winston A.</t>
+  </si>
+  <si>
+    <t>Winston T.</t>
+  </si>
+  <si>
+    <t>Winston L.</t>
+  </si>
+  <si>
+    <t>Winston W.</t>
+  </si>
+  <si>
+    <t>Armorer</t>
+  </si>
+  <si>
+    <t>Toolsmith</t>
+  </si>
+  <si>
+    <t>Leatherworker</t>
+  </si>
+  <si>
+    <t>Weaponsmith</t>
+  </si>
+  <si>
+    <t>emerald</t>
+  </si>
+  <si>
+    <t>leather_chestplate</t>
+  </si>
+  <si>
+    <t>iron_nugget</t>
+  </si>
+  <si>
+    <t>iron_leggings</t>
+  </si>
+  <si>
+    <t>wooden_sword</t>
+  </si>
+  <si>
+    <t>wooden_hoe</t>
+  </si>
+  <si>
+    <t>iron_axe</t>
+  </si>
+  <si>
+    <t>iron_block</t>
+  </si>
+  <si>
+    <t>iron_boots</t>
+  </si>
+  <si>
+    <t>iron_ingot</t>
+  </si>
+  <si>
+    <t>iron_pickaxe</t>
+  </si>
+  <si>
+    <t>iron_helmet</t>
+  </si>
+  <si>
+    <t>iron_chestplate</t>
+  </si>
+  <si>
+    <t>wooden_pickaxe</t>
+  </si>
+  <si>
+    <t>wooden_axe</t>
+  </si>
+  <si>
+    <t>iron_sword</t>
+  </si>
+  <si>
+    <t>wooden_shovel</t>
+  </si>
+  <si>
+    <t>leather_leggings</t>
+  </si>
+  <si>
+    <t>leather_helmet</t>
+  </si>
+  <si>
+    <t>leather_boots</t>
+  </si>
+  <si>
+    <t>Gating trade from L1 to L2</t>
+  </si>
+  <si>
+    <t>Gating trade from L2 to L3</t>
+  </si>
+  <si>
+    <t>oak_log</t>
+  </si>
+  <si>
+    <t>Allows trade-triggered conversation to occur</t>
+  </si>
+  <si>
+    <t>Gating trade</t>
+  </si>
+  <si>
+    <t>Allows trade-triggered conversation to occur. And is a gating trade from L1 to L2.</t>
+  </si>
+  <si>
+    <t>title: INTRO TO METALLURGY
+author: Winston A.
+[PAGE]
+Novice stone miners will find they cannot mine cobblestones efficiently and will mostly just mine gravel. 
+And like them, novice metallurgists will only make great hunks of iron or puny nuggets but not well-refined ingots.
+In fact, novices aren't fit to even HOLD fresh ingots!
+(Continued...)
+[PAGE]
+Only the great metallurgists living in the town of MINOC are ALLOWED to share our dearest guild secrets on these matters.
+In BRITAIN, we can trade a full iron block for a single iron ingot...but you'll get a nasty surprise...</t>
+  </si>
+  <si>
+    <t>Winston M.</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
+    <t>cobblestone</t>
+  </si>
+  <si>
+    <t>clay_ball</t>
+  </si>
+  <si>
+    <t>smooth_stone</t>
+  </si>
+  <si>
+    <t>furnace</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>copper_pickaxe</t>
+  </si>
+  <si>
+    <t>copper_ingot</t>
+  </si>
+  <si>
+    <t>gold_ingot</t>
+  </si>
+  <si>
+    <t>stone_shovel</t>
+  </si>
+  <si>
+    <t>title: INTRO TO COBBLE MINING
+author: Winston M.
+[PAGE]
+Novice stone miners will find they cannot mine cobblestones efficiently and will mostly just mine gravel. 
+EXPERT Masons in BRITAIN, fortunately, can teach the secrets of Mining COBBLESTONEvia better tools.</t>
+  </si>
+  <si>
+    <t>Receiving iron_pickaxe will grant the SKILL-related advancement of "Journeyman Miner"</t>
+  </si>
+  <si>
+    <t>Receiving diamond_pickaxe will grant the SKILL-related advancement of "Expert Miner"</t>
+  </si>
+  <si>
+    <t>Receiving netherite_pickaxe will grant the SKILL-related advancement of "Master Miner"</t>
+  </si>
+  <si>
+    <t>diamond_pickaxe</t>
+  </si>
+  <si>
+    <t>netherite_pickaxe</t>
+  </si>
+  <si>
+    <t>golden_pickaxe</t>
+  </si>
+  <si>
+    <t>Player has no crafting table so can't make a furnace</t>
+  </si>
+  <si>
+    <t>stone_pickaxe</t>
+  </si>
+  <si>
+    <t>Jhelom</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>trial_key</t>
+  </si>
+  <si>
+    <t>goat_horn</t>
+  </si>
+  <si>
+    <t>totem_of_undying</t>
+  </si>
+  <si>
+    <t>wither_skeleton_skull</t>
+  </si>
+  <si>
+    <t>netherite_leggings</t>
+  </si>
+  <si>
+    <t>ghast_tear</t>
+  </si>
+  <si>
+    <t>netherite_boots</t>
+  </si>
+  <si>
+    <t>Hero's Juicy Trades</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>netherite_axe</t>
+  </si>
+  <si>
+    <t>diamond_leggings</t>
+  </si>
+  <si>
+    <t>white_banner</t>
+  </si>
+  <si>
+    <t>Must be an Ominous Banner that a Raid Captain dropped.</t>
+  </si>
+  <si>
+    <t>Skara Brae</t>
+  </si>
+  <si>
+    <t>Tyrone</t>
+  </si>
+  <si>
+    <t>Innkeeper</t>
+  </si>
+  <si>
+    <t>gold_nugget</t>
+  </si>
+  <si>
+    <t>copper_nugget</t>
+  </si>
+  <si>
+    <t>Gating trade L1 to L2; "here's your change"</t>
+  </si>
+  <si>
+    <t>Sasha</t>
+  </si>
+  <si>
+    <t>Herbalist</t>
+  </si>
+  <si>
+    <t>spider_eye</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bone</t>
+  </si>
+  <si>
+    <t>redstone</t>
+  </si>
+  <si>
+    <t>rotten_flesh</t>
+  </si>
+  <si>
+    <t>Trinsic</t>
+  </si>
+  <si>
+    <t>Swindrik</t>
+  </si>
+  <si>
+    <t>Wizard</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>Gating Trade L1 to L2; "a worthy exchange!"</t>
+  </si>
+  <si>
+    <t>chorus_fruit</t>
+  </si>
+  <si>
+    <t>title: TELEPORT POTIONS
+author: Swindrik
+[PAGE]
+About POTIONS:
+Every VIRTUE has always had a MOONGATE and for each a TOWN was built nearby. 
+We use the power of the moongates and chorus fruit to TELEPORT between towns.
+In general, it needs a container, a carrier, a symbolic, and an edible.
+[PAGE]
+Potion List:
+B1. Return Potion    - GB, RD, D, ...and a seed.
+B5. Potion of Honor  - WB, CF, C, ...and a fungus.
+B6. Ptn/Compassion   - GB, RD, BR, and BM 
+[PAGE]
+The RETURN POTION is made from the simplest ingredients -- dirt, wheat seeds, and 1 redstone dust, mixed into a glass bottle.
+The trick, really, is to find a good source of redstone dust... And, some CLERICS are said to hold GREAT amounts of it!</t>
+  </si>
+  <si>
+    <t>Zajac</t>
+  </si>
+  <si>
+    <t>redstone_dust</t>
+  </si>
+  <si>
+    <t>Gating trade L1 to L2; "here's your change. Enjoy your stay".  (He opens iron door to room. It shuts when plate inside is stepped upon)</t>
+  </si>
+  <si>
+    <t>No further leveling required. He says "here's your change. Enjoy your stay".  (He opens iron door to room. It shuts when plate inside is stepped upon)</t>
+  </si>
+  <si>
+    <t>Terran</t>
+  </si>
+  <si>
+    <t>Bartender</t>
+  </si>
+  <si>
+    <t>carrot</t>
+  </si>
+  <si>
+    <t>milk_bucket</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>cooked_rabbit</t>
+  </si>
+  <si>
+    <t>Yew</t>
+  </si>
+  <si>
+    <t>Minoc</t>
+  </si>
+  <si>
+    <t>Magincia</t>
+  </si>
+  <si>
+    <t>Only some trades setup  (eg herbs; inn; Isaac mechanic)</t>
+  </si>
+  <si>
+    <t>Additional Trades need to be setup in Trinsic</t>
+  </si>
+  <si>
+    <t>No Trades set up yet in Yew</t>
+  </si>
+  <si>
+    <t>No Trades set up yet in Minoc</t>
+  </si>
+  <si>
+    <t>No Trades set up yet in Minoc  -- remember to add Fire Protection Potion to one of them!</t>
+  </si>
+  <si>
+    <t>Lycaeum</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Zircon</t>
+  </si>
+  <si>
+    <t>Fire Protection 3 Potion</t>
+  </si>
+  <si>
+    <t>Forgemaster</t>
+  </si>
+  <si>
+    <t>Piedro</t>
+  </si>
+  <si>
+    <t>ancient_debris</t>
+  </si>
+  <si>
+    <t>emerald_block</t>
+  </si>
+  <si>
+    <t>diamond_block</t>
+  </si>
+  <si>
+    <t>copper_block</t>
+  </si>
+  <si>
+    <t>gold_block</t>
+  </si>
+  <si>
+    <t>copper_boots</t>
+  </si>
+  <si>
+    <t>gold_boots</t>
+  </si>
+  <si>
+    <t>gold_helmet</t>
+  </si>
+  <si>
+    <t>copper_helmet</t>
+  </si>
+  <si>
+    <t>copper_leggings</t>
+  </si>
+  <si>
+    <t>gold_leggings</t>
+  </si>
+  <si>
+    <t>copper_chestplate</t>
+  </si>
+  <si>
+    <t>gold_chestplate</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Fletcher</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>&lt;--mystic bow--&gt;</t>
+  </si>
+  <si>
+    <t>Bob the Beggar</t>
+  </si>
+  <si>
+    <t>Beggar</t>
+  </si>
+  <si>
+    <t>orange_carpet</t>
+  </si>
+  <si>
+    <t>Gimble</t>
+  </si>
+  <si>
+    <t>orange_banner</t>
+  </si>
+  <si>
+    <t>Sacrifice advancement: Carpet matches the drapes.</t>
+  </si>
+  <si>
+    <t>Can be given to Zircon as his gating trade.</t>
+  </si>
+  <si>
+    <t>Jude</t>
+  </si>
+  <si>
+    <t>Ragged Soul</t>
+  </si>
+  <si>
+    <t>glistering_melon_slice</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>watermelon_seeds</t>
+  </si>
+  <si>
+    <t>Tinker</t>
+  </si>
+  <si>
+    <t>netherite_scrap</t>
+  </si>
+  <si>
+    <t>bow</t>
+  </si>
+  <si>
+    <t>copper_sword</t>
+  </si>
+  <si>
+    <t>gold_sword</t>
+  </si>
+  <si>
+    <t>copper_axe</t>
+  </si>
+  <si>
+    <t>gold_axe</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_boots--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_helmet--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_leggings--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_chestplate--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_sword--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--mystic_netherite_axe--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--Book of Metallurgy - IRON--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--Book of Metallurgy - COPPER--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--Book of Metallurgy - GOLD--&gt;</t>
+  </si>
+  <si>
+    <t>Unlocks Metallurgy: IRON</t>
+  </si>
+  <si>
+    <t>Unlocks Metallurgy: COPPER</t>
+  </si>
+  <si>
+    <t>Unlocks Metallurgy: GOLD</t>
+  </si>
+  <si>
+    <t>cookie</t>
+  </si>
+  <si>
+    <t>bucket</t>
+  </si>
+  <si>
+    <t>Level 5 only unlockable by Zircon. Any sort of buffed magic on it.</t>
+  </si>
+  <si>
+    <t>The book can have some boilerplate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The potion is made from glistering melon slice, water, redstone dust, and </t>
   </si>
   <si>
     <t>title: On CRAFTING POTIONS
@@ -305,7 +854,7 @@
 B2. Compassion Potion: 
 - blend well: brown mushroom and redstone dust. Sprinkle more redstone on top, and pour into a glass bottle. 
 B3. Potion of Sacrifice:
-- blend: bread and 2 redstone dusts into a water bottle.   Drinking wet bread makes you feel the sacrifice.</t>
+- blend: bread, glistering_melon_slice, and 1 redstone dusts into a water bottle.   Drinking wet bread makes you feel the sacrifice.</t>
   </si>
   <si>
     <t>title: On POTIONS
@@ -318,7 +867,7 @@
 Potions of note:
 B1. Return Potion (returns ye to yer stone circle).
 B2. Compassion Potion
-B3. Potion of Sacrifice (made from wet bread - yuck...)
+B3. Potion of Sacrifice (made partly from wet bread - yuck...)
 B4. Potion of Valor (the recipe was lost but it is believed it needs a ton of IRON).
 etc.
 [PAGE]
@@ -326,389 +875,17 @@
 The trick, really, is to find a good source of redstone dust... And, some CLERICS are said to hold GREAT amounts of it!</t>
   </si>
   <si>
-    <t>Pepper</t>
-  </si>
-  <si>
-    <t>Shepherd</t>
-  </si>
-  <si>
-    <t>black_wool</t>
-  </si>
-  <si>
-    <t>black carpet</t>
-  </si>
-  <si>
-    <t>brown_wool</t>
-  </si>
-  <si>
-    <t>brown_carpet</t>
-  </si>
-  <si>
-    <t>Unlocks conversation about rune location</t>
-  </si>
-  <si>
-    <t>Winston A.</t>
-  </si>
-  <si>
-    <t>Winston T.</t>
-  </si>
-  <si>
-    <t>Winston L.</t>
-  </si>
-  <si>
-    <t>Winston W.</t>
-  </si>
-  <si>
-    <t>Armorer</t>
-  </si>
-  <si>
-    <t>Toolsmith</t>
-  </si>
-  <si>
-    <t>Leatherworker</t>
-  </si>
-  <si>
-    <t>Weaponsmith</t>
-  </si>
-  <si>
-    <t>emerald</t>
-  </si>
-  <si>
-    <t>leather_chestplate</t>
-  </si>
-  <si>
-    <t>iron_nugget</t>
-  </si>
-  <si>
-    <t>iron_leggings</t>
-  </si>
-  <si>
-    <t>wooden_sword</t>
-  </si>
-  <si>
-    <t>wooden_hoe</t>
-  </si>
-  <si>
-    <t>iron_axe</t>
-  </si>
-  <si>
-    <t>iron_block</t>
-  </si>
-  <si>
-    <t>iron_boots</t>
-  </si>
-  <si>
-    <t>iron_ingot</t>
-  </si>
-  <si>
-    <t>iron_pickaxe</t>
-  </si>
-  <si>
-    <t>iron_helmet</t>
-  </si>
-  <si>
-    <t>iron_chestplate</t>
-  </si>
-  <si>
-    <t>wooden_pickaxe</t>
-  </si>
-  <si>
-    <t>wooden_axe</t>
-  </si>
-  <si>
-    <t>iron_sword</t>
-  </si>
-  <si>
-    <t>wooden_shovel</t>
-  </si>
-  <si>
-    <t>leather_leggings</t>
-  </si>
-  <si>
-    <t>leather_helmet</t>
-  </si>
-  <si>
-    <t>leather_boots</t>
-  </si>
-  <si>
-    <t>Gating trade from L1 to L2</t>
-  </si>
-  <si>
-    <t>Gating trade from L2 to L3</t>
-  </si>
-  <si>
-    <t>oak_log</t>
-  </si>
-  <si>
-    <t>Allows trade-triggered conversation to occur</t>
-  </si>
-  <si>
-    <t>Gating trade</t>
-  </si>
-  <si>
-    <t>Allows trade-triggered conversation to occur. And is a gating trade from L1 to L2.</t>
-  </si>
-  <si>
-    <t>title: INTRO TO METALLURGY
-author: Winston A.
-[PAGE]
-Novice stone miners will find they cannot mine cobblestones efficiently and will mostly just mine gravel. 
-And like them, novice metallurgists will only make great hunks of iron or puny nuggets but not well-refined ingots.
-In fact, novices aren't fit to even HOLD fresh ingots!
-(Continued...)
-[PAGE]
-Only the great metallurgists living in the town of MINOC are ALLOWED to share our dearest guild secrets on these matters.
-In BRITAIN, we can trade a full iron block for a single iron ingot...but you'll get a nasty surprise...</t>
-  </si>
-  <si>
-    <t>Winston M.</t>
-  </si>
-  <si>
-    <t>Mason</t>
-  </si>
-  <si>
-    <t>cobblestone</t>
-  </si>
-  <si>
-    <t>clay_ball</t>
-  </si>
-  <si>
-    <t>smooth_stone</t>
-  </si>
-  <si>
-    <t>furnace</t>
-  </si>
-  <si>
-    <t>stone</t>
-  </si>
-  <si>
-    <t>copper_pickaxe</t>
-  </si>
-  <si>
-    <t>copper_ingot</t>
-  </si>
-  <si>
-    <t>gold_ingot</t>
-  </si>
-  <si>
-    <t>stone_shovel</t>
-  </si>
-  <si>
-    <t>title: INTRO TO COBBLE MINING
-author: Winston M.
-[PAGE]
-Novice stone miners will find they cannot mine cobblestones efficiently and will mostly just mine gravel. 
-EXPERT Masons in BRITAIN, fortunately, can teach the secrets of Mining COBBLESTONEvia better tools.</t>
-  </si>
-  <si>
-    <t>Receiving iron_pickaxe will grant the SKILL-related advancement of "Journeyman Miner"</t>
-  </si>
-  <si>
-    <t>Receiving diamond_pickaxe will grant the SKILL-related advancement of "Expert Miner"</t>
-  </si>
-  <si>
-    <t>Receiving netherite_pickaxe will grant the SKILL-related advancement of "Master Miner"</t>
-  </si>
-  <si>
-    <t>diamond_pickaxe</t>
-  </si>
-  <si>
-    <t>netherite_pickaxe</t>
-  </si>
-  <si>
-    <t>golden_pickaxe</t>
-  </si>
-  <si>
-    <t>Player has no crafting table so can't make a furnace</t>
-  </si>
-  <si>
-    <t>stone_pickaxe</t>
-  </si>
-  <si>
-    <t>Jhelom</t>
-  </si>
-  <si>
-    <t>Hero</t>
-  </si>
-  <si>
-    <t>trial_key</t>
-  </si>
-  <si>
-    <t>goat_horn</t>
-  </si>
-  <si>
-    <t>totem_of_undying</t>
-  </si>
-  <si>
-    <t>wither_skeleton_skull</t>
-  </si>
-  <si>
-    <t>netherite_leggings</t>
-  </si>
-  <si>
-    <t>ghast_tear</t>
-  </si>
-  <si>
-    <t>netherite_boots</t>
-  </si>
-  <si>
-    <t>Hero's Juicy Trades</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>netherite_axe</t>
-  </si>
-  <si>
-    <t>diamond_leggings</t>
-  </si>
-  <si>
-    <t>white_banner</t>
-  </si>
-  <si>
-    <t>Must be an Ominous Banner that a Raid Captain dropped.</t>
-  </si>
-  <si>
-    <t>Skara Brae</t>
-  </si>
-  <si>
-    <t>Tyrone</t>
-  </si>
-  <si>
-    <t>Innkeeper</t>
-  </si>
-  <si>
-    <t>gold_nugget</t>
-  </si>
-  <si>
-    <t>copper_nugget</t>
-  </si>
-  <si>
-    <t>Gating trade L1 to L2; "here's your change"</t>
-  </si>
-  <si>
-    <t>Sasha</t>
-  </si>
-  <si>
-    <t>Herbalist</t>
-  </si>
-  <si>
-    <t>spider_eye</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bone</t>
-  </si>
-  <si>
-    <t>redstone</t>
-  </si>
-  <si>
-    <t>rotten_flesh</t>
-  </si>
-  <si>
-    <t>Trinsic</t>
-  </si>
-  <si>
-    <t>Swindrik</t>
-  </si>
-  <si>
-    <t>Wizard</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <t>Gating Trade L1 to L2; "a worthy exchange!"</t>
-  </si>
-  <si>
-    <t>chorus_fruit</t>
-  </si>
-  <si>
-    <t>title: TELEPORT POTIONS
-author: Swindrik
-[PAGE]
-About POTIONS:
-Every VIRTUE has always had a MOONGATE and for each a TOWN was built nearby. 
-We use the power of the moongates and chorus fruit to TELEPORT between towns.
-In general, it needs a container, a carrier, a symbolic, and an edible.
-[PAGE]
-Potion List:
-B1. Return Potion    - GB, RD, D, ...and a seed.
-B5. Potion of Honor  - WB, CF, C, ...and a fungus.
-B6. Ptn/Compassion   - GB, RD, BR, and BM 
-[PAGE]
-The RETURN POTION is made from the simplest ingredients -- dirt, wheat seeds, and 1 redstone dust, mixed into a glass bottle.
-The trick, really, is to find a good source of redstone dust... And, some CLERICS are said to hold GREAT amounts of it!</t>
-  </si>
-  <si>
-    <t>Zajac</t>
-  </si>
-  <si>
-    <t>redstone_dust</t>
-  </si>
-  <si>
-    <t>Gating trade L1 to L2; "here's your change. Enjoy your stay".  (He opens iron door to room. It shuts when plate inside is stepped upon)</t>
-  </si>
-  <si>
-    <t>No further leveling required. He says "here's your change. Enjoy your stay".  (He opens iron door to room. It shuts when plate inside is stepped upon)</t>
-  </si>
-  <si>
-    <t>Terran</t>
-  </si>
-  <si>
-    <t>Bartender</t>
-  </si>
-  <si>
-    <t>carrot</t>
-  </si>
-  <si>
-    <t>milk_bucket</t>
-  </si>
-  <si>
-    <t>sugar</t>
-  </si>
-  <si>
-    <t>cooked_rabbit</t>
-  </si>
-  <si>
-    <t>Yew</t>
-  </si>
-  <si>
-    <t>Minoc</t>
-  </si>
-  <si>
-    <t>Magincia</t>
-  </si>
-  <si>
-    <t>Only some trades setup  (eg herbs; inn; Isaac mechanic)</t>
-  </si>
-  <si>
-    <t>Additional Trades need to be setup in Trinsic</t>
-  </si>
-  <si>
-    <t>No Trades set up yet in Yew</t>
-  </si>
-  <si>
-    <t>No Trades set up yet in Minoc</t>
-  </si>
-  <si>
-    <t>No Trades set up yet in Minoc  -- remember to add Fire Protection Potion to one of them!</t>
-  </si>
-  <si>
-    <t>Lycaeum</t>
-  </si>
-  <si>
-    <t>TBD</t>
+    <t>&lt;--Potion of Sacrifice made from 1 bread, 1 water bottle, 1 redstone dust, and 1 glistering melon slice--&gt;</t>
+  </si>
+  <si>
+    <t>&lt;--Lore Book on Sacrifice--&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -769,8 +946,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF007BB8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -804,6 +988,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -861,7 +1063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -978,9 +1180,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1050,6 +1249,53 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1434,8 +1680,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:1" s="78" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="77" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1479,21 +1725,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L1048576"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L1048574"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="27" customWidth="1"/>
     <col min="2" max="2" width="18" style="27" customWidth="1"/>
     <col min="3" max="3" width="16.5546875" style="27" customWidth="1"/>
     <col min="4" max="4" width="8" style="27" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="23.77734375" customWidth="1"/>
     <col min="6" max="6" width="10" style="27" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
     <col min="8" max="8" width="10" style="27" customWidth="1"/>
-    <col min="9" max="9" width="75.88671875" style="44" customWidth="1"/>
-    <col min="10" max="10" width="10" style="53" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="53" customWidth="1"/>
-    <col min="12" max="12" width="34" style="52" customWidth="1"/>
+    <col min="9" max="9" width="57.109375" style="44" customWidth="1"/>
+    <col min="10" max="10" width="10" style="52" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="52" customWidth="1"/>
+    <col min="12" max="12" width="34" style="51" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1534,7 +1781,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>32</v>
       </c>
@@ -1560,15 +1807,15 @@
         <v>1</v>
       </c>
       <c r="I2" s="36"/>
-      <c r="J2" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K2" s="54">
+      <c r="J2" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K2" s="53">
         <v>10</v>
       </c>
       <c r="L2" s="36"/>
     </row>
-    <row r="3" spans="1:12" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="52.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
@@ -1594,17 +1841,17 @@
         <v>1</v>
       </c>
       <c r="I3" s="36"/>
-      <c r="J3" s="54">
+      <c r="J3" s="53">
         <v>2</v>
       </c>
-      <c r="K3" s="54">
+      <c r="K3" s="53">
         <v>5</v>
       </c>
       <c r="L3" s="36" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
@@ -1630,17 +1877,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="36"/>
-      <c r="J4" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K4" s="54">
+      <c r="J4" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K4" s="53">
         <v>70</v>
       </c>
       <c r="L4" s="36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>32</v>
       </c>
@@ -1666,17 +1913,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="36"/>
-      <c r="J5" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K5" s="54">
+      <c r="J5" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K5" s="53">
         <v>0</v>
       </c>
       <c r="L5" s="36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
@@ -1702,17 +1949,17 @@
         <v>1</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="54">
-        <v>1</v>
-      </c>
-      <c r="K6" s="54">
+      <c r="J6" s="53">
+        <v>1</v>
+      </c>
+      <c r="K6" s="53">
         <v>150</v>
       </c>
       <c r="L6" s="36" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
@@ -1738,15 +1985,15 @@
         <v>1</v>
       </c>
       <c r="I7" s="36"/>
-      <c r="J7" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K7" s="54">
+      <c r="J7" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K7" s="53">
         <v>5</v>
       </c>
       <c r="L7" s="36"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
@@ -1772,15 +2019,15 @@
         <v>1</v>
       </c>
       <c r="I8" s="36"/>
-      <c r="J8" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K8" s="54">
+      <c r="J8" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K8" s="53">
         <v>10</v>
       </c>
       <c r="L8" s="36"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
@@ -1806,17 +2053,17 @@
         <v>2</v>
       </c>
       <c r="I9" s="36"/>
-      <c r="J9" s="54">
+      <c r="J9" s="53">
         <v>2</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="53">
         <v>5</v>
       </c>
       <c r="L9" s="36" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>32</v>
       </c>
@@ -1842,17 +2089,17 @@
         <v>1</v>
       </c>
       <c r="I10" s="36"/>
-      <c r="J10" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K10" s="54">
+      <c r="J10" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K10" s="53">
         <v>70</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
@@ -1878,17 +2125,17 @@
         <v>1</v>
       </c>
       <c r="I11" s="37"/>
-      <c r="J11" s="55">
-        <v>999999</v>
-      </c>
-      <c r="K11" s="55">
+      <c r="J11" s="54">
+        <v>999999</v>
+      </c>
+      <c r="K11" s="54">
         <v>0</v>
       </c>
       <c r="L11" s="37" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
@@ -1914,15 +2161,15 @@
         <v>1</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K12" s="54">
+      <c r="J12" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K12" s="53">
         <v>30</v>
       </c>
       <c r="L12" s="36"/>
     </row>
-    <row r="13" spans="1:12" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="79.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
@@ -1950,17 +2197,17 @@
       <c r="I13" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="J13" s="54">
-        <v>1</v>
-      </c>
-      <c r="K13" s="54">
+      <c r="J13" s="53">
+        <v>1</v>
+      </c>
+      <c r="K13" s="53">
         <v>250</v>
       </c>
       <c r="L13" s="36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>32</v>
       </c>
@@ -1986,15 +2233,15 @@
         <v>1</v>
       </c>
       <c r="I14" s="36"/>
-      <c r="J14" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K14" s="54">
+      <c r="J14" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K14" s="53">
         <v>0</v>
       </c>
       <c r="L14" s="36"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
@@ -2020,15 +2267,15 @@
         <v>1</v>
       </c>
       <c r="I15" s="36"/>
-      <c r="J15" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K15" s="54">
+      <c r="J15" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K15" s="53">
         <v>10</v>
       </c>
       <c r="L15" s="36"/>
     </row>
-    <row r="16" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>32</v>
       </c>
@@ -2054,17 +2301,17 @@
         <v>1</v>
       </c>
       <c r="I16" s="36"/>
-      <c r="J16" s="54">
+      <c r="J16" s="53">
         <v>2</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="53">
         <v>5</v>
       </c>
       <c r="L16" s="36" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
@@ -2090,17 +2337,17 @@
         <v>1</v>
       </c>
       <c r="I17" s="36"/>
-      <c r="J17" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K17" s="54">
+      <c r="J17" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K17" s="53">
         <v>70</v>
       </c>
       <c r="L17" s="36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>32</v>
       </c>
@@ -2128,17 +2375,17 @@
       <c r="I18" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="54">
-        <v>1</v>
-      </c>
-      <c r="K18" s="54">
+      <c r="J18" s="53">
+        <v>1</v>
+      </c>
+      <c r="K18" s="53">
         <v>150</v>
       </c>
       <c r="L18" s="36" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>32</v>
       </c>
@@ -2164,15 +2411,15 @@
         <v>1</v>
       </c>
       <c r="I19" s="36"/>
-      <c r="J19" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K19" s="54">
+      <c r="J19" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K19" s="53">
         <v>5</v>
       </c>
       <c r="L19" s="36"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>32</v>
       </c>
@@ -2198,15 +2445,15 @@
         <v>1</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="54">
-        <v>999999</v>
-      </c>
-      <c r="K20" s="54">
+      <c r="J20" s="53">
+        <v>999999</v>
+      </c>
+      <c r="K20" s="53">
         <v>0</v>
       </c>
       <c r="L20" s="36"/>
     </row>
-    <row r="21" spans="1:12" s="13" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" s="13" customFormat="1" ht="52.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>32</v>
       </c>
@@ -2242,7 +2489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>32</v>
       </c>
@@ -2276,7 +2523,7 @@
       </c>
       <c r="L22" s="38"/>
     </row>
-    <row r="23" spans="1:12" s="13" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" s="13" customFormat="1" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
         <v>32</v>
       </c>
@@ -2314,8 +2561,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="60" t="s">
+    <row r="24" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="23" t="s">
@@ -2346,10 +2593,10 @@
       <c r="K24" s="33">
         <v>1</v>
       </c>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60" t="s">
+      <c r="L24" s="46"/>
+    </row>
+    <row r="25" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="23" t="s">
@@ -2380,10 +2627,10 @@
       <c r="K25" s="33">
         <v>30</v>
       </c>
-      <c r="L25" s="47"/>
-    </row>
-    <row r="26" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="60" t="s">
+      <c r="L25" s="46"/>
+    </row>
+    <row r="26" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="23" t="s">
@@ -2414,10 +2661,10 @@
       <c r="K26" s="33">
         <v>30</v>
       </c>
-      <c r="L26" s="47"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="60" t="s">
+      <c r="L26" s="46"/>
+    </row>
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -2448,16 +2695,16 @@
       <c r="K27" s="33">
         <v>10</v>
       </c>
-      <c r="L27" s="48"/>
-    </row>
-    <row r="28" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="60" t="s">
+      <c r="L27" s="47"/>
+    </row>
+    <row r="28" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="60" t="s">
         <v>79</v>
       </c>
       <c r="D28" s="24">
@@ -2482,18 +2729,18 @@
       <c r="K28" s="22">
         <v>10</v>
       </c>
-      <c r="L28" s="49" t="s">
+      <c r="L28" s="48" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="60" t="s">
+    <row r="29" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="60" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="24">
@@ -2518,16 +2765,16 @@
       <c r="K29" s="22">
         <v>30</v>
       </c>
-      <c r="L29" s="49"/>
-    </row>
-    <row r="30" spans="1:12" s="8" customFormat="1" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="60" t="s">
+      <c r="L29" s="48"/>
+    </row>
+    <row r="30" spans="1:12" s="8" customFormat="1" ht="112.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="60" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="24">
@@ -2545,8 +2792,8 @@
       <c r="H30" s="24">
         <v>1</v>
       </c>
-      <c r="I30" s="45" t="s">
-        <v>88</v>
+      <c r="I30" s="87" t="s">
+        <v>262</v>
       </c>
       <c r="J30" s="21">
         <v>999999</v>
@@ -2554,18 +2801,18 @@
       <c r="K30" s="22">
         <v>80</v>
       </c>
-      <c r="L30" s="49" t="s">
+      <c r="L30" s="48" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="8" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="60" t="s">
+    <row r="31" spans="1:12" s="8" customFormat="1" ht="74.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="60" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="24">
@@ -2583,8 +2830,8 @@
       <c r="H31" s="24">
         <v>1</v>
       </c>
-      <c r="I31" s="45" t="s">
-        <v>87</v>
+      <c r="I31" s="87" t="s">
+        <v>261</v>
       </c>
       <c r="J31" s="21">
         <v>999999</v>
@@ -2592,31 +2839,31 @@
       <c r="K31" s="22">
         <v>10</v>
       </c>
-      <c r="L31" s="49" t="s">
+      <c r="L31" s="48" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A32" s="60" t="s">
+    <row r="32" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="25">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="25">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="F32" s="25">
         <v>3</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H32" s="25">
         <v>1</v>
@@ -2628,31 +2875,31 @@
       <c r="K32" s="29">
         <v>10</v>
       </c>
-      <c r="L32" s="50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A33" s="60" t="s">
+      <c r="L32" s="49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D33" s="25">
         <v>1</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F33" s="25">
         <v>3</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H33" s="25">
         <v>1</v>
@@ -2664,19 +2911,19 @@
       <c r="K33" s="29">
         <v>10</v>
       </c>
-      <c r="L33" s="50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A34" s="60" t="s">
+      <c r="L33" s="49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" s="60" t="s">
-        <v>100</v>
+      <c r="B34" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="59" t="s">
+        <v>98</v>
       </c>
       <c r="D34" s="23">
         <v>1</v>
@@ -2700,31 +2947,31 @@
       <c r="K34" s="22">
         <v>1</v>
       </c>
-      <c r="L34" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="60" t="s">
+      <c r="L34" s="46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="60" t="s">
-        <v>100</v>
+      <c r="B35" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>98</v>
       </c>
       <c r="D35" s="23">
         <v>1</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F35" s="23">
         <v>1</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H35" s="24">
         <v>1</v>
@@ -2736,31 +2983,31 @@
       <c r="K35" s="22">
         <v>10</v>
       </c>
-      <c r="L35" s="47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="60" t="s">
+      <c r="L35" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="60" t="s">
-        <v>100</v>
+      <c r="B36" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="59" t="s">
+        <v>98</v>
       </c>
       <c r="D36" s="23">
         <v>2</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F36" s="23">
         <v>1</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H36" s="24">
         <v>1</v>
@@ -2772,25 +3019,25 @@
       <c r="K36" s="22">
         <v>70</v>
       </c>
-      <c r="L36" s="47" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="30" customFormat="1" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="30" customFormat="1" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37" s="33">
         <v>3</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F37" s="33">
         <v>1</v>
@@ -2801,8 +3048,8 @@
       <c r="H37" s="22">
         <v>1</v>
       </c>
-      <c r="I37" s="46" t="s">
-        <v>130</v>
+      <c r="I37" s="45" t="s">
+        <v>128</v>
       </c>
       <c r="J37" s="21">
         <v>999999</v>
@@ -2810,29 +3057,29 @@
       <c r="K37" s="22">
         <v>10</v>
       </c>
-      <c r="L37" s="51"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L37" s="50"/>
+    </row>
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D38" s="23">
         <v>3</v>
       </c>
       <c r="E38" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="23">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="F38" s="23">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="H38" s="24">
         <v>1</v>
@@ -2844,29 +3091,29 @@
       <c r="K38" s="33">
         <v>5</v>
       </c>
-      <c r="L38" s="47"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L38" s="46"/>
+    </row>
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39" s="23">
         <v>4</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F39" s="23">
         <v>3</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H39" s="24">
         <v>1</v>
@@ -2878,29 +3125,29 @@
       <c r="K39" s="33">
         <v>5</v>
       </c>
-      <c r="L39" s="47"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L39" s="46"/>
+    </row>
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D40" s="23">
         <v>4</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F40" s="23">
         <v>3</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H40" s="24">
         <v>1</v>
@@ -2912,29 +3159,29 @@
       <c r="K40" s="33">
         <v>5</v>
       </c>
-      <c r="L40" s="47"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L40" s="46"/>
+    </row>
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D41" s="23">
         <v>4</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F41" s="23">
         <v>3</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H41" s="24">
         <v>1</v>
@@ -2946,29 +3193,29 @@
       <c r="K41" s="33">
         <v>5</v>
       </c>
-      <c r="L41" s="47"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L41" s="46"/>
+    </row>
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D42" s="23">
         <v>4</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F42" s="23">
         <v>3</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H42" s="24">
         <v>1</v>
@@ -2980,17 +3227,17 @@
       <c r="K42" s="33">
         <v>5</v>
       </c>
-      <c r="L42" s="47"/>
-    </row>
-    <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A43" s="60" t="s">
+      <c r="L42" s="46"/>
+    </row>
+    <row r="43" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="60" t="s">
-        <v>101</v>
+      <c r="B43" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D43" s="23">
         <v>1</v>
@@ -3014,31 +3261,31 @@
       <c r="K43" s="22">
         <v>1</v>
       </c>
-      <c r="L43" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="60" t="s">
+      <c r="L43" s="46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="60" t="s">
-        <v>101</v>
+      <c r="B44" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D44" s="31">
         <v>1</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F44" s="31">
         <v>1</v>
       </c>
       <c r="G44" s="32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H44" s="24">
         <v>1</v>
@@ -3050,31 +3297,31 @@
       <c r="K44" s="22">
         <v>5</v>
       </c>
-      <c r="L44" s="47" t="s">
+      <c r="L44" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="D45" s="31">
+        <v>1</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="60" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="31">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="F45" s="31">
         <v>1</v>
       </c>
       <c r="G45" s="32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H45" s="24">
         <v>1</v>
@@ -3086,31 +3333,31 @@
       <c r="K45" s="22">
         <v>5</v>
       </c>
-      <c r="L45" s="47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="60" t="s">
+      <c r="L45" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="60" t="s">
-        <v>101</v>
+      <c r="B46" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D46" s="31">
         <v>2</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F46" s="31">
         <v>1</v>
       </c>
       <c r="G46" s="32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H46" s="24">
         <v>1</v>
@@ -3122,31 +3369,31 @@
       <c r="K46" s="22">
         <v>50</v>
       </c>
-      <c r="L46" s="49" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
+      <c r="L46" s="48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="60" t="s">
-        <v>101</v>
+      <c r="B47" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D47" s="31">
         <v>2</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F47" s="23">
         <v>1</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H47" s="24">
         <v>1</v>
@@ -3158,29 +3405,29 @@
       <c r="K47" s="33">
         <v>5</v>
       </c>
-      <c r="L47" s="47"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="60" t="s">
+      <c r="L47" s="46"/>
+    </row>
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="60" t="s">
-        <v>101</v>
+      <c r="B48" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D48" s="31">
         <v>2</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F48" s="23">
         <v>1</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H48" s="24">
         <v>1</v>
@@ -3192,29 +3439,29 @@
       <c r="K48" s="33">
         <v>5</v>
       </c>
-      <c r="L48" s="47"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="60" t="s">
+      <c r="L48" s="46"/>
+    </row>
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="60" t="s">
-        <v>101</v>
+      <c r="B49" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D49" s="31">
         <v>2</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F49" s="23">
         <v>1</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H49" s="24">
         <v>1</v>
@@ -3226,29 +3473,29 @@
       <c r="K49" s="33">
         <v>5</v>
       </c>
-      <c r="L49" s="47"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="60" t="s">
+      <c r="L49" s="46"/>
+    </row>
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="60" t="s">
-        <v>101</v>
+      <c r="B50" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="59" t="s">
+        <v>99</v>
       </c>
       <c r="D50" s="31">
         <v>3</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F50" s="23">
         <v>9</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H50" s="24">
         <v>1</v>
@@ -3260,17 +3507,17 @@
       <c r="K50" s="33">
         <v>5</v>
       </c>
-      <c r="L50" s="47"/>
-    </row>
-    <row r="51" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A51" s="60" t="s">
+      <c r="L50" s="46"/>
+    </row>
+    <row r="51" spans="1:12" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" s="60" t="s">
-        <v>102</v>
+      <c r="B51" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="59" t="s">
+        <v>100</v>
       </c>
       <c r="D51" s="23">
         <v>1</v>
@@ -3294,31 +3541,31 @@
       <c r="K51" s="22">
         <v>10</v>
       </c>
-      <c r="L51" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="L51" s="46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="60" t="s">
-        <v>102</v>
+      <c r="B52" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="59" t="s">
+        <v>100</v>
       </c>
       <c r="D52" s="23">
         <v>2</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="23">
         <v>3</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H52" s="24">
         <v>1</v>
@@ -3330,29 +3577,29 @@
       <c r="K52" s="22">
         <v>10</v>
       </c>
-      <c r="L52" s="47"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
+      <c r="L52" s="46"/>
+    </row>
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="60" t="s">
-        <v>102</v>
+      <c r="B53" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="59" t="s">
+        <v>100</v>
       </c>
       <c r="D53" s="23">
         <v>2</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F53" s="23">
         <v>3</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H53" s="24">
         <v>1</v>
@@ -3364,29 +3611,29 @@
       <c r="K53" s="22">
         <v>10</v>
       </c>
-      <c r="L53" s="47"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="60" t="s">
+      <c r="L53" s="46"/>
+    </row>
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" s="60" t="s">
-        <v>102</v>
+      <c r="B54" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="59" t="s">
+        <v>100</v>
       </c>
       <c r="D54" s="23">
         <v>2</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F54" s="23">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H54" s="24">
         <v>1</v>
@@ -3398,29 +3645,29 @@
       <c r="K54" s="22">
         <v>10</v>
       </c>
-      <c r="L54" s="47"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="60" t="s">
+      <c r="L54" s="46"/>
+    </row>
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="60" t="s">
-        <v>102</v>
+      <c r="B55" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="59" t="s">
+        <v>100</v>
       </c>
       <c r="D55" s="23">
         <v>2</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F55" s="23">
         <v>3</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H55" s="24">
         <v>1</v>
@@ -3432,17 +3679,17 @@
       <c r="K55" s="22">
         <v>10</v>
       </c>
-      <c r="L55" s="47"/>
-    </row>
-    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A56" s="60" t="s">
+      <c r="L55" s="46"/>
+    </row>
+    <row r="56" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B56" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="60" t="s">
-        <v>103</v>
+      <c r="B56" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D56" s="23">
         <v>1</v>
@@ -3466,31 +3713,31 @@
       <c r="K56" s="22">
         <v>1</v>
       </c>
-      <c r="L56" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="60" t="s">
+      <c r="L56" s="46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C57" s="60" t="s">
-        <v>103</v>
+      <c r="B57" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D57" s="23">
         <v>1</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F57" s="23">
         <v>1</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H57" s="24">
         <v>1</v>
@@ -3502,31 +3749,31 @@
       <c r="K57" s="22">
         <v>10</v>
       </c>
-      <c r="L57" s="47" t="s">
+      <c r="L57" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="31">
+        <v>1</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C58" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" s="31">
-        <v>1</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="F58" s="31">
         <v>1</v>
       </c>
       <c r="G58" s="32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H58" s="24">
         <v>1</v>
@@ -3538,31 +3785,31 @@
       <c r="K58" s="22">
         <v>10</v>
       </c>
-      <c r="L58" s="47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="60" t="s">
+      <c r="L58" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C59" s="60" t="s">
-        <v>103</v>
+      <c r="B59" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D59" s="23">
         <v>2</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F59" s="23">
         <v>9</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H59" s="24">
         <v>1</v>
@@ -3574,29 +3821,29 @@
       <c r="K59" s="22">
         <v>10</v>
       </c>
-      <c r="L59" s="49"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="60" t="s">
+      <c r="L59" s="48"/>
+    </row>
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C60" s="60" t="s">
-        <v>103</v>
+      <c r="B60" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D60" s="23">
         <v>2</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F60" s="23">
         <v>9</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H60" s="24">
         <v>1</v>
@@ -3608,29 +3855,29 @@
       <c r="K60" s="22">
         <v>10</v>
       </c>
-      <c r="L60" s="49"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="60" t="s">
+      <c r="L60" s="48"/>
+    </row>
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B61" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="60" t="s">
-        <v>103</v>
+      <c r="B61" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D61" s="23">
         <v>2</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F61" s="23">
         <v>1</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H61" s="24">
         <v>1</v>
@@ -3642,29 +3889,29 @@
       <c r="K61" s="22">
         <v>70</v>
       </c>
-      <c r="L61" s="49"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="60" t="s">
+      <c r="L61" s="48"/>
+    </row>
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B62" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="60" t="s">
-        <v>103</v>
+      <c r="B62" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D62" s="23">
         <v>2</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F62" s="23">
         <v>1</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H62" s="24">
         <v>1</v>
@@ -3676,17 +3923,17 @@
       <c r="K62" s="22">
         <v>70</v>
       </c>
-      <c r="L62" s="49"/>
-    </row>
-    <row r="63" spans="1:12" s="27" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L62" s="48"/>
+    </row>
+    <row r="63" spans="1:12" s="27" customFormat="1" ht="25.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D63" s="23">
         <v>1</v>
@@ -3710,31 +3957,31 @@
       <c r="K63" s="22">
         <v>1</v>
       </c>
-      <c r="L63" s="47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L63" s="46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C64" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="31">
+        <v>1</v>
+      </c>
+      <c r="E64" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D64" s="31">
-        <v>1</v>
-      </c>
-      <c r="E64" s="33" t="s">
-        <v>134</v>
-      </c>
       <c r="F64" s="31">
         <v>1</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H64" s="24">
         <v>1</v>
@@ -3746,29 +3993,29 @@
       <c r="K64" s="22">
         <v>1</v>
       </c>
-      <c r="L64" s="47"/>
-    </row>
-    <row r="65" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L64" s="46"/>
+    </row>
+    <row r="65" spans="1:12" s="27" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D65" s="23">
         <v>2</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F65" s="23">
         <v>1</v>
       </c>
       <c r="G65" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H65" s="24">
         <v>1</v>
@@ -3780,31 +4027,31 @@
       <c r="K65" s="33">
         <v>5</v>
       </c>
-      <c r="L65" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="53" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L65" s="46" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C66" s="33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D66" s="33">
         <v>2</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F66" s="33">
         <v>8</v>
       </c>
       <c r="G66" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H66" s="33">
         <v>1</v>
@@ -3816,25 +4063,25 @@
       <c r="K66" s="33">
         <v>10</v>
       </c>
-      <c r="L66" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="53" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L66" s="50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C67" s="33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D67" s="33">
         <v>2</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F67" s="33">
         <v>8</v>
@@ -3845,8 +4092,8 @@
       <c r="H67" s="33">
         <v>1</v>
       </c>
-      <c r="I67" s="46" t="s">
-        <v>142</v>
+      <c r="I67" s="45" t="s">
+        <v>140</v>
       </c>
       <c r="J67" s="33">
         <v>10</v>
@@ -3854,31 +4101,31 @@
       <c r="K67" s="33">
         <v>50</v>
       </c>
-      <c r="L67" s="51" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="53" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L67" s="50" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D68" s="23">
         <v>2</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F68" s="23">
         <v>5</v>
       </c>
       <c r="G68" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H68" s="23">
         <v>1</v>
@@ -3890,31 +4137,31 @@
       <c r="K68" s="22">
         <v>30</v>
       </c>
-      <c r="L68" s="47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="53" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L68" s="46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D69" s="23">
         <v>3</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F69" s="23">
         <v>5</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H69" s="23">
         <v>1</v>
@@ -3926,31 +4173,31 @@
       <c r="K69" s="22">
         <v>20</v>
       </c>
-      <c r="L69" s="47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="L69" s="46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D70" s="23">
         <v>3</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F70" s="23">
         <v>10</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H70" s="23">
         <v>1</v>
@@ -3962,31 +4209,31 @@
       <c r="K70" s="22">
         <v>50</v>
       </c>
-      <c r="L70" s="47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="L70" s="46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D71" s="23">
         <v>4</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F71" s="23">
         <v>15</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H71" s="23">
         <v>1</v>
@@ -3998,31 +4245,31 @@
       <c r="K71" s="22">
         <v>100</v>
       </c>
-      <c r="L71" s="47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="L71" s="46" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D72" s="23">
         <v>5</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F72" s="23">
         <v>20</v>
       </c>
       <c r="G72" s="23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H72" s="23">
         <v>1</v>
@@ -4034,31 +4281,31 @@
       <c r="K72" s="22">
         <v>100</v>
       </c>
-      <c r="L72" s="47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="60" t="s">
+      <c r="L72" s="46" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="31">
+        <v>1</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="60" t="s">
+      <c r="F73" s="31">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="s">
         <v>152</v>
-      </c>
-      <c r="C73" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D73" s="31">
-        <v>1</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F73" s="31">
-        <v>1</v>
-      </c>
-      <c r="G73" s="32" t="s">
-        <v>154</v>
       </c>
       <c r="H73" s="24">
         <v>1</v>
@@ -4070,31 +4317,31 @@
       <c r="K73" s="22">
         <v>10</v>
       </c>
-      <c r="L73" s="47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B74" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C74" s="60" t="s">
-        <v>103</v>
+      <c r="L73" s="46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D74" s="23">
         <v>2</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F74" s="23">
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H74" s="24">
         <v>1</v>
@@ -4106,31 +4353,31 @@
       <c r="K74" s="22">
         <v>70</v>
       </c>
-      <c r="L74" s="47" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B75" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C75" s="60" t="s">
-        <v>103</v>
+      <c r="L74" s="46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D75" s="23">
         <v>3</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F75" s="23">
         <v>1</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H75" s="24">
         <v>1</v>
@@ -4142,31 +4389,31 @@
       <c r="K75" s="22">
         <v>50</v>
       </c>
-      <c r="L75" s="49" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A76" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C76" s="60" t="s">
-        <v>103</v>
+      <c r="L75" s="48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D76" s="23">
         <v>3</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F76" s="23">
         <v>1</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H76" s="24">
         <v>1</v>
@@ -4178,31 +4425,31 @@
       <c r="K76" s="22">
         <v>50</v>
       </c>
-      <c r="L76" s="49" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="60" t="s">
-        <v>103</v>
+      <c r="L76" s="48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D77" s="23">
         <v>3</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F77" s="23">
         <v>1</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H77" s="24">
         <v>1</v>
@@ -4214,31 +4461,31 @@
       <c r="K77" s="22">
         <v>50</v>
       </c>
-      <c r="L77" s="49" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B78" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C78" s="60" t="s">
-        <v>103</v>
+      <c r="L77" s="48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C78" s="59" t="s">
+        <v>101</v>
       </c>
       <c r="D78" s="23">
         <v>3</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F78" s="23">
         <v>1</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H78" s="24">
         <v>1</v>
@@ -4250,31 +4497,31 @@
       <c r="K78" s="22">
         <v>50</v>
       </c>
-      <c r="L78" s="49" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A79" s="62" t="s">
+      <c r="L78" s="48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="B79" s="26" t="s">
+      <c r="D79" s="26">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="C79" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="D79" s="26">
-        <v>1</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="F79" s="26">
         <v>2</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H79" s="26">
         <v>1</v>
@@ -4286,31 +4533,31 @@
       <c r="K79" s="28">
         <v>10</v>
       </c>
-      <c r="L79" s="48" t="s">
+      <c r="L79" s="47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="26" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="62" t="s">
-        <v>166</v>
-      </c>
-      <c r="B80" s="26" t="s">
+      <c r="D80" s="26">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C80" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D80" s="26">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="F80" s="26">
         <v>1</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H80" s="26">
         <v>1</v>
@@ -4322,29 +4569,29 @@
       <c r="K80" s="28">
         <v>5</v>
       </c>
-      <c r="L80" s="48"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="62" t="s">
-        <v>166</v>
+      <c r="L80" s="47"/>
+    </row>
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="61" t="s">
+        <v>164</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C81" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D81" s="26">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D81" s="26">
-        <v>1</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>175</v>
-      </c>
       <c r="F81" s="26">
         <v>1</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H81" s="26">
         <v>1</v>
@@ -4356,29 +4603,29 @@
       <c r="K81" s="28">
         <v>5</v>
       </c>
-      <c r="L81" s="48"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="62" t="s">
-        <v>166</v>
+      <c r="L81" s="47"/>
+    </row>
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="61" t="s">
+        <v>164</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D82" s="26">
         <v>1</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F82" s="26">
         <v>1</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H82" s="26">
         <v>1</v>
@@ -4390,29 +4637,29 @@
       <c r="K82" s="28">
         <v>2</v>
       </c>
-      <c r="L82" s="48"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="62" t="s">
-        <v>166</v>
+      <c r="L82" s="47"/>
+    </row>
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="61" t="s">
+        <v>164</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D83" s="26">
         <v>1</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F83" s="26">
         <v>1</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H83" s="26">
         <v>1</v>
@@ -4424,29 +4671,29 @@
       <c r="K83" s="28">
         <v>2</v>
       </c>
-      <c r="L83" s="48"/>
-    </row>
-    <row r="84" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="L83" s="47"/>
+    </row>
+    <row r="84" spans="1:12" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="D84" s="26">
+        <v>1</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C84" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D84" s="26">
-        <v>1</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="F84" s="26">
         <v>1</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H84" s="26">
         <v>2</v>
@@ -4458,19 +4705,19 @@
       <c r="K84" s="28">
         <v>5</v>
       </c>
-      <c r="L84" s="57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L84" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="26" t="s">
         <v>179</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="C85" s="26" t="s">
-        <v>181</v>
       </c>
       <c r="D85" s="26">
         <v>2</v>
@@ -4482,7 +4729,7 @@
         <v>3</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H85" s="26">
         <v>2</v>
@@ -4494,29 +4741,29 @@
       <c r="K85" s="29">
         <v>30</v>
       </c>
-      <c r="L85" s="57"/>
-    </row>
-    <row r="86" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="L85" s="56"/>
+    </row>
+    <row r="86" spans="1:12" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="26" t="s">
         <v>179</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" s="26" t="s">
-        <v>181</v>
       </c>
       <c r="D86" s="26">
         <v>2</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F86" s="26">
         <v>1</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H86" s="26">
         <v>1</v>
@@ -4528,25 +4775,25 @@
       <c r="K86" s="29">
         <v>30</v>
       </c>
-      <c r="L86" s="57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" s="27" customFormat="1" ht="276" x14ac:dyDescent="0.3">
+      <c r="L86" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="27" customFormat="1" ht="276" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="28" t="s">
         <v>179</v>
-      </c>
-      <c r="B87" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="C87" s="28" t="s">
-        <v>181</v>
       </c>
       <c r="D87" s="28">
         <v>3</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F87" s="28">
         <v>1</v>
@@ -4557,8 +4804,8 @@
       <c r="H87" s="33">
         <v>1</v>
       </c>
-      <c r="I87" s="56" t="s">
-        <v>185</v>
+      <c r="I87" s="55" t="s">
+        <v>183</v>
       </c>
       <c r="J87" s="28">
         <v>999999</v>
@@ -4566,31 +4813,31 @@
       <c r="K87" s="28">
         <v>5</v>
       </c>
-      <c r="L87" s="57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="B88" s="63" t="s">
-        <v>186</v>
+      <c r="L87" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="53.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" s="62" t="s">
+        <v>184</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D88" s="26">
         <v>1</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F88" s="26">
         <v>2</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H88" s="26">
         <v>1</v>
@@ -4602,31 +4849,31 @@
       <c r="K88" s="28">
         <v>10</v>
       </c>
-      <c r="L88" s="48" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="B89" s="63" t="s">
+      <c r="L88" s="47" t="s">
         <v>186</v>
       </c>
+    </row>
+    <row r="89" spans="1:12" ht="53.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" s="62" t="s">
+        <v>184</v>
+      </c>
       <c r="C89" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D89" s="26">
         <v>2</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F89" s="26">
         <v>2</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H89" s="26">
         <v>1</v>
@@ -4638,31 +4885,31 @@
       <c r="K89" s="28">
         <v>0</v>
       </c>
-      <c r="L89" s="48" t="s">
+      <c r="L89" s="47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" s="26" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="B90" s="26" t="s">
+      <c r="D90" s="26">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F90" s="26">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="C90" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="D90" s="26">
-        <v>1</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F90" s="26">
-        <v>1</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="H90" s="26">
         <v>2</v>
@@ -4674,29 +4921,29 @@
       <c r="K90" s="28">
         <v>0</v>
       </c>
-      <c r="L90" s="57"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="62" t="s">
-        <v>179</v>
+      <c r="L90" s="56"/>
+    </row>
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="61" t="s">
+        <v>177</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C91" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="26">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" s="26">
+        <v>1</v>
+      </c>
+      <c r="G91" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="D91" s="26">
-        <v>1</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F91" s="26">
-        <v>1</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="H91" s="26">
         <v>1</v>
@@ -4708,23 +4955,23 @@
       <c r="K91" s="28">
         <v>0</v>
       </c>
-      <c r="L91" s="48"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="62" t="s">
-        <v>179</v>
+      <c r="L91" s="47"/>
+    </row>
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="61" t="s">
+        <v>177</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D92" s="26">
         <v>1</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F92" s="26">
         <v>1</v>
@@ -4742,29 +4989,29 @@
       <c r="K92" s="28">
         <v>0</v>
       </c>
-      <c r="L92" s="48"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="62" t="s">
-        <v>179</v>
+      <c r="L92" s="47"/>
+    </row>
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="61" t="s">
+        <v>177</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D93" s="26">
         <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F93" s="26">
         <v>2</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H93" s="26">
         <v>1</v>
@@ -4776,759 +5023,1719 @@
       <c r="K93" s="28">
         <v>0</v>
       </c>
-      <c r="L93" s="48"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="B94" s="65"/>
-      <c r="C94" s="66" t="s">
-        <v>200</v>
-      </c>
-      <c r="D94" s="59"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="59"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="59"/>
+      <c r="L93" s="47"/>
+    </row>
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" s="64"/>
+      <c r="C94" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="D94" s="58"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="58"/>
       <c r="I94" s="41"/>
       <c r="J94" s="28"/>
       <c r="K94" s="28"/>
-      <c r="L94" s="48"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="B95" s="59"/>
-      <c r="C95" s="67" t="s">
-        <v>199</v>
-      </c>
-      <c r="D95" s="59"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="59"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="59"/>
+      <c r="L94" s="47"/>
+    </row>
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B95" s="58"/>
+      <c r="C95" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" s="58"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="58"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="58"/>
       <c r="I95" s="41"/>
       <c r="J95" s="28"/>
       <c r="K95" s="28"/>
-      <c r="L95" s="48"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="B96" s="59"/>
-      <c r="C96" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="D96" s="59"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="59"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="59"/>
+      <c r="L95" s="47"/>
+    </row>
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B96" s="58"/>
+      <c r="C96" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="D96" s="58"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="58"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="58"/>
       <c r="I96" s="41"/>
       <c r="J96" s="28"/>
       <c r="K96" s="28"/>
-      <c r="L96" s="48"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="B97" s="59"/>
-      <c r="C97" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="D97" s="59"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="59"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="59"/>
+      <c r="L96" s="47"/>
+    </row>
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="66" t="s">
+        <v>196</v>
+      </c>
+      <c r="B97" s="58"/>
+      <c r="C97" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" s="58"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="58"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="58"/>
       <c r="I97" s="41"/>
       <c r="J97" s="28"/>
       <c r="K97" s="28"/>
-      <c r="L97" s="48"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L97" s="47"/>
+    </row>
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="D98" s="59"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="59"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="59"/>
+      <c r="B98" s="58"/>
+      <c r="C98" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="26"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="26"/>
       <c r="I98" s="41"/>
       <c r="J98" s="28"/>
       <c r="K98" s="28"/>
-      <c r="L98" s="48"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="68" t="s">
+      <c r="L98" s="47"/>
+    </row>
+    <row r="99" spans="1:12" s="75" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" s="70"/>
+      <c r="C99" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="D99" s="70"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="70"/>
+      <c r="I99" s="72"/>
+      <c r="J99" s="73"/>
+      <c r="K99" s="73"/>
+      <c r="L99" s="74"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B100" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="B99" s="59"/>
-      <c r="C99" s="69" t="s">
+      <c r="C100" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D100" s="26">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F100" s="26">
+        <v>1</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="26"/>
-      <c r="I99" s="41"/>
-      <c r="J99" s="28"/>
-      <c r="K99" s="28"/>
-      <c r="L99" s="48"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="26"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="26"/>
+      <c r="H100" s="26">
+        <v>1</v>
+      </c>
       <c r="I100" s="41"/>
-      <c r="J100" s="28"/>
-      <c r="K100" s="28"/>
-      <c r="L100" s="48"/>
+      <c r="J100" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K100" s="28">
+        <v>30</v>
+      </c>
+      <c r="L100" s="47"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="26"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="26"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="26"/>
+      <c r="A101" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D101" s="26">
+        <v>1</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F101" s="26">
+        <v>1</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H101" s="26">
+        <v>1</v>
+      </c>
       <c r="I101" s="41"/>
-      <c r="J101" s="28"/>
-      <c r="K101" s="28"/>
-      <c r="L101" s="48"/>
+      <c r="J101" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K101" s="28">
+        <v>30</v>
+      </c>
+      <c r="L101" s="47"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="26"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="26"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="26"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="26"/>
+      <c r="A102" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D102" s="26">
+        <v>1</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F102" s="26">
+        <v>1</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H102" s="26">
+        <v>1</v>
+      </c>
       <c r="I102" s="41"/>
-      <c r="J102" s="28"/>
-      <c r="K102" s="28"/>
-      <c r="L102" s="48"/>
+      <c r="J102" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K102" s="28">
+        <v>100</v>
+      </c>
+      <c r="L102" s="47"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="26"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
-      <c r="D103" s="26"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="26"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="26"/>
+      <c r="A103" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" s="26">
+        <v>1</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F103" s="26">
+        <v>1</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H103" s="26">
+        <v>1</v>
+      </c>
       <c r="I103" s="41"/>
-      <c r="J103" s="28"/>
-      <c r="K103" s="28"/>
-      <c r="L103" s="48"/>
+      <c r="J103" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K103" s="28">
+        <v>100</v>
+      </c>
+      <c r="L103" s="47"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="26"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
-      <c r="D104" s="26"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="26"/>
+      <c r="A104" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C104" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D104" s="26">
+        <v>3</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F104" s="26">
+        <v>1</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H104" s="26">
+        <v>1</v>
+      </c>
       <c r="I104" s="41"/>
-      <c r="J104" s="28"/>
-      <c r="K104" s="28"/>
-      <c r="L104" s="48"/>
+      <c r="J104" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K104" s="28">
+        <v>100</v>
+      </c>
+      <c r="L104" s="47" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="26"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="26"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="26"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="26"/>
+      <c r="A105" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C105" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D105" s="26">
+        <v>3</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F105" s="26">
+        <v>1</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H105" s="26">
+        <v>1</v>
+      </c>
       <c r="I105" s="41"/>
-      <c r="J105" s="28"/>
-      <c r="K105" s="28"/>
-      <c r="L105" s="48"/>
+      <c r="J105" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K105" s="28">
+        <v>100</v>
+      </c>
+      <c r="L105" s="47" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="26"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
-      <c r="D106" s="26"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="26"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="26"/>
+      <c r="A106" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C106" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D106" s="26">
+        <v>3</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F106" s="26">
+        <v>1</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H106" s="26">
+        <v>1</v>
+      </c>
       <c r="I106" s="41"/>
-      <c r="J106" s="28"/>
-      <c r="K106" s="28"/>
-      <c r="L106" s="48"/>
+      <c r="J106" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K106" s="28">
+        <v>100</v>
+      </c>
+      <c r="L106" s="47" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="26"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="26"/>
+      <c r="A107" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C107" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D107" s="26">
+        <v>1</v>
+      </c>
+      <c r="E107" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F107" s="26">
+        <f>4*9</f>
+        <v>36</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H107" s="26">
+        <v>1</v>
+      </c>
       <c r="I107" s="41"/>
-      <c r="J107" s="28"/>
-      <c r="K107" s="28"/>
-      <c r="L107" s="48"/>
+      <c r="J107" s="28">
+        <v>1</v>
+      </c>
+      <c r="K107" s="28">
+        <v>20</v>
+      </c>
+      <c r="L107" s="47"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="26"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="26"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="26"/>
+      <c r="A108" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C108" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D108" s="26">
+        <v>1</v>
+      </c>
+      <c r="E108" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="F108" s="26">
+        <f t="shared" ref="F108:F109" si="0">4*9</f>
+        <v>36</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H108" s="26">
+        <v>1</v>
+      </c>
       <c r="I108" s="41"/>
-      <c r="J108" s="28"/>
-      <c r="K108" s="28"/>
-      <c r="L108" s="48"/>
+      <c r="J108" s="28">
+        <v>1</v>
+      </c>
+      <c r="K108" s="28">
+        <v>20</v>
+      </c>
+      <c r="L108" s="47"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="26"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
-      <c r="D109" s="26"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="26"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="26"/>
+      <c r="A109" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D109" s="26">
+        <v>1</v>
+      </c>
+      <c r="E109" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="F109" s="26">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H109" s="26">
+        <v>1</v>
+      </c>
       <c r="I109" s="41"/>
-      <c r="J109" s="28"/>
-      <c r="K109" s="28"/>
-      <c r="L109" s="48"/>
+      <c r="J109" s="28">
+        <v>1</v>
+      </c>
+      <c r="K109" s="28">
+        <v>20</v>
+      </c>
+      <c r="L109" s="47"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="26"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
-      <c r="D110" s="26"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="26"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="26"/>
+      <c r="A110" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C110" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D110" s="26">
+        <v>2</v>
+      </c>
+      <c r="E110" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F110" s="26">
+        <f>5*9</f>
+        <v>45</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H110" s="26">
+        <v>1</v>
+      </c>
       <c r="I110" s="41"/>
-      <c r="J110" s="28"/>
-      <c r="K110" s="28"/>
-      <c r="L110" s="48"/>
+      <c r="J110" s="28">
+        <v>1</v>
+      </c>
+      <c r="K110" s="28">
+        <v>50</v>
+      </c>
+      <c r="L110" s="47"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="26"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="26"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="26"/>
+      <c r="A111" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C111" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D111" s="27">
+        <v>2</v>
+      </c>
+      <c r="E111" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="F111" s="26">
+        <f>5*9</f>
+        <v>45</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H111" s="26">
+        <v>1</v>
+      </c>
       <c r="I111" s="41"/>
-      <c r="J111" s="28"/>
-      <c r="K111" s="28"/>
-      <c r="L111" s="48"/>
+      <c r="J111" s="28">
+        <v>1</v>
+      </c>
+      <c r="K111" s="28">
+        <v>50</v>
+      </c>
+      <c r="L111" s="47"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="26"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="26"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="26"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="26"/>
+      <c r="A112" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C112" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D112" s="27">
+        <v>2</v>
+      </c>
+      <c r="E112" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="F112" s="26">
+        <f>5*9</f>
+        <v>45</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H112" s="26">
+        <v>1</v>
+      </c>
       <c r="I112" s="41"/>
-      <c r="J112" s="28"/>
-      <c r="K112" s="28"/>
-      <c r="L112" s="48"/>
+      <c r="J112" s="28">
+        <v>1</v>
+      </c>
+      <c r="K112" s="28">
+        <v>50</v>
+      </c>
+      <c r="L112" s="47"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="26"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
-      <c r="D113" s="26"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="26"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="26"/>
+      <c r="A113" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C113" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D113" s="27">
+        <v>3</v>
+      </c>
+      <c r="E113" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F113" s="26">
+        <f>7*9</f>
+        <v>63</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H113" s="26">
+        <v>1</v>
+      </c>
       <c r="I113" s="41"/>
-      <c r="J113" s="28"/>
-      <c r="K113" s="28"/>
-      <c r="L113" s="48"/>
+      <c r="J113" s="28">
+        <v>1</v>
+      </c>
+      <c r="K113" s="28">
+        <v>5</v>
+      </c>
+      <c r="L113" s="47"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="26"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="26"/>
-      <c r="D114" s="26"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="26"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="26"/>
+      <c r="A114" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C114" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D114" s="26">
+        <v>3</v>
+      </c>
+      <c r="E114" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="F114" s="26">
+        <f t="shared" ref="F114:F115" si="1">7*9</f>
+        <v>63</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H114" s="26">
+        <v>1</v>
+      </c>
       <c r="I114" s="41"/>
-      <c r="J114" s="28"/>
-      <c r="K114" s="28"/>
-      <c r="L114" s="48"/>
+      <c r="J114" s="28">
+        <v>1</v>
+      </c>
+      <c r="K114" s="28">
+        <v>5</v>
+      </c>
+      <c r="L114" s="47"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" s="26"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="26"/>
+      <c r="A115" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D115" s="26">
+        <v>3</v>
+      </c>
+      <c r="E115" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="F115" s="26">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H115" s="26">
+        <v>1</v>
+      </c>
       <c r="I115" s="41"/>
-      <c r="J115" s="28"/>
-      <c r="K115" s="28"/>
-      <c r="L115" s="48"/>
+      <c r="J115" s="28">
+        <v>1</v>
+      </c>
+      <c r="K115" s="28">
+        <v>5</v>
+      </c>
+      <c r="L115" s="47"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" s="26"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="26"/>
-      <c r="D116" s="26"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="26"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="26"/>
+      <c r="A116" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D116" s="27">
+        <v>4</v>
+      </c>
+      <c r="E116" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F116" s="26">
+        <f t="shared" ref="F116:F118" si="2">8*9</f>
+        <v>72</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H116" s="26">
+        <v>1</v>
+      </c>
       <c r="I116" s="41"/>
-      <c r="J116" s="28"/>
-      <c r="K116" s="28"/>
-      <c r="L116" s="48"/>
+      <c r="J116" s="28">
+        <v>1</v>
+      </c>
+      <c r="K116" s="28">
+        <v>5</v>
+      </c>
+      <c r="L116" s="47"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="26"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="26"/>
-      <c r="D117" s="26"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="26"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="26"/>
+      <c r="A117" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D117" s="26">
+        <v>4</v>
+      </c>
+      <c r="E117" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="F117" s="26">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H117" s="26">
+        <v>1</v>
+      </c>
       <c r="I117" s="41"/>
-      <c r="J117" s="28"/>
-      <c r="K117" s="28"/>
-      <c r="L117" s="48"/>
+      <c r="J117" s="28">
+        <v>1</v>
+      </c>
+      <c r="K117" s="28">
+        <v>5</v>
+      </c>
+      <c r="L117" s="47"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="26"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26"/>
-      <c r="D118" s="26"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="26"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="26"/>
+      <c r="A118" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C118" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D118" s="26">
+        <v>4</v>
+      </c>
+      <c r="E118" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="F118" s="26">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H118" s="26">
+        <v>1</v>
+      </c>
       <c r="I118" s="41"/>
-      <c r="J118" s="28"/>
-      <c r="K118" s="28"/>
-      <c r="L118" s="48"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="26"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="26"/>
-      <c r="D119" s="26"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="26"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="26"/>
-      <c r="I119" s="41"/>
-      <c r="J119" s="28"/>
-      <c r="K119" s="28"/>
-      <c r="L119" s="48"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="26"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="26"/>
-      <c r="D120" s="26"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="26"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="26"/>
-      <c r="I120" s="41"/>
-      <c r="J120" s="28"/>
-      <c r="K120" s="28"/>
-      <c r="L120" s="48"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" s="26"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="26"/>
-      <c r="D121" s="26"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="26"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="26"/>
-      <c r="I121" s="41"/>
-      <c r="J121" s="28"/>
-      <c r="K121" s="28"/>
-      <c r="L121" s="48"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="26"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="26"/>
-      <c r="D122" s="26"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="26"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="26"/>
-      <c r="I122" s="41"/>
-      <c r="J122" s="28"/>
-      <c r="K122" s="28"/>
-      <c r="L122" s="48"/>
+      <c r="J118" s="28">
+        <v>1</v>
+      </c>
+      <c r="K118" s="28">
+        <v>5</v>
+      </c>
+      <c r="L118" s="47"/>
+    </row>
+    <row r="119" spans="1:12" s="86" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A119" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B119" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C119" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D119" s="80">
+        <v>5</v>
+      </c>
+      <c r="E119" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F119" s="80">
+        <v>1</v>
+      </c>
+      <c r="G119" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="H119" s="80">
+        <v>1</v>
+      </c>
+      <c r="I119" s="82"/>
+      <c r="J119" s="83">
+        <v>1</v>
+      </c>
+      <c r="K119" s="83">
+        <v>100</v>
+      </c>
+      <c r="L119" s="84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" s="86" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A120" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B120" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C120" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D120" s="80">
+        <v>5</v>
+      </c>
+      <c r="E120" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F120" s="80">
+        <v>1</v>
+      </c>
+      <c r="G120" s="81" t="s">
+        <v>245</v>
+      </c>
+      <c r="H120" s="80">
+        <v>1</v>
+      </c>
+      <c r="I120" s="82"/>
+      <c r="J120" s="83">
+        <v>1</v>
+      </c>
+      <c r="K120" s="83">
+        <v>100</v>
+      </c>
+      <c r="L120" s="84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" s="86" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A121" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B121" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C121" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D121" s="80">
+        <v>5</v>
+      </c>
+      <c r="E121" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F121" s="80">
+        <v>1</v>
+      </c>
+      <c r="G121" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="H121" s="80">
+        <v>1</v>
+      </c>
+      <c r="I121" s="82"/>
+      <c r="J121" s="83">
+        <v>1</v>
+      </c>
+      <c r="K121" s="83">
+        <v>100</v>
+      </c>
+      <c r="L121" s="84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" s="86" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A122" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B122" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C122" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D122" s="80">
+        <v>5</v>
+      </c>
+      <c r="E122" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F122" s="80">
+        <v>1</v>
+      </c>
+      <c r="G122" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="H122" s="80">
+        <v>1</v>
+      </c>
+      <c r="I122" s="82"/>
+      <c r="J122" s="83">
+        <v>1</v>
+      </c>
+      <c r="K122" s="83">
+        <v>100</v>
+      </c>
+      <c r="L122" s="84" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="26"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
-      <c r="D123" s="26"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="26"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="26"/>
+      <c r="A123" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B123" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="C123" s="80" t="s">
+        <v>222</v>
+      </c>
+      <c r="D123" s="26">
+        <v>1</v>
+      </c>
+      <c r="E123" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="F123" s="26">
+        <v>15</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H123" s="26">
+        <v>1</v>
+      </c>
       <c r="I123" s="41"/>
-      <c r="J123" s="28"/>
-      <c r="K123" s="28"/>
-      <c r="L123" s="48"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="26"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="26"/>
-      <c r="D124" s="26"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="26"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="26"/>
-      <c r="I124" s="41"/>
-      <c r="J124" s="28"/>
-      <c r="K124" s="28"/>
-      <c r="L124" s="48"/>
+      <c r="J123" s="28">
+        <v>20</v>
+      </c>
+      <c r="K123" s="28">
+        <v>10</v>
+      </c>
+      <c r="L123" s="47"/>
+    </row>
+    <row r="124" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A124" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B124" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="C124" s="80" t="s">
+        <v>222</v>
+      </c>
+      <c r="D124" s="85">
+        <v>5</v>
+      </c>
+      <c r="E124" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F124" s="80">
+        <v>1</v>
+      </c>
+      <c r="G124" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="H124" s="80">
+        <v>1</v>
+      </c>
+      <c r="I124" s="82"/>
+      <c r="J124" s="83">
+        <v>3</v>
+      </c>
+      <c r="K124" s="83">
+        <v>10</v>
+      </c>
+      <c r="L124" s="84" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="26"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="26"/>
-      <c r="D125" s="26"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="26"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="26"/>
-      <c r="I125" s="41"/>
-      <c r="J125" s="28"/>
-      <c r="K125" s="28"/>
-      <c r="L125" s="48"/>
+      <c r="A125" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C125" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D125" s="85">
+        <v>1</v>
+      </c>
+      <c r="E125" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="F125" s="80">
+        <v>27</v>
+      </c>
+      <c r="G125" s="81" t="s">
+        <v>240</v>
+      </c>
+      <c r="H125" s="80">
+        <v>1</v>
+      </c>
+      <c r="I125" s="82"/>
+      <c r="J125" s="83">
+        <v>3</v>
+      </c>
+      <c r="K125" s="83">
+        <v>10</v>
+      </c>
+      <c r="L125" s="84"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="26"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="26"/>
-      <c r="D126" s="26"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="26"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="26"/>
-      <c r="I126" s="41"/>
-      <c r="J126" s="28"/>
-      <c r="K126" s="28"/>
-      <c r="L126" s="48"/>
+      <c r="A126" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B126" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C126" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D126" s="85">
+        <v>1</v>
+      </c>
+      <c r="E126" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="F126" s="80">
+        <v>27</v>
+      </c>
+      <c r="G126" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="H126" s="80">
+        <v>1</v>
+      </c>
+      <c r="I126" s="82"/>
+      <c r="J126" s="83">
+        <v>3</v>
+      </c>
+      <c r="K126" s="83">
+        <v>10</v>
+      </c>
+      <c r="L126" s="84"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="26"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="26"/>
-      <c r="D127" s="26"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="26"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="26"/>
-      <c r="I127" s="41"/>
-      <c r="J127" s="28"/>
-      <c r="K127" s="28"/>
-      <c r="L127" s="48"/>
+      <c r="A127" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B127" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C127" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D127" s="85">
+        <v>2</v>
+      </c>
+      <c r="E127" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="F127" s="80">
+        <v>27</v>
+      </c>
+      <c r="G127" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="H127" s="80">
+        <v>1</v>
+      </c>
+      <c r="I127" s="82"/>
+      <c r="J127" s="83">
+        <v>3</v>
+      </c>
+      <c r="K127" s="83">
+        <v>10</v>
+      </c>
+      <c r="L127" s="84"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="26"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26"/>
-      <c r="D128" s="26"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="5"/>
-      <c r="H128" s="26"/>
-      <c r="I128" s="41"/>
-      <c r="J128" s="28"/>
-      <c r="K128" s="28"/>
-      <c r="L128" s="48"/>
+      <c r="A128" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B128" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C128" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D128" s="85">
+        <v>2</v>
+      </c>
+      <c r="E128" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="F128" s="80">
+        <v>27</v>
+      </c>
+      <c r="G128" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="H128" s="80">
+        <v>1</v>
+      </c>
+      <c r="I128" s="82"/>
+      <c r="J128" s="83">
+        <v>3</v>
+      </c>
+      <c r="K128" s="83">
+        <v>10</v>
+      </c>
+      <c r="L128" s="84"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="26"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="26"/>
-      <c r="D129" s="26"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="26"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="26"/>
-      <c r="I129" s="41"/>
-      <c r="J129" s="28"/>
-      <c r="K129" s="28"/>
-      <c r="L129" s="48"/>
+      <c r="A129" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B129" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C129" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D129" s="85">
+        <v>3</v>
+      </c>
+      <c r="E129" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="F129" s="80">
+        <v>27</v>
+      </c>
+      <c r="G129" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="H129" s="80">
+        <v>1</v>
+      </c>
+      <c r="I129" s="82"/>
+      <c r="J129" s="83">
+        <v>3</v>
+      </c>
+      <c r="K129" s="83">
+        <v>10</v>
+      </c>
+      <c r="L129" s="84"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="26"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="26"/>
-      <c r="D130" s="26"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="26"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="26"/>
-      <c r="I130" s="41"/>
-      <c r="J130" s="28"/>
-      <c r="K130" s="28"/>
-      <c r="L130" s="48"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="26"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="26"/>
-      <c r="D131" s="26"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="26"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="26"/>
-      <c r="I131" s="41"/>
-      <c r="J131" s="28"/>
-      <c r="K131" s="28"/>
-      <c r="L131" s="48"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="26"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="5"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="41"/>
-      <c r="J132" s="28"/>
-      <c r="K132" s="28"/>
-      <c r="L132" s="48"/>
+      <c r="A130" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B130" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C130" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D130" s="85">
+        <v>3</v>
+      </c>
+      <c r="E130" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="F130" s="80">
+        <v>27</v>
+      </c>
+      <c r="G130" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="H130" s="80">
+        <v>1</v>
+      </c>
+      <c r="I130" s="82"/>
+      <c r="J130" s="83">
+        <v>3</v>
+      </c>
+      <c r="K130" s="83">
+        <v>10</v>
+      </c>
+      <c r="L130" s="84"/>
+    </row>
+    <row r="131" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A131" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B131" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C131" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D131" s="85">
+        <v>5</v>
+      </c>
+      <c r="E131" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F131" s="80">
+        <v>1</v>
+      </c>
+      <c r="G131" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="H131" s="80">
+        <v>1</v>
+      </c>
+      <c r="I131" s="82"/>
+      <c r="J131" s="83">
+        <v>1</v>
+      </c>
+      <c r="K131" s="83">
+        <v>100</v>
+      </c>
+      <c r="L131" s="84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A132" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="B132" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C132" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D132" s="85">
+        <v>5</v>
+      </c>
+      <c r="E132" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="F132" s="80">
+        <v>1</v>
+      </c>
+      <c r="G132" s="81" t="s">
+        <v>249</v>
+      </c>
+      <c r="H132" s="80">
+        <v>1</v>
+      </c>
+      <c r="I132" s="82"/>
+      <c r="J132" s="83">
+        <v>1</v>
+      </c>
+      <c r="K132" s="83">
+        <v>100</v>
+      </c>
+      <c r="L132" s="84" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" s="26"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="26"/>
-      <c r="D133" s="26"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="26"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="26"/>
+      <c r="A133" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D133" s="26">
+        <v>1</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F133" s="26">
+        <v>3</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H133" s="26">
+        <v>1</v>
+      </c>
       <c r="I133" s="41"/>
-      <c r="J133" s="28"/>
-      <c r="K133" s="28"/>
-      <c r="L133" s="48"/>
+      <c r="J133" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K133" s="28">
+        <v>2</v>
+      </c>
+      <c r="L133" s="47"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" s="26"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="26"/>
-      <c r="D134" s="26"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="26"/>
-      <c r="G134" s="5"/>
-      <c r="H134" s="26"/>
+      <c r="A134" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D134" s="26">
+        <v>2</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F134" s="26">
+        <v>5</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H134" s="26">
+        <v>1</v>
+      </c>
       <c r="I134" s="41"/>
-      <c r="J134" s="28"/>
-      <c r="K134" s="28"/>
-      <c r="L134" s="48"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="26"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="26"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="26"/>
+      <c r="J134" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K134" s="28">
+        <v>10</v>
+      </c>
+      <c r="L134" s="47"/>
+    </row>
+    <row r="135" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A135" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C135" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D135" s="26">
+        <v>3</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F135" s="26">
+        <v>1</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H135" s="26">
+        <v>1</v>
+      </c>
       <c r="I135" s="41"/>
-      <c r="J135" s="28"/>
-      <c r="K135" s="28"/>
-      <c r="L135" s="48"/>
+      <c r="J135" s="28">
+        <v>1</v>
+      </c>
+      <c r="K135" s="28">
+        <v>100</v>
+      </c>
+      <c r="L135" s="47" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="26"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="26"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="5"/>
-      <c r="H136" s="26"/>
+      <c r="A136" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C136" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D136" s="26">
+        <v>1</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F136" s="26">
+        <v>3</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H136" s="26">
+        <v>1</v>
+      </c>
       <c r="I136" s="41"/>
-      <c r="J136" s="28"/>
-      <c r="K136" s="28"/>
-      <c r="L136" s="48"/>
+      <c r="J136" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K136" s="28">
+        <v>2</v>
+      </c>
+      <c r="L136" s="47"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="26"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="26"/>
-      <c r="D137" s="26"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="26"/>
-      <c r="G137" s="5"/>
-      <c r="H137" s="26"/>
+      <c r="A137" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C137" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D137" s="26">
+        <v>2</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F137" s="26">
+        <v>1</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H137" s="26">
+        <v>1</v>
+      </c>
       <c r="I137" s="41"/>
-      <c r="J137" s="28"/>
-      <c r="K137" s="28"/>
-      <c r="L137" s="48"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="26"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
-      <c r="D138" s="26"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="26"/>
-      <c r="G138" s="5"/>
-      <c r="H138" s="26"/>
+      <c r="J137" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K137" s="28">
+        <v>100</v>
+      </c>
+      <c r="L137" s="47"/>
+    </row>
+    <row r="138" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A138" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C138" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D138" s="26">
+        <v>3</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F138" s="26">
+        <v>1</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H138" s="26">
+        <v>1</v>
+      </c>
       <c r="I138" s="41"/>
-      <c r="J138" s="28"/>
-      <c r="K138" s="28"/>
-      <c r="L138" s="48"/>
+      <c r="J138" s="28">
+        <v>1</v>
+      </c>
+      <c r="K138" s="28">
+        <v>100</v>
+      </c>
+      <c r="L138" s="47" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" s="26"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
-      <c r="D139" s="26"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="26"/>
-      <c r="G139" s="5"/>
-      <c r="H139" s="26"/>
+      <c r="A139" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C139" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D139" s="26">
+        <v>1</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F139" s="26">
+        <v>3</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H139" s="26">
+        <v>1</v>
+      </c>
       <c r="I139" s="41"/>
-      <c r="J139" s="28"/>
-      <c r="K139" s="28"/>
-      <c r="L139" s="48"/>
+      <c r="J139" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K139" s="28">
+        <v>2</v>
+      </c>
+      <c r="L139" s="47"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" s="26"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
-      <c r="D140" s="26"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="26"/>
-      <c r="G140" s="5"/>
-      <c r="H140" s="26"/>
+      <c r="A140" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C140" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D140" s="26">
+        <v>2</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F140" s="26">
+        <v>1</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H140" s="26">
+        <v>2</v>
+      </c>
       <c r="I140" s="41"/>
-      <c r="J140" s="28"/>
-      <c r="K140" s="28"/>
-      <c r="L140" s="48"/>
+      <c r="J140" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K140" s="28">
+        <v>15</v>
+      </c>
+      <c r="L140" s="47"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A141" s="26"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="26"/>
-      <c r="D141" s="26"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="26"/>
-      <c r="G141" s="5"/>
-      <c r="H141" s="26"/>
+      <c r="A141" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B141" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C141" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D141" s="26">
+        <v>2</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141" s="26">
+        <v>1</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H141" s="26">
+        <v>2</v>
+      </c>
       <c r="I141" s="41"/>
-      <c r="J141" s="28"/>
-      <c r="K141" s="28"/>
-      <c r="L141" s="48"/>
+      <c r="J141" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K141" s="28">
+        <v>15</v>
+      </c>
+      <c r="L141" s="47"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" s="26"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="26"/>
-      <c r="D142" s="26"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="26"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="26"/>
+      <c r="A142" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C142" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D142" s="26">
+        <v>2</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F142" s="26">
+        <v>1</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H142" s="26">
+        <v>2</v>
+      </c>
       <c r="I142" s="41"/>
-      <c r="J142" s="28"/>
-      <c r="K142" s="28"/>
-      <c r="L142" s="48"/>
+      <c r="J142" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K142" s="28">
+        <v>15</v>
+      </c>
+      <c r="L142" s="47"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" s="26"/>
-      <c r="B143" s="26"/>
-      <c r="C143" s="26"/>
-      <c r="D143" s="26"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="26"/>
-      <c r="G143" s="5"/>
-      <c r="H143" s="26"/>
+      <c r="A143" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C143" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D143" s="26">
+        <v>1</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F143" s="26">
+        <v>3</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H143" s="26">
+        <v>1</v>
+      </c>
       <c r="I143" s="41"/>
-      <c r="J143" s="28"/>
-      <c r="K143" s="28"/>
-      <c r="L143" s="48"/>
+      <c r="J143" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K143" s="28">
+        <v>2</v>
+      </c>
+      <c r="L143" s="47"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" s="26"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="26"/>
-      <c r="D144" s="26"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="26"/>
-      <c r="G144" s="5"/>
-      <c r="H144" s="26"/>
+      <c r="A144" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B144" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C144" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D144" s="26">
+        <v>2</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F144" s="26">
+        <v>1</v>
+      </c>
+      <c r="G144" s="89" t="s">
+        <v>264</v>
+      </c>
+      <c r="H144" s="26">
+        <v>1</v>
+      </c>
       <c r="I144" s="41"/>
-      <c r="J144" s="28"/>
-      <c r="K144" s="28"/>
-      <c r="L144" s="48"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" s="26"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="26"/>
-      <c r="D145" s="26"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="26"/>
-      <c r="G145" s="5"/>
-      <c r="H145" s="26"/>
+      <c r="J144" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K144" s="28">
+        <v>10</v>
+      </c>
+      <c r="L144" s="47" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A145" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C145" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D145" s="26">
+        <v>3</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F145" s="26">
+        <v>1</v>
+      </c>
+      <c r="G145" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="H145" s="26">
+        <v>1</v>
+      </c>
       <c r="I145" s="41"/>
-      <c r="J145" s="28"/>
-      <c r="K145" s="28"/>
-      <c r="L145" s="48"/>
+      <c r="J145" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K145" s="28">
+        <v>10</v>
+      </c>
+      <c r="L145" s="47" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="26"/>
@@ -5542,7 +6749,7 @@
       <c r="I146" s="41"/>
       <c r="J146" s="28"/>
       <c r="K146" s="28"/>
-      <c r="L146" s="48"/>
+      <c r="L146" s="47"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="26"/>
@@ -5556,7 +6763,7 @@
       <c r="I147" s="41"/>
       <c r="J147" s="28"/>
       <c r="K147" s="28"/>
-      <c r="L147" s="48"/>
+      <c r="L147" s="47"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="26"/>
@@ -5570,7 +6777,7 @@
       <c r="I148" s="41"/>
       <c r="J148" s="28"/>
       <c r="K148" s="28"/>
-      <c r="L148" s="48"/>
+      <c r="L148" s="47"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="26"/>
@@ -5584,7 +6791,7 @@
       <c r="I149" s="41"/>
       <c r="J149" s="28"/>
       <c r="K149" s="28"/>
-      <c r="L149" s="48"/>
+      <c r="L149" s="47"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="26"/>
@@ -5598,7 +6805,7 @@
       <c r="I150" s="41"/>
       <c r="J150" s="28"/>
       <c r="K150" s="28"/>
-      <c r="L150" s="48"/>
+      <c r="L150" s="47"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="26"/>
@@ -5612,7 +6819,7 @@
       <c r="I151" s="41"/>
       <c r="J151" s="28"/>
       <c r="K151" s="28"/>
-      <c r="L151" s="48"/>
+      <c r="L151" s="47"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="26"/>
@@ -5626,7 +6833,7 @@
       <c r="I152" s="41"/>
       <c r="J152" s="28"/>
       <c r="K152" s="28"/>
-      <c r="L152" s="48"/>
+      <c r="L152" s="47"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="26"/>
@@ -5640,7 +6847,7 @@
       <c r="I153" s="41"/>
       <c r="J153" s="28"/>
       <c r="K153" s="28"/>
-      <c r="L153" s="48"/>
+      <c r="L153" s="47"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="26"/>
@@ -5654,7 +6861,7 @@
       <c r="I154" s="41"/>
       <c r="J154" s="28"/>
       <c r="K154" s="28"/>
-      <c r="L154" s="48"/>
+      <c r="L154" s="47"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="26"/>
@@ -5668,7 +6875,7 @@
       <c r="I155" s="41"/>
       <c r="J155" s="28"/>
       <c r="K155" s="28"/>
-      <c r="L155" s="48"/>
+      <c r="L155" s="47"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="26"/>
@@ -5682,7 +6889,7 @@
       <c r="I156" s="41"/>
       <c r="J156" s="28"/>
       <c r="K156" s="28"/>
-      <c r="L156" s="48"/>
+      <c r="L156" s="47"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="26"/>
@@ -5696,7 +6903,7 @@
       <c r="I157" s="41"/>
       <c r="J157" s="28"/>
       <c r="K157" s="28"/>
-      <c r="L157" s="48"/>
+      <c r="L157" s="47"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="26"/>
@@ -5710,7 +6917,7 @@
       <c r="I158" s="41"/>
       <c r="J158" s="28"/>
       <c r="K158" s="28"/>
-      <c r="L158" s="48"/>
+      <c r="L158" s="47"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="26"/>
@@ -5724,7 +6931,7 @@
       <c r="I159" s="41"/>
       <c r="J159" s="28"/>
       <c r="K159" s="28"/>
-      <c r="L159" s="48"/>
+      <c r="L159" s="47"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="26"/>
@@ -5738,7 +6945,7 @@
       <c r="I160" s="41"/>
       <c r="J160" s="28"/>
       <c r="K160" s="28"/>
-      <c r="L160" s="48"/>
+      <c r="L160" s="47"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="26"/>
@@ -5752,7 +6959,7 @@
       <c r="I161" s="41"/>
       <c r="J161" s="28"/>
       <c r="K161" s="28"/>
-      <c r="L161" s="48"/>
+      <c r="L161" s="47"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="26"/>
@@ -5766,7 +6973,7 @@
       <c r="I162" s="41"/>
       <c r="J162" s="28"/>
       <c r="K162" s="28"/>
-      <c r="L162" s="48"/>
+      <c r="L162" s="47"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="26"/>
@@ -5780,7 +6987,7 @@
       <c r="I163" s="41"/>
       <c r="J163" s="28"/>
       <c r="K163" s="28"/>
-      <c r="L163" s="48"/>
+      <c r="L163" s="47"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="26"/>
@@ -5794,7 +7001,7 @@
       <c r="I164" s="41"/>
       <c r="J164" s="28"/>
       <c r="K164" s="28"/>
-      <c r="L164" s="48"/>
+      <c r="L164" s="47"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="26"/>
@@ -5808,7 +7015,7 @@
       <c r="I165" s="41"/>
       <c r="J165" s="28"/>
       <c r="K165" s="28"/>
-      <c r="L165" s="48"/>
+      <c r="L165" s="47"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="26"/>
@@ -5822,7 +7029,7 @@
       <c r="I166" s="41"/>
       <c r="J166" s="28"/>
       <c r="K166" s="28"/>
-      <c r="L166" s="48"/>
+      <c r="L166" s="47"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="26"/>
@@ -5836,7 +7043,7 @@
       <c r="I167" s="41"/>
       <c r="J167" s="28"/>
       <c r="K167" s="28"/>
-      <c r="L167" s="48"/>
+      <c r="L167" s="47"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="26"/>
@@ -5850,7 +7057,7 @@
       <c r="I168" s="41"/>
       <c r="J168" s="28"/>
       <c r="K168" s="28"/>
-      <c r="L168" s="48"/>
+      <c r="L168" s="47"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="26"/>
@@ -5864,7 +7071,7 @@
       <c r="I169" s="41"/>
       <c r="J169" s="28"/>
       <c r="K169" s="28"/>
-      <c r="L169" s="48"/>
+      <c r="L169" s="47"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="26"/>
@@ -5878,7 +7085,7 @@
       <c r="I170" s="41"/>
       <c r="J170" s="28"/>
       <c r="K170" s="28"/>
-      <c r="L170" s="48"/>
+      <c r="L170" s="47"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="26"/>
@@ -5892,7 +7099,7 @@
       <c r="I171" s="41"/>
       <c r="J171" s="28"/>
       <c r="K171" s="28"/>
-      <c r="L171" s="48"/>
+      <c r="L171" s="47"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="26"/>
@@ -5906,7 +7113,7 @@
       <c r="I172" s="41"/>
       <c r="J172" s="28"/>
       <c r="K172" s="28"/>
-      <c r="L172" s="48"/>
+      <c r="L172" s="47"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="26"/>
@@ -5920,7 +7127,7 @@
       <c r="I173" s="41"/>
       <c r="J173" s="28"/>
       <c r="K173" s="28"/>
-      <c r="L173" s="48"/>
+      <c r="L173" s="47"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="26"/>
@@ -5934,7 +7141,7 @@
       <c r="I174" s="41"/>
       <c r="J174" s="28"/>
       <c r="K174" s="28"/>
-      <c r="L174" s="48"/>
+      <c r="L174" s="47"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="26"/>
@@ -5948,7 +7155,7 @@
       <c r="I175" s="41"/>
       <c r="J175" s="28"/>
       <c r="K175" s="28"/>
-      <c r="L175" s="48"/>
+      <c r="L175" s="47"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="26"/>
@@ -5962,7 +7169,7 @@
       <c r="I176" s="41"/>
       <c r="J176" s="28"/>
       <c r="K176" s="28"/>
-      <c r="L176" s="48"/>
+      <c r="L176" s="47"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="26"/>
@@ -5976,7 +7183,7 @@
       <c r="I177" s="41"/>
       <c r="J177" s="28"/>
       <c r="K177" s="28"/>
-      <c r="L177" s="48"/>
+      <c r="L177" s="47"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="26"/>
@@ -5990,7 +7197,7 @@
       <c r="I178" s="41"/>
       <c r="J178" s="28"/>
       <c r="K178" s="28"/>
-      <c r="L178" s="48"/>
+      <c r="L178" s="47"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="26"/>
@@ -6004,7 +7211,7 @@
       <c r="I179" s="41"/>
       <c r="J179" s="28"/>
       <c r="K179" s="28"/>
-      <c r="L179" s="48"/>
+      <c r="L179" s="47"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="26"/>
@@ -6018,7 +7225,7 @@
       <c r="I180" s="41"/>
       <c r="J180" s="28"/>
       <c r="K180" s="28"/>
-      <c r="L180" s="48"/>
+      <c r="L180" s="47"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="26"/>
@@ -6032,7 +7239,7 @@
       <c r="I181" s="41"/>
       <c r="J181" s="28"/>
       <c r="K181" s="28"/>
-      <c r="L181" s="48"/>
+      <c r="L181" s="47"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="26"/>
@@ -6046,7 +7253,7 @@
       <c r="I182" s="41"/>
       <c r="J182" s="28"/>
       <c r="K182" s="28"/>
-      <c r="L182" s="48"/>
+      <c r="L182" s="47"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="26"/>
@@ -6060,7 +7267,7 @@
       <c r="I183" s="41"/>
       <c r="J183" s="28"/>
       <c r="K183" s="28"/>
-      <c r="L183" s="48"/>
+      <c r="L183" s="47"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="26"/>
@@ -6074,7 +7281,7 @@
       <c r="I184" s="41"/>
       <c r="J184" s="28"/>
       <c r="K184" s="28"/>
-      <c r="L184" s="48"/>
+      <c r="L184" s="47"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="26"/>
@@ -6088,7 +7295,7 @@
       <c r="I185" s="41"/>
       <c r="J185" s="28"/>
       <c r="K185" s="28"/>
-      <c r="L185" s="48"/>
+      <c r="L185" s="47"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="26"/>
@@ -6102,7 +7309,7 @@
       <c r="I186" s="41"/>
       <c r="J186" s="28"/>
       <c r="K186" s="28"/>
-      <c r="L186" s="48"/>
+      <c r="L186" s="47"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="26"/>
@@ -6116,7 +7323,7 @@
       <c r="I187" s="41"/>
       <c r="J187" s="28"/>
       <c r="K187" s="28"/>
-      <c r="L187" s="48"/>
+      <c r="L187" s="47"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="26"/>
@@ -6130,7 +7337,7 @@
       <c r="I188" s="41"/>
       <c r="J188" s="28"/>
       <c r="K188" s="28"/>
-      <c r="L188" s="48"/>
+      <c r="L188" s="47"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="26"/>
@@ -6144,7 +7351,7 @@
       <c r="I189" s="41"/>
       <c r="J189" s="28"/>
       <c r="K189" s="28"/>
-      <c r="L189" s="48"/>
+      <c r="L189" s="47"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="26"/>
@@ -6158,7 +7365,7 @@
       <c r="I190" s="41"/>
       <c r="J190" s="28"/>
       <c r="K190" s="28"/>
-      <c r="L190" s="48"/>
+      <c r="L190" s="47"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="26"/>
@@ -6172,7 +7379,7 @@
       <c r="I191" s="41"/>
       <c r="J191" s="28"/>
       <c r="K191" s="28"/>
-      <c r="L191" s="48"/>
+      <c r="L191" s="47"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="26"/>
@@ -6186,7 +7393,7 @@
       <c r="I192" s="41"/>
       <c r="J192" s="28"/>
       <c r="K192" s="28"/>
-      <c r="L192" s="48"/>
+      <c r="L192" s="47"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="26"/>
@@ -6200,7 +7407,7 @@
       <c r="I193" s="41"/>
       <c r="J193" s="28"/>
       <c r="K193" s="28"/>
-      <c r="L193" s="48"/>
+      <c r="L193" s="47"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="26"/>
@@ -6214,7 +7421,7 @@
       <c r="I194" s="41"/>
       <c r="J194" s="28"/>
       <c r="K194" s="28"/>
-      <c r="L194" s="48"/>
+      <c r="L194" s="47"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="26"/>
@@ -6228,7 +7435,7 @@
       <c r="I195" s="41"/>
       <c r="J195" s="28"/>
       <c r="K195" s="28"/>
-      <c r="L195" s="48"/>
+      <c r="L195" s="47"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="26"/>
@@ -6242,7 +7449,7 @@
       <c r="I196" s="41"/>
       <c r="J196" s="28"/>
       <c r="K196" s="28"/>
-      <c r="L196" s="48"/>
+      <c r="L196" s="47"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="26"/>
@@ -6256,7 +7463,7 @@
       <c r="I197" s="41"/>
       <c r="J197" s="28"/>
       <c r="K197" s="28"/>
-      <c r="L197" s="48"/>
+      <c r="L197" s="47"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="26"/>
@@ -6270,7 +7477,7 @@
       <c r="I198" s="41"/>
       <c r="J198" s="28"/>
       <c r="K198" s="28"/>
-      <c r="L198" s="48"/>
+      <c r="L198" s="47"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="26"/>
@@ -6284,7 +7491,7 @@
       <c r="I199" s="41"/>
       <c r="J199" s="28"/>
       <c r="K199" s="28"/>
-      <c r="L199" s="48"/>
+      <c r="L199" s="47"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="26"/>
@@ -6298,7 +7505,7 @@
       <c r="I200" s="41"/>
       <c r="J200" s="28"/>
       <c r="K200" s="28"/>
-      <c r="L200" s="48"/>
+      <c r="L200" s="47"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="26"/>
@@ -6312,7 +7519,7 @@
       <c r="I201" s="41"/>
       <c r="J201" s="28"/>
       <c r="K201" s="28"/>
-      <c r="L201" s="48"/>
+      <c r="L201" s="47"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="26"/>
@@ -6326,7 +7533,7 @@
       <c r="I202" s="41"/>
       <c r="J202" s="28"/>
       <c r="K202" s="28"/>
-      <c r="L202" s="48"/>
+      <c r="L202" s="47"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="26"/>
@@ -6340,7 +7547,7 @@
       <c r="I203" s="41"/>
       <c r="J203" s="28"/>
       <c r="K203" s="28"/>
-      <c r="L203" s="48"/>
+      <c r="L203" s="47"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="26"/>
@@ -6354,7 +7561,7 @@
       <c r="I204" s="41"/>
       <c r="J204" s="28"/>
       <c r="K204" s="28"/>
-      <c r="L204" s="48"/>
+      <c r="L204" s="47"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="26"/>
@@ -6368,7 +7575,7 @@
       <c r="I205" s="41"/>
       <c r="J205" s="28"/>
       <c r="K205" s="28"/>
-      <c r="L205" s="48"/>
+      <c r="L205" s="47"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="26"/>
@@ -6382,7 +7589,7 @@
       <c r="I206" s="41"/>
       <c r="J206" s="28"/>
       <c r="K206" s="28"/>
-      <c r="L206" s="48"/>
+      <c r="L206" s="47"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="26"/>
@@ -6396,7 +7603,7 @@
       <c r="I207" s="41"/>
       <c r="J207" s="28"/>
       <c r="K207" s="28"/>
-      <c r="L207" s="48"/>
+      <c r="L207" s="47"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="26"/>
@@ -6410,7 +7617,7 @@
       <c r="I208" s="41"/>
       <c r="J208" s="28"/>
       <c r="K208" s="28"/>
-      <c r="L208" s="48"/>
+      <c r="L208" s="47"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="26"/>
@@ -6424,7 +7631,7 @@
       <c r="I209" s="41"/>
       <c r="J209" s="28"/>
       <c r="K209" s="28"/>
-      <c r="L209" s="48"/>
+      <c r="L209" s="47"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="26"/>
@@ -6438,7 +7645,7 @@
       <c r="I210" s="41"/>
       <c r="J210" s="28"/>
       <c r="K210" s="28"/>
-      <c r="L210" s="48"/>
+      <c r="L210" s="47"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="26"/>
@@ -6452,7 +7659,7 @@
       <c r="I211" s="41"/>
       <c r="J211" s="28"/>
       <c r="K211" s="28"/>
-      <c r="L211" s="48"/>
+      <c r="L211" s="47"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="26"/>
@@ -6466,7 +7673,7 @@
       <c r="I212" s="41"/>
       <c r="J212" s="28"/>
       <c r="K212" s="28"/>
-      <c r="L212" s="48"/>
+      <c r="L212" s="47"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="26"/>
@@ -6480,7 +7687,7 @@
       <c r="I213" s="41"/>
       <c r="J213" s="28"/>
       <c r="K213" s="28"/>
-      <c r="L213" s="48"/>
+      <c r="L213" s="47"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="26"/>
@@ -6494,7 +7701,7 @@
       <c r="I214" s="41"/>
       <c r="J214" s="28"/>
       <c r="K214" s="28"/>
-      <c r="L214" s="48"/>
+      <c r="L214" s="47"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="26"/>
@@ -6508,7 +7715,7 @@
       <c r="I215" s="41"/>
       <c r="J215" s="28"/>
       <c r="K215" s="28"/>
-      <c r="L215" s="48"/>
+      <c r="L215" s="47"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="26"/>
@@ -6522,7 +7729,7 @@
       <c r="I216" s="41"/>
       <c r="J216" s="28"/>
       <c r="K216" s="28"/>
-      <c r="L216" s="48"/>
+      <c r="L216" s="47"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="26"/>
@@ -6536,7 +7743,7 @@
       <c r="I217" s="41"/>
       <c r="J217" s="28"/>
       <c r="K217" s="28"/>
-      <c r="L217" s="48"/>
+      <c r="L217" s="47"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="26"/>
@@ -6550,7 +7757,7 @@
       <c r="I218" s="41"/>
       <c r="J218" s="28"/>
       <c r="K218" s="28"/>
-      <c r="L218" s="48"/>
+      <c r="L218" s="47"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="26"/>
@@ -6564,7 +7771,7 @@
       <c r="I219" s="41"/>
       <c r="J219" s="28"/>
       <c r="K219" s="28"/>
-      <c r="L219" s="48"/>
+      <c r="L219" s="47"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="26"/>
@@ -6578,7 +7785,7 @@
       <c r="I220" s="41"/>
       <c r="J220" s="28"/>
       <c r="K220" s="28"/>
-      <c r="L220" s="48"/>
+      <c r="L220" s="47"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="26"/>
@@ -6592,7 +7799,7 @@
       <c r="I221" s="41"/>
       <c r="J221" s="28"/>
       <c r="K221" s="28"/>
-      <c r="L221" s="48"/>
+      <c r="L221" s="47"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="26"/>
@@ -6606,7 +7813,7 @@
       <c r="I222" s="41"/>
       <c r="J222" s="28"/>
       <c r="K222" s="28"/>
-      <c r="L222" s="48"/>
+      <c r="L222" s="47"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="26"/>
@@ -6620,7 +7827,7 @@
       <c r="I223" s="41"/>
       <c r="J223" s="28"/>
       <c r="K223" s="28"/>
-      <c r="L223" s="48"/>
+      <c r="L223" s="47"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="26"/>
@@ -6634,7 +7841,7 @@
       <c r="I224" s="41"/>
       <c r="J224" s="28"/>
       <c r="K224" s="28"/>
-      <c r="L224" s="48"/>
+      <c r="L224" s="47"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="26"/>
@@ -6648,7 +7855,7 @@
       <c r="I225" s="41"/>
       <c r="J225" s="28"/>
       <c r="K225" s="28"/>
-      <c r="L225" s="48"/>
+      <c r="L225" s="47"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="26"/>
@@ -6662,7 +7869,7 @@
       <c r="I226" s="41"/>
       <c r="J226" s="28"/>
       <c r="K226" s="28"/>
-      <c r="L226" s="48"/>
+      <c r="L226" s="47"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="26"/>
@@ -6676,7 +7883,7 @@
       <c r="I227" s="41"/>
       <c r="J227" s="28"/>
       <c r="K227" s="28"/>
-      <c r="L227" s="48"/>
+      <c r="L227" s="47"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="26"/>
@@ -6690,7 +7897,7 @@
       <c r="I228" s="41"/>
       <c r="J228" s="28"/>
       <c r="K228" s="28"/>
-      <c r="L228" s="48"/>
+      <c r="L228" s="47"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="26"/>
@@ -6704,7 +7911,7 @@
       <c r="I229" s="41"/>
       <c r="J229" s="28"/>
       <c r="K229" s="28"/>
-      <c r="L229" s="48"/>
+      <c r="L229" s="47"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="26"/>
@@ -6718,7 +7925,7 @@
       <c r="I230" s="41"/>
       <c r="J230" s="28"/>
       <c r="K230" s="28"/>
-      <c r="L230" s="48"/>
+      <c r="L230" s="47"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="26"/>
@@ -6732,7 +7939,7 @@
       <c r="I231" s="41"/>
       <c r="J231" s="28"/>
       <c r="K231" s="28"/>
-      <c r="L231" s="48"/>
+      <c r="L231" s="47"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="26"/>
@@ -6746,7 +7953,7 @@
       <c r="I232" s="41"/>
       <c r="J232" s="28"/>
       <c r="K232" s="28"/>
-      <c r="L232" s="48"/>
+      <c r="L232" s="47"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="26"/>
@@ -6760,7 +7967,7 @@
       <c r="I233" s="41"/>
       <c r="J233" s="28"/>
       <c r="K233" s="28"/>
-      <c r="L233" s="48"/>
+      <c r="L233" s="47"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="26"/>
@@ -6774,7 +7981,7 @@
       <c r="I234" s="41"/>
       <c r="J234" s="28"/>
       <c r="K234" s="28"/>
-      <c r="L234" s="48"/>
+      <c r="L234" s="47"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="26"/>
@@ -6788,7 +7995,7 @@
       <c r="I235" s="41"/>
       <c r="J235" s="28"/>
       <c r="K235" s="28"/>
-      <c r="L235" s="48"/>
+      <c r="L235" s="47"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="26"/>
@@ -6802,7 +8009,7 @@
       <c r="I236" s="41"/>
       <c r="J236" s="28"/>
       <c r="K236" s="28"/>
-      <c r="L236" s="48"/>
+      <c r="L236" s="47"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="26"/>
@@ -6816,7 +8023,7 @@
       <c r="I237" s="41"/>
       <c r="J237" s="28"/>
       <c r="K237" s="28"/>
-      <c r="L237" s="48"/>
+      <c r="L237" s="47"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="26"/>
@@ -6830,7 +8037,7 @@
       <c r="I238" s="41"/>
       <c r="J238" s="28"/>
       <c r="K238" s="28"/>
-      <c r="L238" s="48"/>
+      <c r="L238" s="47"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="26"/>
@@ -6844,7 +8051,7 @@
       <c r="I239" s="41"/>
       <c r="J239" s="28"/>
       <c r="K239" s="28"/>
-      <c r="L239" s="48"/>
+      <c r="L239" s="47"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="26"/>
@@ -6858,7 +8065,7 @@
       <c r="I240" s="41"/>
       <c r="J240" s="28"/>
       <c r="K240" s="28"/>
-      <c r="L240" s="48"/>
+      <c r="L240" s="47"/>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="26"/>
@@ -6872,7 +8079,7 @@
       <c r="I241" s="41"/>
       <c r="J241" s="28"/>
       <c r="K241" s="28"/>
-      <c r="L241" s="48"/>
+      <c r="L241" s="47"/>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="26"/>
@@ -6886,7 +8093,7 @@
       <c r="I242" s="41"/>
       <c r="J242" s="28"/>
       <c r="K242" s="28"/>
-      <c r="L242" s="48"/>
+      <c r="L242" s="47"/>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="26"/>
@@ -6900,7 +8107,7 @@
       <c r="I243" s="41"/>
       <c r="J243" s="28"/>
       <c r="K243" s="28"/>
-      <c r="L243" s="48"/>
+      <c r="L243" s="47"/>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="26"/>
@@ -6914,7 +8121,7 @@
       <c r="I244" s="41"/>
       <c r="J244" s="28"/>
       <c r="K244" s="28"/>
-      <c r="L244" s="48"/>
+      <c r="L244" s="47"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="26"/>
@@ -6928,7 +8135,7 @@
       <c r="I245" s="41"/>
       <c r="J245" s="28"/>
       <c r="K245" s="28"/>
-      <c r="L245" s="48"/>
+      <c r="L245" s="47"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="26"/>
@@ -6942,7 +8149,7 @@
       <c r="I246" s="41"/>
       <c r="J246" s="28"/>
       <c r="K246" s="28"/>
-      <c r="L246" s="48"/>
+      <c r="L246" s="47"/>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="26"/>
@@ -6956,7 +8163,7 @@
       <c r="I247" s="41"/>
       <c r="J247" s="28"/>
       <c r="K247" s="28"/>
-      <c r="L247" s="48"/>
+      <c r="L247" s="47"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="26"/>
@@ -6970,7 +8177,7 @@
       <c r="I248" s="41"/>
       <c r="J248" s="28"/>
       <c r="K248" s="28"/>
-      <c r="L248" s="48"/>
+      <c r="L248" s="47"/>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="26"/>
@@ -6984,7 +8191,7 @@
       <c r="I249" s="41"/>
       <c r="J249" s="28"/>
       <c r="K249" s="28"/>
-      <c r="L249" s="48"/>
+      <c r="L249" s="47"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="26"/>
@@ -6998,7 +8205,7 @@
       <c r="I250" s="41"/>
       <c r="J250" s="28"/>
       <c r="K250" s="28"/>
-      <c r="L250" s="48"/>
+      <c r="L250" s="47"/>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="26"/>
@@ -7012,7 +8219,7 @@
       <c r="I251" s="41"/>
       <c r="J251" s="28"/>
       <c r="K251" s="28"/>
-      <c r="L251" s="48"/>
+      <c r="L251" s="47"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="26"/>
@@ -7026,7 +8233,7 @@
       <c r="I252" s="41"/>
       <c r="J252" s="28"/>
       <c r="K252" s="28"/>
-      <c r="L252" s="48"/>
+      <c r="L252" s="47"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="26"/>
@@ -7040,7 +8247,7 @@
       <c r="I253" s="41"/>
       <c r="J253" s="28"/>
       <c r="K253" s="28"/>
-      <c r="L253" s="48"/>
+      <c r="L253" s="47"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="26"/>
@@ -7054,7 +8261,7 @@
       <c r="I254" s="41"/>
       <c r="J254" s="28"/>
       <c r="K254" s="28"/>
-      <c r="L254" s="48"/>
+      <c r="L254" s="47"/>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="26"/>
@@ -7068,7 +8275,7 @@
       <c r="I255" s="41"/>
       <c r="J255" s="28"/>
       <c r="K255" s="28"/>
-      <c r="L255" s="48"/>
+      <c r="L255" s="47"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="26"/>
@@ -7082,7 +8289,7 @@
       <c r="I256" s="41"/>
       <c r="J256" s="28"/>
       <c r="K256" s="28"/>
-      <c r="L256" s="48"/>
+      <c r="L256" s="47"/>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="26"/>
@@ -7096,7 +8303,7 @@
       <c r="I257" s="41"/>
       <c r="J257" s="28"/>
       <c r="K257" s="28"/>
-      <c r="L257" s="48"/>
+      <c r="L257" s="47"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="26"/>
@@ -7110,7 +8317,7 @@
       <c r="I258" s="41"/>
       <c r="J258" s="28"/>
       <c r="K258" s="28"/>
-      <c r="L258" s="48"/>
+      <c r="L258" s="47"/>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="26"/>
@@ -7124,7 +8331,7 @@
       <c r="I259" s="41"/>
       <c r="J259" s="28"/>
       <c r="K259" s="28"/>
-      <c r="L259" s="48"/>
+      <c r="L259" s="47"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="26"/>
@@ -7138,7 +8345,7 @@
       <c r="I260" s="41"/>
       <c r="J260" s="28"/>
       <c r="K260" s="28"/>
-      <c r="L260" s="48"/>
+      <c r="L260" s="47"/>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="26"/>
@@ -7152,7 +8359,7 @@
       <c r="I261" s="41"/>
       <c r="J261" s="28"/>
       <c r="K261" s="28"/>
-      <c r="L261" s="48"/>
+      <c r="L261" s="47"/>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="26"/>
@@ -7166,7 +8373,7 @@
       <c r="I262" s="41"/>
       <c r="J262" s="28"/>
       <c r="K262" s="28"/>
-      <c r="L262" s="48"/>
+      <c r="L262" s="47"/>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="26"/>
@@ -7180,7 +8387,7 @@
       <c r="I263" s="41"/>
       <c r="J263" s="28"/>
       <c r="K263" s="28"/>
-      <c r="L263" s="48"/>
+      <c r="L263" s="47"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="26"/>
@@ -7194,7 +8401,7 @@
       <c r="I264" s="41"/>
       <c r="J264" s="28"/>
       <c r="K264" s="28"/>
-      <c r="L264" s="48"/>
+      <c r="L264" s="47"/>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="26"/>
@@ -7208,7 +8415,7 @@
       <c r="I265" s="41"/>
       <c r="J265" s="28"/>
       <c r="K265" s="28"/>
-      <c r="L265" s="48"/>
+      <c r="L265" s="47"/>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="26"/>
@@ -7222,7 +8429,7 @@
       <c r="I266" s="41"/>
       <c r="J266" s="28"/>
       <c r="K266" s="28"/>
-      <c r="L266" s="48"/>
+      <c r="L266" s="47"/>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="26"/>
@@ -7236,7 +8443,7 @@
       <c r="I267" s="41"/>
       <c r="J267" s="28"/>
       <c r="K267" s="28"/>
-      <c r="L267" s="48"/>
+      <c r="L267" s="47"/>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="26"/>
@@ -7250,7 +8457,7 @@
       <c r="I268" s="41"/>
       <c r="J268" s="28"/>
       <c r="K268" s="28"/>
-      <c r="L268" s="48"/>
+      <c r="L268" s="47"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="26"/>
@@ -7264,7 +8471,7 @@
       <c r="I269" s="41"/>
       <c r="J269" s="28"/>
       <c r="K269" s="28"/>
-      <c r="L269" s="48"/>
+      <c r="L269" s="47"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="26"/>
@@ -7278,7 +8485,7 @@
       <c r="I270" s="41"/>
       <c r="J270" s="28"/>
       <c r="K270" s="28"/>
-      <c r="L270" s="48"/>
+      <c r="L270" s="47"/>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="26"/>
@@ -7292,7 +8499,7 @@
       <c r="I271" s="41"/>
       <c r="J271" s="28"/>
       <c r="K271" s="28"/>
-      <c r="L271" s="48"/>
+      <c r="L271" s="47"/>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="26"/>
@@ -7306,7 +8513,7 @@
       <c r="I272" s="41"/>
       <c r="J272" s="28"/>
       <c r="K272" s="28"/>
-      <c r="L272" s="48"/>
+      <c r="L272" s="47"/>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="26"/>
@@ -7320,7 +8527,7 @@
       <c r="I273" s="41"/>
       <c r="J273" s="28"/>
       <c r="K273" s="28"/>
-      <c r="L273" s="48"/>
+      <c r="L273" s="47"/>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="26"/>
@@ -7334,7 +8541,7 @@
       <c r="I274" s="41"/>
       <c r="J274" s="28"/>
       <c r="K274" s="28"/>
-      <c r="L274" s="48"/>
+      <c r="L274" s="47"/>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="26"/>
@@ -7348,7 +8555,7 @@
       <c r="I275" s="41"/>
       <c r="J275" s="28"/>
       <c r="K275" s="28"/>
-      <c r="L275" s="48"/>
+      <c r="L275" s="47"/>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="26"/>
@@ -7362,7 +8569,7 @@
       <c r="I276" s="41"/>
       <c r="J276" s="28"/>
       <c r="K276" s="28"/>
-      <c r="L276" s="48"/>
+      <c r="L276" s="47"/>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="26"/>
@@ -7376,7 +8583,7 @@
       <c r="I277" s="41"/>
       <c r="J277" s="28"/>
       <c r="K277" s="28"/>
-      <c r="L277" s="48"/>
+      <c r="L277" s="47"/>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="26"/>
@@ -7390,7 +8597,7 @@
       <c r="I278" s="41"/>
       <c r="J278" s="28"/>
       <c r="K278" s="28"/>
-      <c r="L278" s="48"/>
+      <c r="L278" s="47"/>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="26"/>
@@ -7404,7 +8611,7 @@
       <c r="I279" s="41"/>
       <c r="J279" s="28"/>
       <c r="K279" s="28"/>
-      <c r="L279" s="48"/>
+      <c r="L279" s="47"/>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="26"/>
@@ -7418,7 +8625,7 @@
       <c r="I280" s="41"/>
       <c r="J280" s="28"/>
       <c r="K280" s="28"/>
-      <c r="L280" s="48"/>
+      <c r="L280" s="47"/>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="26"/>
@@ -7432,7 +8639,7 @@
       <c r="I281" s="41"/>
       <c r="J281" s="28"/>
       <c r="K281" s="28"/>
-      <c r="L281" s="48"/>
+      <c r="L281" s="47"/>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="26"/>
@@ -7446,7 +8653,7 @@
       <c r="I282" s="41"/>
       <c r="J282" s="28"/>
       <c r="K282" s="28"/>
-      <c r="L282" s="48"/>
+      <c r="L282" s="47"/>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="26"/>
@@ -7460,7 +8667,7 @@
       <c r="I283" s="41"/>
       <c r="J283" s="28"/>
       <c r="K283" s="28"/>
-      <c r="L283" s="48"/>
+      <c r="L283" s="47"/>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="26"/>
@@ -7474,7 +8681,7 @@
       <c r="I284" s="41"/>
       <c r="J284" s="28"/>
       <c r="K284" s="28"/>
-      <c r="L284" s="48"/>
+      <c r="L284" s="47"/>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="26"/>
@@ -7488,7 +8695,7 @@
       <c r="I285" s="41"/>
       <c r="J285" s="28"/>
       <c r="K285" s="28"/>
-      <c r="L285" s="48"/>
+      <c r="L285" s="47"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="26"/>
@@ -7502,7 +8709,7 @@
       <c r="I286" s="41"/>
       <c r="J286" s="28"/>
       <c r="K286" s="28"/>
-      <c r="L286" s="48"/>
+      <c r="L286" s="47"/>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="26"/>
@@ -7516,7 +8723,7 @@
       <c r="I287" s="41"/>
       <c r="J287" s="28"/>
       <c r="K287" s="28"/>
-      <c r="L287" s="48"/>
+      <c r="L287" s="47"/>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="26"/>
@@ -7530,7 +8737,7 @@
       <c r="I288" s="41"/>
       <c r="J288" s="28"/>
       <c r="K288" s="28"/>
-      <c r="L288" s="48"/>
+      <c r="L288" s="47"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="26"/>
@@ -7544,7 +8751,7 @@
       <c r="I289" s="41"/>
       <c r="J289" s="28"/>
       <c r="K289" s="28"/>
-      <c r="L289" s="48"/>
+      <c r="L289" s="47"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="26"/>
@@ -7558,7 +8765,7 @@
       <c r="I290" s="41"/>
       <c r="J290" s="28"/>
       <c r="K290" s="28"/>
-      <c r="L290" s="48"/>
+      <c r="L290" s="47"/>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="26"/>
@@ -7572,7 +8779,7 @@
       <c r="I291" s="41"/>
       <c r="J291" s="28"/>
       <c r="K291" s="28"/>
-      <c r="L291" s="48"/>
+      <c r="L291" s="47"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="26"/>
@@ -7586,7 +8793,7 @@
       <c r="I292" s="41"/>
       <c r="J292" s="28"/>
       <c r="K292" s="28"/>
-      <c r="L292" s="48"/>
+      <c r="L292" s="47"/>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="26"/>
@@ -7600,7 +8807,7 @@
       <c r="I293" s="41"/>
       <c r="J293" s="28"/>
       <c r="K293" s="28"/>
-      <c r="L293" s="48"/>
+      <c r="L293" s="47"/>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="26"/>
@@ -7614,7 +8821,7 @@
       <c r="I294" s="41"/>
       <c r="J294" s="28"/>
       <c r="K294" s="28"/>
-      <c r="L294" s="48"/>
+      <c r="L294" s="47"/>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="26"/>
@@ -7628,7 +8835,7 @@
       <c r="I295" s="41"/>
       <c r="J295" s="28"/>
       <c r="K295" s="28"/>
-      <c r="L295" s="48"/>
+      <c r="L295" s="47"/>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="26"/>
@@ -7642,7 +8849,7 @@
       <c r="I296" s="41"/>
       <c r="J296" s="28"/>
       <c r="K296" s="28"/>
-      <c r="L296" s="48"/>
+      <c r="L296" s="47"/>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="26"/>
@@ -7656,7 +8863,7 @@
       <c r="I297" s="41"/>
       <c r="J297" s="28"/>
       <c r="K297" s="28"/>
-      <c r="L297" s="48"/>
+      <c r="L297" s="47"/>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="26"/>
@@ -7670,7 +8877,7 @@
       <c r="I298" s="41"/>
       <c r="J298" s="28"/>
       <c r="K298" s="28"/>
-      <c r="L298" s="48"/>
+      <c r="L298" s="47"/>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="26"/>
@@ -7684,7 +8891,7 @@
       <c r="I299" s="41"/>
       <c r="J299" s="28"/>
       <c r="K299" s="28"/>
-      <c r="L299" s="48"/>
+      <c r="L299" s="47"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="26"/>
@@ -7698,7 +8905,7 @@
       <c r="I300" s="41"/>
       <c r="J300" s="28"/>
       <c r="K300" s="28"/>
-      <c r="L300" s="48"/>
+      <c r="L300" s="47"/>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="26"/>
@@ -7712,7 +8919,7 @@
       <c r="I301" s="41"/>
       <c r="J301" s="28"/>
       <c r="K301" s="28"/>
-      <c r="L301" s="48"/>
+      <c r="L301" s="47"/>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="26"/>
@@ -7726,7 +8933,7 @@
       <c r="I302" s="41"/>
       <c r="J302" s="28"/>
       <c r="K302" s="28"/>
-      <c r="L302" s="48"/>
+      <c r="L302" s="47"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="26"/>
@@ -7740,7 +8947,7 @@
       <c r="I303" s="41"/>
       <c r="J303" s="28"/>
       <c r="K303" s="28"/>
-      <c r="L303" s="48"/>
+      <c r="L303" s="47"/>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="26"/>
@@ -7754,7 +8961,7 @@
       <c r="I304" s="41"/>
       <c r="J304" s="28"/>
       <c r="K304" s="28"/>
-      <c r="L304" s="48"/>
+      <c r="L304" s="47"/>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="26"/>
@@ -7768,7 +8975,7 @@
       <c r="I305" s="41"/>
       <c r="J305" s="28"/>
       <c r="K305" s="28"/>
-      <c r="L305" s="48"/>
+      <c r="L305" s="47"/>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="26"/>
@@ -7782,7 +8989,7 @@
       <c r="I306" s="41"/>
       <c r="J306" s="28"/>
       <c r="K306" s="28"/>
-      <c r="L306" s="48"/>
+      <c r="L306" s="47"/>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="26"/>
@@ -7796,7 +9003,7 @@
       <c r="I307" s="41"/>
       <c r="J307" s="28"/>
       <c r="K307" s="28"/>
-      <c r="L307" s="48"/>
+      <c r="L307" s="47"/>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="26"/>
@@ -7810,7 +9017,7 @@
       <c r="I308" s="41"/>
       <c r="J308" s="28"/>
       <c r="K308" s="28"/>
-      <c r="L308" s="48"/>
+      <c r="L308" s="47"/>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="26"/>
@@ -7824,7 +9031,7 @@
       <c r="I309" s="41"/>
       <c r="J309" s="28"/>
       <c r="K309" s="28"/>
-      <c r="L309" s="48"/>
+      <c r="L309" s="47"/>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="26"/>
@@ -7838,7 +9045,7 @@
       <c r="I310" s="41"/>
       <c r="J310" s="28"/>
       <c r="K310" s="28"/>
-      <c r="L310" s="48"/>
+      <c r="L310" s="47"/>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="26"/>
@@ -7852,7 +9059,7 @@
       <c r="I311" s="41"/>
       <c r="J311" s="28"/>
       <c r="K311" s="28"/>
-      <c r="L311" s="48"/>
+      <c r="L311" s="47"/>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="26"/>
@@ -7866,7 +9073,7 @@
       <c r="I312" s="41"/>
       <c r="J312" s="28"/>
       <c r="K312" s="28"/>
-      <c r="L312" s="48"/>
+      <c r="L312" s="47"/>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="26"/>
@@ -7880,7 +9087,7 @@
       <c r="I313" s="41"/>
       <c r="J313" s="28"/>
       <c r="K313" s="28"/>
-      <c r="L313" s="48"/>
+      <c r="L313" s="47"/>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="26"/>
@@ -7894,7 +9101,7 @@
       <c r="I314" s="41"/>
       <c r="J314" s="28"/>
       <c r="K314" s="28"/>
-      <c r="L314" s="48"/>
+      <c r="L314" s="47"/>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="26"/>
@@ -7908,7 +9115,7 @@
       <c r="I315" s="41"/>
       <c r="J315" s="28"/>
       <c r="K315" s="28"/>
-      <c r="L315" s="48"/>
+      <c r="L315" s="47"/>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="26"/>
@@ -7922,7 +9129,7 @@
       <c r="I316" s="41"/>
       <c r="J316" s="28"/>
       <c r="K316" s="28"/>
-      <c r="L316" s="48"/>
+      <c r="L316" s="47"/>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="26"/>
@@ -7936,45 +9143,23 @@
       <c r="I317" s="41"/>
       <c r="J317" s="28"/>
       <c r="K317" s="28"/>
-      <c r="L317" s="48"/>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A318" s="26"/>
-      <c r="B318" s="26"/>
-      <c r="C318" s="26"/>
-      <c r="D318" s="26"/>
-      <c r="E318" s="5"/>
-      <c r="F318" s="26"/>
-      <c r="G318" s="5"/>
-      <c r="H318" s="26"/>
-      <c r="I318" s="41"/>
-      <c r="J318" s="28"/>
-      <c r="K318" s="28"/>
-      <c r="L318" s="48"/>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A319" s="26"/>
-      <c r="B319" s="26"/>
-      <c r="C319" s="26"/>
-      <c r="D319" s="26"/>
-      <c r="E319" s="5"/>
-      <c r="F319" s="26"/>
-      <c r="G319" s="5"/>
-      <c r="H319" s="26"/>
-      <c r="I319" s="41"/>
-      <c r="J319" s="28"/>
-      <c r="K319" s="28"/>
-      <c r="L319" s="48"/>
-    </row>
-    <row r="1048576" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1048576" s="26" t="s">
-        <v>190</v>
+      <c r="L317" s="47"/>
+    </row>
+    <row r="1048574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1048574" s="26" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:L145" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Minoc"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D51:D57 D2:D43 D59:D72 D74:D319" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D51:D57 D2:D43 D59:D72 D114:D115 D117:D317 D74:D110" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/spoilers/trades.xlsx
+++ b/spoilers/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0296F742-0C33-46F1-A098-A3C0F3D704B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26527552-570C-4726-97D9-8BE2B99A3482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1266,7 +1266,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1725,7 +1725,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L1048574"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1781,7 +1780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>32</v>
       </c>
@@ -1815,7 +1814,7 @@
       </c>
       <c r="L2" s="36"/>
     </row>
-    <row r="3" spans="1:12" ht="52.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>32</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
@@ -1993,7 +1992,7 @@
       </c>
       <c r="L7" s="36"/>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
@@ -2027,7 +2026,7 @@
       </c>
       <c r="L8" s="36"/>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>32</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
@@ -2169,7 +2168,7 @@
       </c>
       <c r="L12" s="36"/>
     </row>
-    <row r="13" spans="1:12" ht="79.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
@@ -2207,7 +2206,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>32</v>
       </c>
@@ -2241,7 +2240,7 @@
       </c>
       <c r="L14" s="36"/>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
@@ -2275,7 +2274,7 @@
       </c>
       <c r="L15" s="36"/>
     </row>
-    <row r="16" spans="1:12" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>32</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
@@ -2347,7 +2346,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>32</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>32</v>
       </c>
@@ -2419,7 +2418,7 @@
       </c>
       <c r="L19" s="36"/>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>32</v>
       </c>
@@ -2453,7 +2452,7 @@
       </c>
       <c r="L20" s="36"/>
     </row>
-    <row r="21" spans="1:12" s="13" customFormat="1" ht="52.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" s="13" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>32</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>32</v>
       </c>
@@ -2523,7 +2522,7 @@
       </c>
       <c r="L22" s="38"/>
     </row>
-    <row r="23" spans="1:12" s="13" customFormat="1" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" s="13" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
         <v>32</v>
       </c>
@@ -2561,7 +2560,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="59" t="s">
         <v>32</v>
       </c>
@@ -2595,7 +2594,7 @@
       </c>
       <c r="L24" s="46"/>
     </row>
-    <row r="25" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="59" t="s">
         <v>32</v>
       </c>
@@ -2629,7 +2628,7 @@
       </c>
       <c r="L25" s="46"/>
     </row>
-    <row r="26" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>32</v>
       </c>
@@ -2663,7 +2662,7 @@
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="59" t="s">
         <v>32</v>
       </c>
@@ -2697,7 +2696,7 @@
       </c>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="59" t="s">
         <v>32</v>
       </c>
@@ -2733,7 +2732,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="59" t="s">
         <v>32</v>
       </c>
@@ -2767,7 +2766,7 @@
       </c>
       <c r="L29" s="48"/>
     </row>
-    <row r="30" spans="1:12" s="8" customFormat="1" ht="112.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" s="8" customFormat="1" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="59" t="s">
         <v>32</v>
       </c>
@@ -2805,7 +2804,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="8" customFormat="1" ht="74.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" s="8" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="59" t="s">
         <v>32</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="59" t="s">
         <v>32</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="59" t="s">
         <v>32</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A34" s="59" t="s">
         <v>32</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="59" t="s">
         <v>32</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="59" t="s">
         <v>32</v>
       </c>
@@ -3023,7 +3022,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="30" customFormat="1" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" s="30" customFormat="1" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>32</v>
       </c>
@@ -3059,7 +3058,7 @@
       </c>
       <c r="L37" s="50"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>32</v>
       </c>
@@ -3093,7 +3092,7 @@
       </c>
       <c r="L38" s="46"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>32</v>
       </c>
@@ -3127,7 +3126,7 @@
       </c>
       <c r="L39" s="46"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>32</v>
       </c>
@@ -3161,7 +3160,7 @@
       </c>
       <c r="L40" s="46"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>32</v>
       </c>
@@ -3195,7 +3194,7 @@
       </c>
       <c r="L41" s="46"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
         <v>32</v>
       </c>
@@ -3229,7 +3228,7 @@
       </c>
       <c r="L42" s="46"/>
     </row>
-    <row r="43" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A43" s="59" t="s">
         <v>32</v>
       </c>
@@ -3265,7 +3264,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="59" t="s">
         <v>32</v>
       </c>
@@ -3301,7 +3300,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="59" t="s">
         <v>32</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="59" t="s">
         <v>32</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="59" t="s">
         <v>32</v>
       </c>
@@ -3407,7 +3406,7 @@
       </c>
       <c r="L47" s="46"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="59" t="s">
         <v>32</v>
       </c>
@@ -3441,7 +3440,7 @@
       </c>
       <c r="L48" s="46"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="59" t="s">
         <v>32</v>
       </c>
@@ -3475,7 +3474,7 @@
       </c>
       <c r="L49" s="46"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="59" t="s">
         <v>32</v>
       </c>
@@ -3509,7 +3508,7 @@
       </c>
       <c r="L50" s="46"/>
     </row>
-    <row r="51" spans="1:12" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A51" s="59" t="s">
         <v>32</v>
       </c>
@@ -3545,7 +3544,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="59" t="s">
         <v>32</v>
       </c>
@@ -3579,7 +3578,7 @@
       </c>
       <c r="L52" s="46"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="59" t="s">
         <v>32</v>
       </c>
@@ -3613,7 +3612,7 @@
       </c>
       <c r="L53" s="46"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="59" t="s">
         <v>32</v>
       </c>
@@ -3647,7 +3646,7 @@
       </c>
       <c r="L54" s="46"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>32</v>
       </c>
@@ -3681,7 +3680,7 @@
       </c>
       <c r="L55" s="46"/>
     </row>
-    <row r="56" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="59" t="s">
         <v>32</v>
       </c>
@@ -3717,7 +3716,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="59" t="s">
         <v>32</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="59" t="s">
         <v>32</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="59" t="s">
         <v>32</v>
       </c>
@@ -3823,7 +3822,7 @@
       </c>
       <c r="L59" s="48"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="59" t="s">
         <v>32</v>
       </c>
@@ -3857,7 +3856,7 @@
       </c>
       <c r="L60" s="48"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="59" t="s">
         <v>32</v>
       </c>
@@ -3891,7 +3890,7 @@
       </c>
       <c r="L61" s="48"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="59" t="s">
         <v>32</v>
       </c>
@@ -3925,7 +3924,7 @@
       </c>
       <c r="L62" s="48"/>
     </row>
-    <row r="63" spans="1:12" s="27" customFormat="1" ht="25.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" s="27" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>32</v>
       </c>
@@ -3961,7 +3960,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>32</v>
       </c>
@@ -3995,7 +3994,7 @@
       </c>
       <c r="L64" s="46"/>
     </row>
-    <row r="65" spans="1:12" s="27" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>32</v>
       </c>
@@ -4031,7 +4030,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="33" t="s">
         <v>32</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>32</v>
       </c>
@@ -4105,7 +4104,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
         <v>32</v>
       </c>
@@ -4141,7 +4140,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" s="52" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
         <v>32</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>32</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" s="27" customFormat="1" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>32</v>
       </c>
@@ -4249,7 +4248,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>32</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="59" t="s">
         <v>149</v>
       </c>
@@ -4321,7 +4320,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="59" t="s">
         <v>149</v>
       </c>
@@ -4357,7 +4356,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
         <v>149</v>
       </c>
@@ -4393,7 +4392,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A76" s="59" t="s">
         <v>149</v>
       </c>
@@ -4429,7 +4428,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="59" t="s">
         <v>149</v>
       </c>
@@ -4465,7 +4464,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="59" t="s">
         <v>149</v>
       </c>
@@ -4501,7 +4500,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A79" s="61" t="s">
         <v>164</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="61" t="s">
         <v>164</v>
       </c>
@@ -4571,7 +4570,7 @@
       </c>
       <c r="L80" s="47"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="61" t="s">
         <v>164</v>
       </c>
@@ -4605,7 +4604,7 @@
       </c>
       <c r="L81" s="47"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="61" t="s">
         <v>164</v>
       </c>
@@ -4639,7 +4638,7 @@
       </c>
       <c r="L82" s="47"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="61" t="s">
         <v>164</v>
       </c>
@@ -4673,7 +4672,7 @@
       </c>
       <c r="L83" s="47"/>
     </row>
-    <row r="84" spans="1:12" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
         <v>177</v>
       </c>
@@ -4709,7 +4708,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="26" t="s">
         <v>177</v>
       </c>
@@ -4743,7 +4742,7 @@
       </c>
       <c r="L85" s="56"/>
     </row>
-    <row r="86" spans="1:12" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A86" s="26" t="s">
         <v>177</v>
       </c>
@@ -4779,7 +4778,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="27" customFormat="1" ht="276" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" s="27" customFormat="1" ht="276" x14ac:dyDescent="0.3">
       <c r="A87" s="28" t="s">
         <v>177</v>
       </c>
@@ -4817,7 +4816,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="53.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A88" s="61" t="s">
         <v>177</v>
       </c>
@@ -4853,7 +4852,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="53.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A89" s="61" t="s">
         <v>177</v>
       </c>
@@ -4889,7 +4888,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="61" t="s">
         <v>177</v>
       </c>
@@ -4923,7 +4922,7 @@
       </c>
       <c r="L90" s="56"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="61" t="s">
         <v>177</v>
       </c>
@@ -4957,7 +4956,7 @@
       </c>
       <c r="L91" s="47"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="61" t="s">
         <v>177</v>
       </c>
@@ -4991,7 +4990,7 @@
       </c>
       <c r="L92" s="47"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="61" t="s">
         <v>177</v>
       </c>
@@ -5025,7 +5024,7 @@
       </c>
       <c r="L93" s="47"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="63" t="s">
         <v>177</v>
       </c>
@@ -5043,7 +5042,7 @@
       <c r="K94" s="28"/>
       <c r="L94" s="47"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="66" t="s">
         <v>164</v>
       </c>
@@ -5061,7 +5060,7 @@
       <c r="K95" s="28"/>
       <c r="L95" s="47"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="66" t="s">
         <v>194</v>
       </c>
@@ -5079,7 +5078,7 @@
       <c r="K96" s="28"/>
       <c r="L96" s="47"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="66" t="s">
         <v>196</v>
       </c>
@@ -5097,7 +5096,7 @@
       <c r="K97" s="28"/>
       <c r="L97" s="47"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="67" t="s">
         <v>202</v>
       </c>
@@ -9151,13 +9150,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L145" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Minoc"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L145" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="D51:D57 D2:D43 D59:D72 D114:D115 D117:D317 D74:D110" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>

--- a/spoilers/trades.xlsx
+++ b/spoilers/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26527552-570C-4726-97D9-8BE2B99A3482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E017F24-F98F-44E5-8F84-816F81003A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="270">
   <si>
     <t>NBT Villager Trade Template</t>
   </si>
@@ -879,6 +879,21 @@
   </si>
   <si>
     <t>&lt;--Lore Book on Sacrifice--&gt;</t>
+  </si>
+  <si>
+    <t>Estro</t>
+  </si>
+  <si>
+    <t>Butch</t>
+  </si>
+  <si>
+    <t>Barkeep</t>
+  </si>
+  <si>
+    <t>potion (water bottle)</t>
+  </si>
+  <si>
+    <t>potion_contents: water</t>
   </si>
 </sst>
 </file>
@@ -6737,129 +6752,311 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" s="26"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="26"/>
-      <c r="D146" s="26"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="26"/>
-      <c r="G146" s="5"/>
-      <c r="H146" s="26"/>
+      <c r="A146" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C146" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D146" s="26">
+        <v>1</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F146" s="26">
+        <v>3</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H146" s="26">
+        <v>1</v>
+      </c>
       <c r="I146" s="41"/>
-      <c r="J146" s="28"/>
-      <c r="K146" s="28"/>
+      <c r="J146" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K146" s="28">
+        <v>10</v>
+      </c>
       <c r="L146" s="47"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" s="26"/>
-      <c r="B147" s="26"/>
-      <c r="C147" s="26"/>
-      <c r="D147" s="26"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="26"/>
-      <c r="G147" s="5"/>
-      <c r="H147" s="26"/>
+      <c r="A147" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B147" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C147" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D147" s="26">
+        <v>1</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F147" s="26">
+        <v>6</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H147" s="26">
+        <v>2</v>
+      </c>
       <c r="I147" s="41"/>
-      <c r="J147" s="28"/>
-      <c r="K147" s="28"/>
+      <c r="J147" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K147" s="28">
+        <v>10</v>
+      </c>
       <c r="L147" s="47"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="26"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="26"/>
-      <c r="D148" s="26"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="26"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="26"/>
+      <c r="A148" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B148" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C148" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D148" s="26">
+        <v>1</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F148" s="26">
+        <v>9</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H148" s="26">
+        <v>3</v>
+      </c>
       <c r="I148" s="41"/>
-      <c r="J148" s="28"/>
-      <c r="K148" s="28"/>
+      <c r="J148" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K148" s="28">
+        <v>10</v>
+      </c>
       <c r="L148" s="47"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" s="26"/>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="26"/>
+      <c r="A149" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B149" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C149" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D149" s="26">
+        <v>1</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F149" s="26">
+        <v>5</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H149" s="26">
+        <v>1</v>
+      </c>
       <c r="I149" s="41"/>
-      <c r="J149" s="28"/>
-      <c r="K149" s="28"/>
+      <c r="J149" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K149" s="28">
+        <v>1</v>
+      </c>
       <c r="L149" s="47"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" s="26"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="26"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="26"/>
+      <c r="A150" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B150" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C150" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D150" s="26">
+        <v>1</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F150" s="26">
+        <v>2</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H150" s="26">
+        <v>1</v>
+      </c>
       <c r="I150" s="41"/>
-      <c r="J150" s="28"/>
-      <c r="K150" s="28"/>
+      <c r="J150" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K150" s="28">
+        <v>1</v>
+      </c>
       <c r="L150" s="47"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" s="26"/>
-      <c r="B151" s="26"/>
-      <c r="C151" s="26"/>
-      <c r="D151" s="26"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="26"/>
-      <c r="G151" s="5"/>
-      <c r="H151" s="26"/>
-      <c r="I151" s="41"/>
-      <c r="J151" s="28"/>
-      <c r="K151" s="28"/>
+      <c r="A151" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D151" s="26">
+        <v>1</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F151" s="26">
+        <v>1</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="H151" s="26">
+        <v>1</v>
+      </c>
+      <c r="I151" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="J151" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K151" s="28">
+        <v>1</v>
+      </c>
       <c r="L151" s="47"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A152" s="26"/>
-      <c r="B152" s="26"/>
-      <c r="C152" s="26"/>
-      <c r="D152" s="26"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="26"/>
-      <c r="G152" s="5"/>
-      <c r="H152" s="26"/>
+      <c r="A152" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C152" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D152" s="26">
+        <v>1</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F152" s="26">
+        <v>1</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="H152" s="26">
+        <v>1</v>
+      </c>
       <c r="I152" s="41"/>
-      <c r="J152" s="28"/>
-      <c r="K152" s="28"/>
+      <c r="J152" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K152" s="28">
+        <v>1</v>
+      </c>
       <c r="L152" s="47"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A153" s="26"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="26"/>
-      <c r="D153" s="26"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="26"/>
-      <c r="G153" s="5"/>
-      <c r="H153" s="26"/>
+      <c r="A153" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C153" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D153" s="26">
+        <v>1</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F153" s="26">
+        <v>1</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H153" s="26">
+        <v>1</v>
+      </c>
       <c r="I153" s="41"/>
-      <c r="J153" s="28"/>
-      <c r="K153" s="28"/>
+      <c r="J153" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K153" s="28">
+        <v>1</v>
+      </c>
       <c r="L153" s="47"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A154" s="26"/>
-      <c r="B154" s="26"/>
-      <c r="C154" s="26"/>
-      <c r="D154" s="26"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="26"/>
-      <c r="G154" s="5"/>
-      <c r="H154" s="26"/>
+      <c r="A154" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D154" s="26">
+        <v>1</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F154" s="26">
+        <v>10</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H154" s="26">
+        <v>1</v>
+      </c>
       <c r="I154" s="41"/>
-      <c r="J154" s="28"/>
-      <c r="K154" s="28"/>
+      <c r="J154" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K154" s="28">
+        <v>1</v>
+      </c>
       <c r="L154" s="47"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">

--- a/spoilers/trades.xlsx
+++ b/spoilers/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E017F24-F98F-44E5-8F84-816F81003A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0CDD2-6E7B-4E41-A648-63C8496D70D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="276">
   <si>
     <t>NBT Villager Trade Template</t>
   </si>
@@ -894,6 +894,24 @@
   </si>
   <si>
     <t>potion_contents: water</t>
+  </si>
+  <si>
+    <t>potion (Potion of Health)</t>
+  </si>
+  <si>
+    <t>potion_contents: healing</t>
+  </si>
+  <si>
+    <t>potion (Potion of Health II)</t>
+  </si>
+  <si>
+    <t>potion_contents: strong_healing</t>
+  </si>
+  <si>
+    <t>Just used as FX</t>
+  </si>
+  <si>
+    <t>Fires Sacrifice advancement "Nimble Gimble" if it hasn’t prevoiusly fired. Item icon is Health Potion.</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L1048574"/>
+  <dimension ref="A1:L1048540"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="27" customWidth="1"/>
@@ -6883,7 +6901,7 @@
         <v>999999</v>
       </c>
       <c r="K149" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L149" s="47"/>
     </row>
@@ -6917,7 +6935,7 @@
         <v>999999</v>
       </c>
       <c r="K150" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L150" s="47"/>
     </row>
@@ -6953,7 +6971,7 @@
         <v>999999</v>
       </c>
       <c r="K151" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L151" s="47"/>
     </row>
@@ -6987,7 +7005,7 @@
         <v>999999</v>
       </c>
       <c r="K152" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L152" s="47"/>
     </row>
@@ -7021,7 +7039,7 @@
         <v>999999</v>
       </c>
       <c r="K153" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L153" s="47"/>
     </row>
@@ -7055,107 +7073,259 @@
         <v>999999</v>
       </c>
       <c r="K154" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="47"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" s="26"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="26"/>
-      <c r="D155" s="26"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="26"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="26"/>
-      <c r="I155" s="41"/>
-      <c r="J155" s="28"/>
-      <c r="K155" s="28"/>
+      <c r="A155" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C155" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D155" s="26">
+        <v>1</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F155" s="26">
+        <v>1</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="H155" s="26">
+        <v>1</v>
+      </c>
+      <c r="I155" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="J155" s="28">
+        <v>3</v>
+      </c>
+      <c r="K155" s="28">
+        <v>50</v>
+      </c>
       <c r="L155" s="47"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" s="26"/>
-      <c r="B156" s="26"/>
-      <c r="C156" s="26"/>
-      <c r="D156" s="26"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="26"/>
-      <c r="G156" s="5"/>
-      <c r="H156" s="26"/>
-      <c r="I156" s="41"/>
-      <c r="J156" s="28"/>
-      <c r="K156" s="28"/>
+      <c r="A156" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B156" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C156" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D156" s="26">
+        <v>1</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F156" s="26">
+        <v>2</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H156" s="26">
+        <v>1</v>
+      </c>
+      <c r="I156" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="J156" s="28">
+        <v>3</v>
+      </c>
+      <c r="K156" s="28">
+        <v>100</v>
+      </c>
       <c r="L156" s="47"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" s="26"/>
-      <c r="B157" s="26"/>
-      <c r="C157" s="26"/>
-      <c r="D157" s="26"/>
-      <c r="E157" s="5"/>
-      <c r="F157" s="26"/>
-      <c r="G157" s="5"/>
-      <c r="H157" s="26"/>
+      <c r="A157" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C157" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D157" s="26">
+        <v>2</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F157" s="26">
+        <v>1</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H157" s="26">
+        <v>70</v>
+      </c>
       <c r="I157" s="41"/>
-      <c r="J157" s="28"/>
-      <c r="K157" s="28"/>
-      <c r="L157" s="47"/>
+      <c r="J157" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K157" s="28">
+        <v>10</v>
+      </c>
+      <c r="L157" s="47" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" s="26"/>
-      <c r="B158" s="26"/>
-      <c r="C158" s="26"/>
-      <c r="D158" s="26"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="26"/>
-      <c r="G158" s="5"/>
-      <c r="H158" s="26"/>
+      <c r="A158" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B158" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C158" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="D158" s="26">
+        <v>2</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F158" s="26">
+        <v>1</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H158" s="26">
+        <v>50</v>
+      </c>
       <c r="I158" s="41"/>
-      <c r="J158" s="28"/>
-      <c r="K158" s="28"/>
-      <c r="L158" s="47"/>
+      <c r="J158" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K158" s="28">
+        <v>10</v>
+      </c>
+      <c r="L158" s="47" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" s="26"/>
-      <c r="B159" s="26"/>
-      <c r="C159" s="26"/>
-      <c r="D159" s="26"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="26"/>
-      <c r="G159" s="5"/>
-      <c r="H159" s="26"/>
+      <c r="A159" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B159" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C159" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D159" s="26">
+        <v>1</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F159" s="26">
+        <v>1</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H159" s="26">
+        <v>1</v>
+      </c>
       <c r="I159" s="41"/>
-      <c r="J159" s="28"/>
-      <c r="K159" s="28"/>
+      <c r="J159" s="28">
+        <v>999999</v>
+      </c>
+      <c r="K159" s="28">
+        <v>10</v>
+      </c>
       <c r="L159" s="47"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" s="26"/>
-      <c r="B160" s="26"/>
-      <c r="C160" s="26"/>
-      <c r="D160" s="26"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="26"/>
-      <c r="G160" s="5"/>
-      <c r="H160" s="26"/>
+    <row r="160" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A160" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B160" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C160" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D160" s="26">
+        <v>2</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F160" s="26">
+        <v>1</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160" s="26">
+        <v>1</v>
+      </c>
       <c r="I160" s="41"/>
-      <c r="J160" s="28"/>
-      <c r="K160" s="28"/>
-      <c r="L160" s="47"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" s="26"/>
-      <c r="B161" s="26"/>
-      <c r="C161" s="26"/>
-      <c r="D161" s="26"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="26"/>
-      <c r="G161" s="5"/>
-      <c r="H161" s="26"/>
+      <c r="J160" s="28">
+        <v>1</v>
+      </c>
+      <c r="K160" s="28">
+        <v>250</v>
+      </c>
+      <c r="L160" s="47" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A161" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C161" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D161" s="26">
+        <v>2</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F161" s="26">
+        <v>1</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H161" s="26">
+        <v>1</v>
+      </c>
       <c r="I161" s="41"/>
-      <c r="J161" s="28"/>
-      <c r="K161" s="28"/>
-      <c r="L161" s="47"/>
+      <c r="J161" s="28">
+        <v>1</v>
+      </c>
+      <c r="K161" s="28">
+        <v>500</v>
+      </c>
+      <c r="L161" s="47" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="26"/>
@@ -8865,491 +9035,15 @@
       <c r="K283" s="28"/>
       <c r="L283" s="47"/>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A284" s="26"/>
-      <c r="B284" s="26"/>
-      <c r="C284" s="26"/>
-      <c r="D284" s="26"/>
-      <c r="E284" s="5"/>
-      <c r="F284" s="26"/>
-      <c r="G284" s="5"/>
-      <c r="H284" s="26"/>
-      <c r="I284" s="41"/>
-      <c r="J284" s="28"/>
-      <c r="K284" s="28"/>
-      <c r="L284" s="47"/>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A285" s="26"/>
-      <c r="B285" s="26"/>
-      <c r="C285" s="26"/>
-      <c r="D285" s="26"/>
-      <c r="E285" s="5"/>
-      <c r="F285" s="26"/>
-      <c r="G285" s="5"/>
-      <c r="H285" s="26"/>
-      <c r="I285" s="41"/>
-      <c r="J285" s="28"/>
-      <c r="K285" s="28"/>
-      <c r="L285" s="47"/>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A286" s="26"/>
-      <c r="B286" s="26"/>
-      <c r="C286" s="26"/>
-      <c r="D286" s="26"/>
-      <c r="E286" s="5"/>
-      <c r="F286" s="26"/>
-      <c r="G286" s="5"/>
-      <c r="H286" s="26"/>
-      <c r="I286" s="41"/>
-      <c r="J286" s="28"/>
-      <c r="K286" s="28"/>
-      <c r="L286" s="47"/>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A287" s="26"/>
-      <c r="B287" s="26"/>
-      <c r="C287" s="26"/>
-      <c r="D287" s="26"/>
-      <c r="E287" s="5"/>
-      <c r="F287" s="26"/>
-      <c r="G287" s="5"/>
-      <c r="H287" s="26"/>
-      <c r="I287" s="41"/>
-      <c r="J287" s="28"/>
-      <c r="K287" s="28"/>
-      <c r="L287" s="47"/>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A288" s="26"/>
-      <c r="B288" s="26"/>
-      <c r="C288" s="26"/>
-      <c r="D288" s="26"/>
-      <c r="E288" s="5"/>
-      <c r="F288" s="26"/>
-      <c r="G288" s="5"/>
-      <c r="H288" s="26"/>
-      <c r="I288" s="41"/>
-      <c r="J288" s="28"/>
-      <c r="K288" s="28"/>
-      <c r="L288" s="47"/>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A289" s="26"/>
-      <c r="B289" s="26"/>
-      <c r="C289" s="26"/>
-      <c r="D289" s="26"/>
-      <c r="E289" s="5"/>
-      <c r="F289" s="26"/>
-      <c r="G289" s="5"/>
-      <c r="H289" s="26"/>
-      <c r="I289" s="41"/>
-      <c r="J289" s="28"/>
-      <c r="K289" s="28"/>
-      <c r="L289" s="47"/>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A290" s="26"/>
-      <c r="B290" s="26"/>
-      <c r="C290" s="26"/>
-      <c r="D290" s="26"/>
-      <c r="E290" s="5"/>
-      <c r="F290" s="26"/>
-      <c r="G290" s="5"/>
-      <c r="H290" s="26"/>
-      <c r="I290" s="41"/>
-      <c r="J290" s="28"/>
-      <c r="K290" s="28"/>
-      <c r="L290" s="47"/>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A291" s="26"/>
-      <c r="B291" s="26"/>
-      <c r="C291" s="26"/>
-      <c r="D291" s="26"/>
-      <c r="E291" s="5"/>
-      <c r="F291" s="26"/>
-      <c r="G291" s="5"/>
-      <c r="H291" s="26"/>
-      <c r="I291" s="41"/>
-      <c r="J291" s="28"/>
-      <c r="K291" s="28"/>
-      <c r="L291" s="47"/>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A292" s="26"/>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="5"/>
-      <c r="F292" s="26"/>
-      <c r="G292" s="5"/>
-      <c r="H292" s="26"/>
-      <c r="I292" s="41"/>
-      <c r="J292" s="28"/>
-      <c r="K292" s="28"/>
-      <c r="L292" s="47"/>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A293" s="26"/>
-      <c r="B293" s="26"/>
-      <c r="C293" s="26"/>
-      <c r="D293" s="26"/>
-      <c r="E293" s="5"/>
-      <c r="F293" s="26"/>
-      <c r="G293" s="5"/>
-      <c r="H293" s="26"/>
-      <c r="I293" s="41"/>
-      <c r="J293" s="28"/>
-      <c r="K293" s="28"/>
-      <c r="L293" s="47"/>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A294" s="26"/>
-      <c r="B294" s="26"/>
-      <c r="C294" s="26"/>
-      <c r="D294" s="26"/>
-      <c r="E294" s="5"/>
-      <c r="F294" s="26"/>
-      <c r="G294" s="5"/>
-      <c r="H294" s="26"/>
-      <c r="I294" s="41"/>
-      <c r="J294" s="28"/>
-      <c r="K294" s="28"/>
-      <c r="L294" s="47"/>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A295" s="26"/>
-      <c r="B295" s="26"/>
-      <c r="C295" s="26"/>
-      <c r="D295" s="26"/>
-      <c r="E295" s="5"/>
-      <c r="F295" s="26"/>
-      <c r="G295" s="5"/>
-      <c r="H295" s="26"/>
-      <c r="I295" s="41"/>
-      <c r="J295" s="28"/>
-      <c r="K295" s="28"/>
-      <c r="L295" s="47"/>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A296" s="26"/>
-      <c r="B296" s="26"/>
-      <c r="C296" s="26"/>
-      <c r="D296" s="26"/>
-      <c r="E296" s="5"/>
-      <c r="F296" s="26"/>
-      <c r="G296" s="5"/>
-      <c r="H296" s="26"/>
-      <c r="I296" s="41"/>
-      <c r="J296" s="28"/>
-      <c r="K296" s="28"/>
-      <c r="L296" s="47"/>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A297" s="26"/>
-      <c r="B297" s="26"/>
-      <c r="C297" s="26"/>
-      <c r="D297" s="26"/>
-      <c r="E297" s="5"/>
-      <c r="F297" s="26"/>
-      <c r="G297" s="5"/>
-      <c r="H297" s="26"/>
-      <c r="I297" s="41"/>
-      <c r="J297" s="28"/>
-      <c r="K297" s="28"/>
-      <c r="L297" s="47"/>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A298" s="26"/>
-      <c r="B298" s="26"/>
-      <c r="C298" s="26"/>
-      <c r="D298" s="26"/>
-      <c r="E298" s="5"/>
-      <c r="F298" s="26"/>
-      <c r="G298" s="5"/>
-      <c r="H298" s="26"/>
-      <c r="I298" s="41"/>
-      <c r="J298" s="28"/>
-      <c r="K298" s="28"/>
-      <c r="L298" s="47"/>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A299" s="26"/>
-      <c r="B299" s="26"/>
-      <c r="C299" s="26"/>
-      <c r="D299" s="26"/>
-      <c r="E299" s="5"/>
-      <c r="F299" s="26"/>
-      <c r="G299" s="5"/>
-      <c r="H299" s="26"/>
-      <c r="I299" s="41"/>
-      <c r="J299" s="28"/>
-      <c r="K299" s="28"/>
-      <c r="L299" s="47"/>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A300" s="26"/>
-      <c r="B300" s="26"/>
-      <c r="C300" s="26"/>
-      <c r="D300" s="26"/>
-      <c r="E300" s="5"/>
-      <c r="F300" s="26"/>
-      <c r="G300" s="5"/>
-      <c r="H300" s="26"/>
-      <c r="I300" s="41"/>
-      <c r="J300" s="28"/>
-      <c r="K300" s="28"/>
-      <c r="L300" s="47"/>
-    </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A301" s="26"/>
-      <c r="B301" s="26"/>
-      <c r="C301" s="26"/>
-      <c r="D301" s="26"/>
-      <c r="E301" s="5"/>
-      <c r="F301" s="26"/>
-      <c r="G301" s="5"/>
-      <c r="H301" s="26"/>
-      <c r="I301" s="41"/>
-      <c r="J301" s="28"/>
-      <c r="K301" s="28"/>
-      <c r="L301" s="47"/>
-    </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A302" s="26"/>
-      <c r="B302" s="26"/>
-      <c r="C302" s="26"/>
-      <c r="D302" s="26"/>
-      <c r="E302" s="5"/>
-      <c r="F302" s="26"/>
-      <c r="G302" s="5"/>
-      <c r="H302" s="26"/>
-      <c r="I302" s="41"/>
-      <c r="J302" s="28"/>
-      <c r="K302" s="28"/>
-      <c r="L302" s="47"/>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A303" s="26"/>
-      <c r="B303" s="26"/>
-      <c r="C303" s="26"/>
-      <c r="D303" s="26"/>
-      <c r="E303" s="5"/>
-      <c r="F303" s="26"/>
-      <c r="G303" s="5"/>
-      <c r="H303" s="26"/>
-      <c r="I303" s="41"/>
-      <c r="J303" s="28"/>
-      <c r="K303" s="28"/>
-      <c r="L303" s="47"/>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A304" s="26"/>
-      <c r="B304" s="26"/>
-      <c r="C304" s="26"/>
-      <c r="D304" s="26"/>
-      <c r="E304" s="5"/>
-      <c r="F304" s="26"/>
-      <c r="G304" s="5"/>
-      <c r="H304" s="26"/>
-      <c r="I304" s="41"/>
-      <c r="J304" s="28"/>
-      <c r="K304" s="28"/>
-      <c r="L304" s="47"/>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A305" s="26"/>
-      <c r="B305" s="26"/>
-      <c r="C305" s="26"/>
-      <c r="D305" s="26"/>
-      <c r="E305" s="5"/>
-      <c r="F305" s="26"/>
-      <c r="G305" s="5"/>
-      <c r="H305" s="26"/>
-      <c r="I305" s="41"/>
-      <c r="J305" s="28"/>
-      <c r="K305" s="28"/>
-      <c r="L305" s="47"/>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A306" s="26"/>
-      <c r="B306" s="26"/>
-      <c r="C306" s="26"/>
-      <c r="D306" s="26"/>
-      <c r="E306" s="5"/>
-      <c r="F306" s="26"/>
-      <c r="G306" s="5"/>
-      <c r="H306" s="26"/>
-      <c r="I306" s="41"/>
-      <c r="J306" s="28"/>
-      <c r="K306" s="28"/>
-      <c r="L306" s="47"/>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A307" s="26"/>
-      <c r="B307" s="26"/>
-      <c r="C307" s="26"/>
-      <c r="D307" s="26"/>
-      <c r="E307" s="5"/>
-      <c r="F307" s="26"/>
-      <c r="G307" s="5"/>
-      <c r="H307" s="26"/>
-      <c r="I307" s="41"/>
-      <c r="J307" s="28"/>
-      <c r="K307" s="28"/>
-      <c r="L307" s="47"/>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A308" s="26"/>
-      <c r="B308" s="26"/>
-      <c r="C308" s="26"/>
-      <c r="D308" s="26"/>
-      <c r="E308" s="5"/>
-      <c r="F308" s="26"/>
-      <c r="G308" s="5"/>
-      <c r="H308" s="26"/>
-      <c r="I308" s="41"/>
-      <c r="J308" s="28"/>
-      <c r="K308" s="28"/>
-      <c r="L308" s="47"/>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A309" s="26"/>
-      <c r="B309" s="26"/>
-      <c r="C309" s="26"/>
-      <c r="D309" s="26"/>
-      <c r="E309" s="5"/>
-      <c r="F309" s="26"/>
-      <c r="G309" s="5"/>
-      <c r="H309" s="26"/>
-      <c r="I309" s="41"/>
-      <c r="J309" s="28"/>
-      <c r="K309" s="28"/>
-      <c r="L309" s="47"/>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A310" s="26"/>
-      <c r="B310" s="26"/>
-      <c r="C310" s="26"/>
-      <c r="D310" s="26"/>
-      <c r="E310" s="5"/>
-      <c r="F310" s="26"/>
-      <c r="G310" s="5"/>
-      <c r="H310" s="26"/>
-      <c r="I310" s="41"/>
-      <c r="J310" s="28"/>
-      <c r="K310" s="28"/>
-      <c r="L310" s="47"/>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A311" s="26"/>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="5"/>
-      <c r="F311" s="26"/>
-      <c r="G311" s="5"/>
-      <c r="H311" s="26"/>
-      <c r="I311" s="41"/>
-      <c r="J311" s="28"/>
-      <c r="K311" s="28"/>
-      <c r="L311" s="47"/>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A312" s="26"/>
-      <c r="B312" s="26"/>
-      <c r="C312" s="26"/>
-      <c r="D312" s="26"/>
-      <c r="E312" s="5"/>
-      <c r="F312" s="26"/>
-      <c r="G312" s="5"/>
-      <c r="H312" s="26"/>
-      <c r="I312" s="41"/>
-      <c r="J312" s="28"/>
-      <c r="K312" s="28"/>
-      <c r="L312" s="47"/>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A313" s="26"/>
-      <c r="B313" s="26"/>
-      <c r="C313" s="26"/>
-      <c r="D313" s="26"/>
-      <c r="E313" s="5"/>
-      <c r="F313" s="26"/>
-      <c r="G313" s="5"/>
-      <c r="H313" s="26"/>
-      <c r="I313" s="41"/>
-      <c r="J313" s="28"/>
-      <c r="K313" s="28"/>
-      <c r="L313" s="47"/>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A314" s="26"/>
-      <c r="B314" s="26"/>
-      <c r="C314" s="26"/>
-      <c r="D314" s="26"/>
-      <c r="E314" s="5"/>
-      <c r="F314" s="26"/>
-      <c r="G314" s="5"/>
-      <c r="H314" s="26"/>
-      <c r="I314" s="41"/>
-      <c r="J314" s="28"/>
-      <c r="K314" s="28"/>
-      <c r="L314" s="47"/>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A315" s="26"/>
-      <c r="B315" s="26"/>
-      <c r="C315" s="26"/>
-      <c r="D315" s="26"/>
-      <c r="E315" s="5"/>
-      <c r="F315" s="26"/>
-      <c r="G315" s="5"/>
-      <c r="H315" s="26"/>
-      <c r="I315" s="41"/>
-      <c r="J315" s="28"/>
-      <c r="K315" s="28"/>
-      <c r="L315" s="47"/>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A316" s="26"/>
-      <c r="B316" s="26"/>
-      <c r="C316" s="26"/>
-      <c r="D316" s="26"/>
-      <c r="E316" s="5"/>
-      <c r="F316" s="26"/>
-      <c r="G316" s="5"/>
-      <c r="H316" s="26"/>
-      <c r="I316" s="41"/>
-      <c r="J316" s="28"/>
-      <c r="K316" s="28"/>
-      <c r="L316" s="47"/>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A317" s="26"/>
-      <c r="B317" s="26"/>
-      <c r="C317" s="26"/>
-      <c r="D317" s="26"/>
-      <c r="E317" s="5"/>
-      <c r="F317" s="26"/>
-      <c r="G317" s="5"/>
-      <c r="H317" s="26"/>
-      <c r="I317" s="41"/>
-      <c r="J317" s="28"/>
-      <c r="K317" s="28"/>
-      <c r="L317" s="47"/>
-    </row>
-    <row r="1048574" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1048574" s="26" t="s">
+    <row r="1048540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1048540" s="26" t="s">
         <v>188</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L145" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D51:D57 D2:D43 D59:D72 D114:D115 D117:D317 D74:D110" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D51:D57 D2:D43 D59:D72 D114:D115 D74:D110 D117:D283" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
